--- a/youzi/大小说家/index.xlsx
+++ b/youzi/大小说家/index.xlsx
@@ -45,79 +45,427 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF228F3B"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE46370"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF7ECA90"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9EA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4352"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFCF2F3E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEAF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
+        <fgColor rgb="FF45B25E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -129,12 +477,288 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEFF0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBE3C4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8E1C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB9199"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CDD1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91D2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -147,6 +771,210 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15663"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF3F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDE4C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -159,253 +987,1489 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91D2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBD5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF59BB6F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3DAF57"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8336"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD75"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7833"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF35AC50"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3948"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4453"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAEFDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBD6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF37AD52"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB766"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF73C586"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4BB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7E1C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2DA949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB4E0BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD23040"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9EA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4352"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42331"/>
+        <fgColor rgb="FF7BC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8790"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFC"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -417,2058 +2481,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF5C9CD"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B25E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBE3C4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEFF0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB9199"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CDD1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8E1C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91D2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15663"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDE4C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF3F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91D2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEB9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFEBD5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEB9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEB9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8336"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7833"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3DAF57"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD75"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF59BB6F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF35AC50"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4453"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFEBD6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3948"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAEFDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF37AD52"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB766"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF73C586"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2DA949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB4E0BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8790"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4BB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7BC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -2481,66 +2529,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDA3444"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFAD202D"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFAD202D"/>
         <bgColor/>
       </patternFill>
@@ -2553,78 +2565,48 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFAD202D"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1F8538"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -2644,6 +2626,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -7434,7 +7434,7 @@
       <c r="C2" t="str">
         <v>603319</v>
       </c>
-      <c r="D2" s="11" t="str">
+      <c r="D2" s="9" t="str">
         <v>净卖: -4050.11万</v>
       </c>
       <c r="E2">
@@ -7449,40 +7449,40 @@
       <c r="H2">
         <v>-2.13</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="3">
         <v>-8.04</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="5">
         <v>-7</v>
       </c>
-      <c r="K2" s="12">
+      <c r="K2" s="10">
         <v>-0.47</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2" s="7">
         <v>3.68</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="11">
         <v>10.89</v>
       </c>
-      <c r="N2" s="3">
+      <c r="N2" s="12">
         <v>3.84</v>
       </c>
       <c r="O2" s="6">
         <v>6.4</v>
       </c>
-      <c r="P2" s="13">
+      <c r="P2" s="8">
         <v>7.52</v>
       </c>
-      <c r="Q2" s="7">
+      <c r="Q2" s="13">
         <v>-2.98</v>
       </c>
       <c r="R2" s="1">
         <v>2.88</v>
       </c>
-      <c r="S2" s="8">
+      <c r="S2" s="4">
         <v>6.19</v>
       </c>
-      <c r="T2" s="10">
+      <c r="T2" s="2">
         <v>-9.36</v>
       </c>
     </row>
@@ -7496,7 +7496,7 @@
       <c r="C3" t="str">
         <v>002923</v>
       </c>
-      <c r="D3" s="22" t="str">
+      <c r="D3" s="20" t="str">
         <v>净卖: -1342.21万</v>
       </c>
       <c r="E3">
@@ -7511,40 +7511,40 @@
       <c r="H3">
         <v>2.17</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="25">
         <v>7.69</v>
       </c>
-      <c r="J3" s="17">
+      <c r="J3" s="14">
         <v>17.63</v>
       </c>
-      <c r="K3" s="23">
+      <c r="K3" s="18">
         <v>5.88</v>
       </c>
-      <c r="L3" s="26">
+      <c r="L3" s="21">
         <v>-4.3</v>
       </c>
-      <c r="M3" s="18">
+      <c r="M3" s="15">
         <v>-13.87</v>
       </c>
-      <c r="N3" s="24">
+      <c r="N3" s="19">
         <v>-11.45</v>
       </c>
-      <c r="O3" s="15">
+      <c r="O3" s="16">
         <v>-15.08</v>
       </c>
-      <c r="P3" s="19">
+      <c r="P3" s="26">
         <v>-14.66</v>
       </c>
-      <c r="Q3" s="20">
+      <c r="Q3" s="22">
         <v>-12.84</v>
       </c>
-      <c r="R3" s="21">
+      <c r="R3" s="23">
         <v>-21.56</v>
       </c>
-      <c r="S3" s="16">
+      <c r="S3" s="17">
         <v>-24.59</v>
       </c>
-      <c r="T3" s="25">
+      <c r="T3" s="24">
         <v>-23.92</v>
       </c>
     </row>
@@ -7558,7 +7558,7 @@
       <c r="C4" t="str">
         <v>002564</v>
       </c>
-      <c r="D4" s="35" t="str">
+      <c r="D4" s="29" t="str">
         <v>净买: 1737.48万</v>
       </c>
       <c r="E4">
@@ -7573,37 +7573,37 @@
       <c r="H4">
         <v>-1.38</v>
       </c>
-      <c r="I4" s="39">
+      <c r="I4" s="35">
         <v>11.55</v>
       </c>
-      <c r="J4" s="28">
+      <c r="J4" s="36">
         <v>2.39</v>
       </c>
-      <c r="K4" s="33">
+      <c r="K4" s="37">
         <v>12.55</v>
       </c>
-      <c r="L4" s="36">
+      <c r="L4" s="38">
         <v>5.58</v>
       </c>
-      <c r="M4" s="29">
+      <c r="M4" s="39">
         <v>16.14</v>
       </c>
-      <c r="N4" s="30">
+      <c r="N4" s="27">
         <v>21.51</v>
       </c>
-      <c r="O4" s="37">
+      <c r="O4" s="32">
         <v>16.14</v>
       </c>
-      <c r="P4" s="31">
+      <c r="P4" s="28">
         <v>19.92</v>
       </c>
-      <c r="Q4" s="32">
+      <c r="Q4" s="30">
         <v>20.72</v>
       </c>
-      <c r="R4" s="38">
+      <c r="R4" s="31">
         <v>15.94</v>
       </c>
-      <c r="S4" s="27">
+      <c r="S4" s="33">
         <v>8.96</v>
       </c>
       <c r="T4" s="34">
@@ -7620,7 +7620,7 @@
       <c r="C5" t="str">
         <v>600735</v>
       </c>
-      <c r="D5" s="44" t="str">
+      <c r="D5" s="43" t="str">
         <v>净买: 1155.67万</v>
       </c>
       <c r="E5">
@@ -7635,40 +7635,40 @@
       <c r="H5">
         <v>1.24</v>
       </c>
-      <c r="I5" s="41">
+      <c r="I5" s="52">
         <v>8.71</v>
       </c>
-      <c r="J5" s="45">
+      <c r="J5" s="49">
         <v>8.84</v>
       </c>
-      <c r="K5" s="49">
+      <c r="K5" s="40">
         <v>7.48</v>
       </c>
-      <c r="L5" s="42">
+      <c r="L5" s="47">
         <v>4.63</v>
       </c>
-      <c r="M5" s="46">
+      <c r="M5" s="44">
         <v>5.71</v>
       </c>
-      <c r="N5" s="50">
+      <c r="N5" s="41">
         <v>11.16</v>
       </c>
-      <c r="O5" s="51">
+      <c r="O5" s="42">
         <v>9.66</v>
       </c>
-      <c r="P5" s="52">
+      <c r="P5" s="45">
         <v>6.8</v>
       </c>
-      <c r="Q5" s="40">
+      <c r="Q5" s="50">
         <v>12.24</v>
       </c>
-      <c r="R5" s="43">
+      <c r="R5" s="48">
         <v>13.88</v>
       </c>
-      <c r="S5" s="47">
+      <c r="S5" s="46">
         <v>10.07</v>
       </c>
-      <c r="T5" s="48">
+      <c r="T5" s="51">
         <v>-8.44</v>
       </c>
     </row>
@@ -7682,7 +7682,7 @@
       <c r="C6" t="str">
         <v>600735</v>
       </c>
-      <c r="D6" s="63" t="str">
+      <c r="D6" s="60" t="str">
         <v>净卖: -1139.95万</v>
       </c>
       <c r="E6">
@@ -7697,40 +7697,40 @@
       <c r="H6">
         <v>-5.01</v>
       </c>
-      <c r="I6" s="60">
+      <c r="I6" s="57">
         <v>5.4</v>
       </c>
       <c r="J6" s="61">
         <v>4.08</v>
       </c>
-      <c r="K6" s="64">
+      <c r="K6" s="58">
         <v>1.32</v>
       </c>
-      <c r="L6" s="65">
+      <c r="L6" s="62">
         <v>2.37</v>
       </c>
-      <c r="M6" s="56">
+      <c r="M6" s="64">
         <v>7.64</v>
       </c>
-      <c r="N6" s="57">
+      <c r="N6" s="65">
         <v>6.19</v>
       </c>
-      <c r="O6" s="58">
+      <c r="O6" s="63">
         <v>3.43</v>
       </c>
-      <c r="P6" s="62">
+      <c r="P6" s="59">
         <v>8.7</v>
       </c>
-      <c r="Q6" s="53">
+      <c r="Q6" s="54">
         <v>10.28</v>
       </c>
-      <c r="R6" s="54">
+      <c r="R6" s="55">
         <v>6.59</v>
       </c>
-      <c r="S6" s="59">
+      <c r="S6" s="53">
         <v>3.43</v>
       </c>
-      <c r="T6" s="55">
+      <c r="T6" s="56">
         <v>-11.33</v>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       <c r="C7" t="str">
         <v>002365</v>
       </c>
-      <c r="D7" s="71" t="str">
+      <c r="D7" s="66" t="str">
         <v>净卖: -2887.03万</v>
       </c>
       <c r="E7">
@@ -7759,40 +7759,40 @@
       <c r="H7">
         <v>3.76</v>
       </c>
-      <c r="I7" s="66">
+      <c r="I7" s="67">
         <v>-4.32</v>
       </c>
-      <c r="J7" s="72">
+      <c r="J7" s="74">
         <v>5.25</v>
       </c>
-      <c r="K7" s="78">
+      <c r="K7" s="71">
         <v>15.76</v>
       </c>
-      <c r="L7" s="73">
+      <c r="L7" s="78">
         <v>27.33</v>
       </c>
-      <c r="M7" s="74">
+      <c r="M7" s="75">
         <v>35.58</v>
       </c>
-      <c r="N7" s="75">
+      <c r="N7" s="68">
         <v>40.03</v>
       </c>
-      <c r="O7" s="67">
+      <c r="O7" s="69">
         <v>54.03</v>
       </c>
-      <c r="P7" s="68">
+      <c r="P7" s="76">
         <v>38.65</v>
       </c>
-      <c r="Q7" s="69">
+      <c r="Q7" s="72">
         <v>24.77</v>
       </c>
-      <c r="R7" s="76">
+      <c r="R7" s="77">
         <v>28.27</v>
       </c>
-      <c r="S7" s="77">
+      <c r="S7" s="70">
         <v>22.51</v>
       </c>
-      <c r="T7" s="70">
+      <c r="T7" s="73">
         <v>-14.7</v>
       </c>
     </row>
@@ -7806,7 +7806,7 @@
       <c r="C8" t="str">
         <v>603585</v>
       </c>
-      <c r="D8" s="84" t="str">
+      <c r="D8" s="79" t="str">
         <v>净买: 590.46万</v>
       </c>
       <c r="E8">
@@ -7821,40 +7821,40 @@
       <c r="H8">
         <v>-2.32</v>
       </c>
-      <c r="I8" s="85">
+      <c r="I8" s="86">
         <v>8.09</v>
       </c>
-      <c r="J8" s="86">
+      <c r="J8" s="80">
         <v>7.12</v>
       </c>
-      <c r="K8" s="81">
+      <c r="K8" s="89">
         <v>17.86</v>
       </c>
-      <c r="L8" s="87">
+      <c r="L8" s="81">
         <v>29.63</v>
       </c>
       <c r="M8" s="90">
         <v>16.68</v>
       </c>
-      <c r="N8" s="89">
+      <c r="N8" s="82">
         <v>5.02</v>
       </c>
-      <c r="O8" s="82">
+      <c r="O8" s="83">
         <v>0.38</v>
       </c>
-      <c r="P8" s="83">
+      <c r="P8" s="87">
         <v>2.75</v>
       </c>
-      <c r="Q8" s="88">
+      <c r="Q8" s="84">
         <v>2.05</v>
       </c>
-      <c r="R8" s="91">
+      <c r="R8" s="85">
         <v>-0.32</v>
       </c>
-      <c r="S8" s="79">
+      <c r="S8" s="91">
         <v>-1.57</v>
       </c>
-      <c r="T8" s="80">
+      <c r="T8" s="88">
         <v>29.84</v>
       </c>
     </row>
@@ -7868,7 +7868,7 @@
       <c r="C9" t="str">
         <v>003029</v>
       </c>
-      <c r="D9" s="99" t="str">
+      <c r="D9" s="103" t="str">
         <v>净卖: -1441.18万</v>
       </c>
       <c r="E9">
@@ -7883,40 +7883,40 @@
       <c r="H9">
         <v>0.04</v>
       </c>
-      <c r="I9" s="100">
+      <c r="I9" s="104">
         <v>9.96</v>
       </c>
-      <c r="J9" s="97">
+      <c r="J9" s="95">
         <v>14.48</v>
       </c>
-      <c r="K9" s="93">
+      <c r="K9" s="98">
         <v>8.49</v>
       </c>
-      <c r="L9" s="101">
+      <c r="L9" s="102">
         <v>8.99</v>
       </c>
-      <c r="M9" s="94">
+      <c r="M9" s="92">
         <v>7.77</v>
       </c>
-      <c r="N9" s="95">
+      <c r="N9" s="99">
         <v>2.72</v>
       </c>
-      <c r="O9" s="102">
+      <c r="O9" s="100">
         <v>1.22</v>
       </c>
-      <c r="P9" s="96">
+      <c r="P9" s="93">
         <v>-1.33</v>
       </c>
-      <c r="Q9" s="103">
+      <c r="Q9" s="94">
         <v>-1.65</v>
       </c>
-      <c r="R9" s="104">
+      <c r="R9" s="101">
         <v>-1.04</v>
       </c>
-      <c r="S9" s="98">
+      <c r="S9" s="96">
         <v>-2.01</v>
       </c>
-      <c r="T9" s="92">
+      <c r="T9" s="97">
         <v>-22.79</v>
       </c>
     </row>
@@ -7930,7 +7930,7 @@
       <c r="C10" t="str">
         <v>301486</v>
       </c>
-      <c r="D10" s="109" t="str">
+      <c r="D10" s="105" t="str">
         <v>净买: 2150.96万</v>
       </c>
       <c r="E10">
@@ -7945,40 +7945,40 @@
       <c r="H10">
         <v>1.79</v>
       </c>
-      <c r="I10" s="114">
+      <c r="I10" s="112">
         <v>17.9</v>
       </c>
-      <c r="J10" s="110">
+      <c r="J10" s="106">
         <v>21.2</v>
       </c>
-      <c r="K10" s="107">
+      <c r="K10" s="114">
         <v>12.29</v>
       </c>
-      <c r="L10" s="108">
+      <c r="L10" s="115">
         <v>14.55</v>
       </c>
-      <c r="M10" s="111">
+      <c r="M10" s="107">
         <v>21.65</v>
       </c>
-      <c r="N10" s="115">
+      <c r="N10" s="108">
         <v>15.36</v>
       </c>
-      <c r="O10" s="112">
+      <c r="O10" s="109">
         <v>9.81</v>
       </c>
       <c r="P10" s="116">
         <v>10.06</v>
       </c>
-      <c r="Q10" s="105">
+      <c r="Q10" s="117">
         <v>17.68</v>
       </c>
-      <c r="R10" s="117">
+      <c r="R10" s="113">
         <v>24.45</v>
       </c>
-      <c r="S10" s="106">
+      <c r="S10" s="110">
         <v>20.16</v>
       </c>
-      <c r="T10" s="113">
+      <c r="T10" s="111">
         <v>117.52</v>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       <c r="C11" t="str">
         <v>002052</v>
       </c>
-      <c r="D11" s="124" t="str">
+      <c r="D11" s="127" t="str">
         <v>净卖: -1505.16万</v>
       </c>
       <c r="E11">
@@ -8007,40 +8007,40 @@
       <c r="H11">
         <v>10.03</v>
       </c>
-      <c r="I11" s="121">
+      <c r="I11" s="128">
         <v>0</v>
       </c>
       <c r="J11" s="130">
         <v>4.18</v>
       </c>
-      <c r="K11" s="122">
+      <c r="K11" s="118">
         <v>14.59</v>
       </c>
-      <c r="L11" s="125">
+      <c r="L11" s="119">
         <v>26.06</v>
       </c>
-      <c r="M11" s="126">
+      <c r="M11" s="123">
         <v>38.68</v>
       </c>
-      <c r="N11" s="118">
+      <c r="N11" s="129">
         <v>44.38</v>
       </c>
-      <c r="O11" s="119">
+      <c r="O11" s="124">
         <v>45.82</v>
       </c>
-      <c r="P11" s="127">
+      <c r="P11" s="120">
         <v>53.88</v>
       </c>
-      <c r="Q11" s="120">
+      <c r="Q11" s="125">
         <v>45.36</v>
       </c>
-      <c r="R11" s="128">
+      <c r="R11" s="121">
         <v>34.42</v>
       </c>
-      <c r="S11" s="123">
+      <c r="S11" s="126">
         <v>39.06</v>
       </c>
-      <c r="T11" s="129">
+      <c r="T11" s="122">
         <v>-20.36</v>
       </c>
     </row>
@@ -8054,7 +8054,7 @@
       <c r="C12" t="str">
         <v>430476</v>
       </c>
-      <c r="D12" s="140" t="str">
+      <c r="D12" s="131" t="str">
         <v>净买: 566.61万</v>
       </c>
       <c r="E12">
@@ -8075,34 +8075,34 @@
       <c r="J12" s="132">
         <v>65.32</v>
       </c>
-      <c r="K12" s="143">
+      <c r="K12" s="138">
         <v>65.69</v>
       </c>
       <c r="L12" s="133">
         <v>47.53</v>
       </c>
-      <c r="M12" s="134">
+      <c r="M12" s="142">
         <v>34.9</v>
       </c>
-      <c r="N12" s="131">
+      <c r="N12" s="134">
         <v>37.51</v>
       </c>
-      <c r="O12" s="141">
+      <c r="O12" s="139">
         <v>35.45</v>
       </c>
-      <c r="P12" s="142">
+      <c r="P12" s="140">
         <v>35.86</v>
       </c>
-      <c r="Q12" s="138">
+      <c r="Q12" s="141">
         <v>29.23</v>
       </c>
-      <c r="R12" s="135">
+      <c r="R12" s="143">
         <v>29.87</v>
       </c>
-      <c r="S12" s="136">
+      <c r="S12" s="135">
         <v>29.96</v>
       </c>
-      <c r="T12" s="139">
+      <c r="T12" s="136">
         <v>14.04</v>
       </c>
     </row>
@@ -8116,7 +8116,7 @@
       <c r="C13" t="str">
         <v>871981</v>
       </c>
-      <c r="D13" s="145" t="str">
+      <c r="D13" s="149" t="str">
         <v>净买: 779.65万</v>
       </c>
       <c r="E13">
@@ -8131,40 +8131,40 @@
       <c r="H13">
         <v>10.55</v>
       </c>
-      <c r="I13" s="155">
+      <c r="I13" s="146">
         <v>17.58</v>
       </c>
-      <c r="J13" s="151">
+      <c r="J13" s="150">
         <v>17.95</v>
       </c>
-      <c r="K13" s="152">
+      <c r="K13" s="151">
         <v>13.64</v>
       </c>
-      <c r="L13" s="146">
+      <c r="L13" s="145">
         <v>14.65</v>
       </c>
-      <c r="M13" s="153">
+      <c r="M13" s="155">
         <v>17.15</v>
       </c>
-      <c r="N13" s="147">
+      <c r="N13" s="152">
         <v>11.72</v>
       </c>
-      <c r="O13" s="148">
+      <c r="O13" s="156">
         <v>6.52</v>
       </c>
-      <c r="P13" s="156">
+      <c r="P13" s="147">
         <v>0.28</v>
       </c>
-      <c r="Q13" s="144">
+      <c r="Q13" s="153">
         <v>1.84</v>
       </c>
-      <c r="R13" s="149">
+      <c r="R13" s="154">
         <v>-1.52</v>
       </c>
-      <c r="S13" s="154">
+      <c r="S13" s="144">
         <v>0.2</v>
       </c>
-      <c r="T13" s="150">
+      <c r="T13" s="148">
         <v>-6.54</v>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       <c r="C14" t="str">
         <v>871981</v>
       </c>
-      <c r="D14" s="162" t="str">
+      <c r="D14" s="159" t="str">
         <v>净卖: -825.29万</v>
       </c>
       <c r="E14">
@@ -8193,40 +8193,40 @@
       <c r="H14">
         <v>7.39</v>
       </c>
-      <c r="I14" s="159">
+      <c r="I14" s="160">
         <v>-6.58</v>
       </c>
-      <c r="J14" s="163">
+      <c r="J14" s="162">
         <v>-10</v>
       </c>
-      <c r="K14" s="164">
+      <c r="K14" s="165">
         <v>-9.2</v>
       </c>
-      <c r="L14" s="167">
+      <c r="L14" s="166">
         <v>-7.22</v>
       </c>
-      <c r="M14" s="168">
+      <c r="M14" s="157">
         <v>-11.52</v>
       </c>
-      <c r="N14" s="165">
+      <c r="N14" s="167">
         <v>-15.64</v>
       </c>
-      <c r="O14" s="169">
+      <c r="O14" s="168">
         <v>-20.58</v>
       </c>
-      <c r="P14" s="160">
+      <c r="P14" s="169">
         <v>-19.34</v>
       </c>
-      <c r="Q14" s="157">
+      <c r="Q14" s="158">
         <v>-22</v>
       </c>
-      <c r="R14" s="166">
+      <c r="R14" s="161">
         <v>-20.64</v>
       </c>
-      <c r="S14" s="158">
+      <c r="S14" s="163">
         <v>-21.32</v>
       </c>
-      <c r="T14" s="161">
+      <c r="T14" s="164">
         <v>-25.98</v>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       <c r="C15" t="str">
         <v>301389</v>
       </c>
-      <c r="D15" s="182" t="str">
+      <c r="D15" s="177" t="str">
         <v>净买: 4127.06万</v>
       </c>
       <c r="E15">
@@ -8255,37 +8255,37 @@
       <c r="H15">
         <v>0.95</v>
       </c>
-      <c r="I15" s="170">
+      <c r="I15" s="178">
         <v>18.87</v>
       </c>
-      <c r="J15" s="177">
+      <c r="J15" s="179">
         <v>42.65</v>
       </c>
-      <c r="K15" s="178">
+      <c r="K15" s="170">
         <v>49.96</v>
       </c>
-      <c r="L15" s="171">
+      <c r="L15" s="172">
         <v>46.52</v>
       </c>
       <c r="M15" s="174">
         <v>28.73</v>
       </c>
-      <c r="N15" s="179">
+      <c r="N15" s="175">
         <v>24.55</v>
       </c>
-      <c r="O15" s="175">
+      <c r="O15" s="171">
         <v>17.98</v>
       </c>
-      <c r="P15" s="172">
+      <c r="P15" s="180">
         <v>30.5</v>
       </c>
-      <c r="Q15" s="176">
+      <c r="Q15" s="181">
         <v>23.88</v>
       </c>
-      <c r="R15" s="180">
+      <c r="R15" s="176">
         <v>19.89</v>
       </c>
-      <c r="S15" s="181">
+      <c r="S15" s="182">
         <v>21.91</v>
       </c>
       <c r="T15" s="173">
@@ -8302,7 +8302,7 @@
       <c r="C16" t="str">
         <v>301389</v>
       </c>
-      <c r="D16" s="188" t="str">
+      <c r="D16" s="190" t="str">
         <v>净买: 932.40万</v>
       </c>
       <c r="E16">
@@ -8317,40 +8317,40 @@
       <c r="H16">
         <v>-5.75</v>
       </c>
-      <c r="I16" s="189">
+      <c r="I16" s="191">
         <v>27.33</v>
       </c>
-      <c r="J16" s="185">
+      <c r="J16" s="195">
         <v>33.86</v>
       </c>
-      <c r="K16" s="190">
+      <c r="K16" s="183">
         <v>30.79</v>
       </c>
-      <c r="L16" s="194">
+      <c r="L16" s="192">
         <v>14.91</v>
       </c>
-      <c r="M16" s="191">
+      <c r="M16" s="193">
         <v>11.18</v>
       </c>
-      <c r="N16" s="192">
+      <c r="N16" s="185">
         <v>5.32</v>
       </c>
-      <c r="O16" s="193">
+      <c r="O16" s="186">
         <v>16.49</v>
       </c>
-      <c r="P16" s="186">
+      <c r="P16" s="187">
         <v>10.58</v>
       </c>
-      <c r="Q16" s="195">
+      <c r="Q16" s="188">
         <v>7.02</v>
       </c>
-      <c r="R16" s="183">
+      <c r="R16" s="194">
         <v>8.82</v>
       </c>
-      <c r="S16" s="184">
+      <c r="S16" s="189">
         <v>15.05</v>
       </c>
-      <c r="T16" s="187">
+      <c r="T16" s="184">
         <v>1.75</v>
       </c>
     </row>
@@ -8379,40 +8379,40 @@
       <c r="H17">
         <v>5.71</v>
       </c>
-      <c r="I17" s="203">
+      <c r="I17" s="199">
         <v>13.52</v>
       </c>
       <c r="J17" s="208">
         <v>30.12</v>
       </c>
-      <c r="K17" s="204">
+      <c r="K17" s="198">
         <v>40.03</v>
       </c>
-      <c r="L17" s="196">
+      <c r="L17" s="204">
         <v>40.54</v>
       </c>
-      <c r="M17" s="199">
+      <c r="M17" s="200">
         <v>43.32</v>
       </c>
-      <c r="N17" s="197">
+      <c r="N17" s="201">
         <v>71.99</v>
       </c>
-      <c r="O17" s="198">
+      <c r="O17" s="202">
         <v>83.47</v>
       </c>
-      <c r="P17" s="200">
+      <c r="P17" s="196">
         <v>79.22</v>
       </c>
-      <c r="Q17" s="201">
+      <c r="Q17" s="203">
         <v>87.37</v>
       </c>
-      <c r="R17" s="202">
+      <c r="R17" s="205">
         <v>92.23</v>
       </c>
-      <c r="S17" s="205">
+      <c r="S17" s="206">
         <v>75.19</v>
       </c>
-      <c r="T17" s="206">
+      <c r="T17" s="197">
         <v>79.03</v>
       </c>
     </row>
@@ -8426,7 +8426,7 @@
       <c r="C18" t="str">
         <v>301389</v>
       </c>
-      <c r="D18" s="217" t="str">
+      <c r="D18" s="210" t="str">
         <v>净卖: -3733.12万</v>
       </c>
       <c r="E18">
@@ -8441,37 +8441,37 @@
       <c r="H18">
         <v>2.9</v>
       </c>
-      <c r="I18" s="218">
+      <c r="I18" s="217">
         <v>-5.04</v>
       </c>
-      <c r="J18" s="213">
+      <c r="J18" s="211">
         <v>-16.57</v>
       </c>
-      <c r="K18" s="209">
+      <c r="K18" s="218">
         <v>-19.28</v>
       </c>
-      <c r="L18" s="210">
+      <c r="L18" s="219">
         <v>-23.54</v>
       </c>
-      <c r="M18" s="214">
+      <c r="M18" s="212">
         <v>-15.42</v>
       </c>
-      <c r="N18" s="211">
+      <c r="N18" s="213">
         <v>-19.72</v>
       </c>
-      <c r="O18" s="219">
+      <c r="O18" s="214">
         <v>-22.3</v>
       </c>
       <c r="P18" s="220">
         <v>-20.99</v>
       </c>
-      <c r="Q18" s="221">
+      <c r="Q18" s="209">
         <v>-16.47</v>
       </c>
       <c r="R18" s="215">
         <v>-13.65</v>
       </c>
-      <c r="S18" s="212">
+      <c r="S18" s="221">
         <v>-15.93</v>
       </c>
       <c r="T18" s="216">
@@ -8488,7 +8488,7 @@
       <c r="C19" t="str">
         <v>833580</v>
       </c>
-      <c r="D19" s="229" t="str">
+      <c r="D19" s="228" t="str">
         <v>净买: 656.67万</v>
       </c>
       <c r="E19">
@@ -8503,19 +8503,19 @@
       <c r="H19">
         <v>-1.6</v>
       </c>
-      <c r="I19" s="223">
+      <c r="I19" s="229">
         <v>32.07</v>
       </c>
-      <c r="J19" s="226">
+      <c r="J19" s="230">
         <v>19.86</v>
       </c>
-      <c r="K19" s="230">
+      <c r="K19" s="222">
         <v>10.83</v>
       </c>
       <c r="L19" s="231">
         <v>7.1</v>
       </c>
-      <c r="M19" s="232">
+      <c r="M19" s="223">
         <v>12.21</v>
       </c>
       <c r="N19" s="233">
@@ -8524,19 +8524,19 @@
       <c r="O19" s="224">
         <v>16.13</v>
       </c>
-      <c r="P19" s="234">
+      <c r="P19" s="232">
         <v>10.95</v>
       </c>
       <c r="Q19" s="225">
         <v>8.72</v>
       </c>
-      <c r="R19" s="222">
+      <c r="R19" s="226">
         <v>8.78</v>
       </c>
       <c r="S19" s="227">
         <v>9.81</v>
       </c>
-      <c r="T19" s="228">
+      <c r="T19" s="234">
         <v>-2.53</v>
       </c>
     </row>
@@ -8550,7 +8550,7 @@
       <c r="C20" t="str">
         <v>833580</v>
       </c>
-      <c r="D20" s="246" t="str">
+      <c r="D20" s="245" t="str">
         <v>净卖: -782.72万</v>
       </c>
       <c r="E20">
@@ -8565,40 +8565,40 @@
       <c r="H20">
         <v>8.88</v>
       </c>
-      <c r="I20" s="247">
+      <c r="I20" s="246">
         <v>-16.65</v>
       </c>
-      <c r="J20" s="235">
+      <c r="J20" s="243">
         <v>-22.93</v>
       </c>
       <c r="K20" s="241">
         <v>-25.52</v>
       </c>
-      <c r="L20" s="238">
+      <c r="L20" s="247">
         <v>-21.97</v>
       </c>
-      <c r="M20" s="239">
+      <c r="M20" s="235">
         <v>-17.2</v>
       </c>
-      <c r="N20" s="236">
+      <c r="N20" s="239">
         <v>-19.25</v>
       </c>
-      <c r="O20" s="244">
+      <c r="O20" s="236">
         <v>-22.85</v>
       </c>
-      <c r="P20" s="242">
+      <c r="P20" s="237">
         <v>-24.39</v>
       </c>
-      <c r="Q20" s="245">
+      <c r="Q20" s="240">
         <v>-24.35</v>
       </c>
-      <c r="R20" s="243">
+      <c r="R20" s="244">
         <v>-23.64</v>
       </c>
-      <c r="S20" s="240">
+      <c r="S20" s="242">
         <v>-28.45</v>
       </c>
-      <c r="T20" s="237">
+      <c r="T20" s="238">
         <v>-32.22</v>
       </c>
     </row>
@@ -8612,7 +8612,7 @@
       <c r="C21" t="str">
         <v>601068</v>
       </c>
-      <c r="D21" s="255" t="str">
+      <c r="D21" s="254" t="str">
         <v>净买: 656.95万</v>
       </c>
       <c r="E21">
@@ -8627,40 +8627,40 @@
       <c r="H21">
         <v>0</v>
       </c>
-      <c r="I21" s="248">
+      <c r="I21" s="255">
         <v>10.02</v>
       </c>
-      <c r="J21" s="256">
+      <c r="J21" s="258">
         <v>5.75</v>
       </c>
-      <c r="K21" s="249">
+      <c r="K21" s="256">
         <v>0.37</v>
       </c>
-      <c r="L21" s="257">
+      <c r="L21" s="250">
         <v>0</v>
       </c>
-      <c r="M21" s="258">
+      <c r="M21" s="257">
         <v>-1.86</v>
       </c>
-      <c r="N21" s="250">
+      <c r="N21" s="251">
         <v>0.19</v>
       </c>
-      <c r="O21" s="251">
+      <c r="O21" s="259">
         <v>0.37</v>
       </c>
-      <c r="P21" s="252">
+      <c r="P21" s="260">
         <v>-1.86</v>
       </c>
-      <c r="Q21" s="253">
+      <c r="Q21" s="248">
         <v>-1.11</v>
       </c>
-      <c r="R21" s="254">
+      <c r="R21" s="252">
         <v>-1.86</v>
       </c>
-      <c r="S21" s="259">
+      <c r="S21" s="253">
         <v>-0.74</v>
       </c>
-      <c r="T21" s="260">
+      <c r="T21" s="249">
         <v>16.51</v>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       <c r="C22" t="str">
         <v>688146</v>
       </c>
-      <c r="D22" s="269" t="str">
+      <c r="D22" s="270" t="str">
         <v>净买: 1029.87万</v>
       </c>
       <c r="E22">
@@ -8689,40 +8689,40 @@
       <c r="H22">
         <v>-0.49</v>
       </c>
-      <c r="I22" s="261">
+      <c r="I22" s="271">
         <v>16.28</v>
       </c>
-      <c r="J22" s="270">
+      <c r="J22" s="272">
         <v>21.96</v>
       </c>
-      <c r="K22" s="271">
+      <c r="K22" s="263">
         <v>26.12</v>
       </c>
-      <c r="L22" s="264">
+      <c r="L22" s="273">
         <v>18.55</v>
       </c>
-      <c r="M22" s="265">
+      <c r="M22" s="264">
         <v>21.14</v>
       </c>
-      <c r="N22" s="262">
+      <c r="N22" s="265">
         <v>18.6</v>
       </c>
       <c r="O22" s="267">
         <v>17.6</v>
       </c>
-      <c r="P22" s="263">
+      <c r="P22" s="261">
         <v>15.63</v>
       </c>
-      <c r="Q22" s="266">
+      <c r="Q22" s="268">
         <v>18.84</v>
       </c>
-      <c r="R22" s="272">
+      <c r="R22" s="262">
         <v>17.44</v>
       </c>
-      <c r="S22" s="273">
+      <c r="S22" s="269">
         <v>15.25</v>
       </c>
-      <c r="T22" s="268">
+      <c r="T22" s="266">
         <v>66.18</v>
       </c>
     </row>
@@ -8751,40 +8751,40 @@
       <c r="H23">
         <v>-7.51</v>
       </c>
-      <c r="I23" s="282">
+      <c r="I23" s="275">
         <v>-2.71</v>
       </c>
-      <c r="J23" s="283">
+      <c r="J23" s="279">
         <v>-7.69</v>
       </c>
-      <c r="K23" s="286">
+      <c r="K23" s="276">
         <v>-3.85</v>
       </c>
-      <c r="L23" s="281">
+      <c r="L23" s="277">
         <v>-4.99</v>
       </c>
-      <c r="M23" s="274">
+      <c r="M23" s="281">
         <v>-9.33</v>
       </c>
-      <c r="N23" s="275">
+      <c r="N23" s="282">
         <v>-8.05</v>
       </c>
-      <c r="O23" s="284">
+      <c r="O23" s="283">
         <v>-3.7</v>
       </c>
-      <c r="P23" s="277">
+      <c r="P23" s="284">
         <v>-5.98</v>
       </c>
-      <c r="Q23" s="278">
+      <c r="Q23" s="285">
         <v>-8.9</v>
       </c>
-      <c r="R23" s="279">
+      <c r="R23" s="278">
         <v>-4.49</v>
       </c>
-      <c r="S23" s="276">
+      <c r="S23" s="286">
         <v>-2.49</v>
       </c>
-      <c r="T23" s="285">
+      <c r="T23" s="274">
         <v>-25.43</v>
       </c>
     </row>
@@ -8798,7 +8798,7 @@
       <c r="C24" t="str">
         <v>301449</v>
       </c>
-      <c r="D24" s="294" t="str">
+      <c r="D24" s="290" t="str">
         <v>净卖: -1931.35万</v>
       </c>
       <c r="E24">
@@ -8813,40 +8813,40 @@
       <c r="H24">
         <v>-7.39</v>
       </c>
-      <c r="I24" s="299">
+      <c r="I24" s="297">
         <v>-10.16</v>
       </c>
-      <c r="J24" s="288">
+      <c r="J24" s="298">
         <v>-12.52</v>
       </c>
-      <c r="K24" s="289">
+      <c r="K24" s="294">
         <v>-14.52</v>
       </c>
-      <c r="L24" s="290">
+      <c r="L24" s="291">
         <v>-15.32</v>
       </c>
-      <c r="M24" s="295">
+      <c r="M24" s="299">
         <v>-9.86</v>
       </c>
       <c r="N24" s="292">
         <v>-11.91</v>
       </c>
-      <c r="O24" s="296">
+      <c r="O24" s="293">
         <v>-12.71</v>
       </c>
-      <c r="P24" s="291">
+      <c r="P24" s="287">
         <v>-12.71</v>
       </c>
-      <c r="Q24" s="287">
+      <c r="Q24" s="288">
         <v>-16.26</v>
       </c>
-      <c r="R24" s="297">
+      <c r="R24" s="289">
         <v>-10.13</v>
       </c>
-      <c r="S24" s="298">
+      <c r="S24" s="295">
         <v>-12.25</v>
       </c>
-      <c r="T24" s="293">
+      <c r="T24" s="296">
         <v>-17.11</v>
       </c>
     </row>
@@ -8860,7 +8860,7 @@
       <c r="C25" t="str">
         <v>688137</v>
       </c>
-      <c r="D25" s="303" t="str">
+      <c r="D25" s="304" t="str">
         <v>净买: 809.16万</v>
       </c>
       <c r="E25">
@@ -8875,40 +8875,40 @@
       <c r="H25">
         <v>-0.09</v>
       </c>
-      <c r="I25" s="304">
+      <c r="I25" s="311">
         <v>15.54</v>
       </c>
       <c r="J25" s="305">
         <v>13.21</v>
       </c>
-      <c r="K25" s="306">
+      <c r="K25" s="308">
         <v>11.95</v>
       </c>
-      <c r="L25" s="307">
+      <c r="L25" s="309">
         <v>9.95</v>
       </c>
-      <c r="M25" s="311">
+      <c r="M25" s="300">
         <v>6.85</v>
       </c>
-      <c r="N25" s="308">
+      <c r="N25" s="301">
         <v>6.78</v>
       </c>
-      <c r="O25" s="301">
+      <c r="O25" s="312">
         <v>13.58</v>
       </c>
-      <c r="P25" s="312">
+      <c r="P25" s="306">
         <v>14.61</v>
       </c>
-      <c r="Q25" s="309">
+      <c r="Q25" s="302">
         <v>16.47</v>
       </c>
-      <c r="R25" s="300">
+      <c r="R25" s="303">
         <v>23.92</v>
       </c>
-      <c r="S25" s="302">
+      <c r="S25" s="310">
         <v>15.3</v>
       </c>
-      <c r="T25" s="310">
+      <c r="T25" s="307">
         <v>16.63</v>
       </c>
     </row>
@@ -8922,7 +8922,7 @@
       <c r="C26" t="str">
         <v>301408</v>
       </c>
-      <c r="D26" s="318" t="str">
+      <c r="D26" s="313" t="str">
         <v>净卖: -2207.20万</v>
       </c>
       <c r="E26">
@@ -8937,37 +8937,37 @@
       <c r="H26">
         <v>1.45</v>
       </c>
-      <c r="I26" s="322">
+      <c r="I26" s="319">
         <v>18.28</v>
       </c>
-      <c r="J26" s="323">
+      <c r="J26" s="314">
         <v>-5.37</v>
       </c>
-      <c r="K26" s="324">
+      <c r="K26" s="315">
         <v>-14.43</v>
       </c>
-      <c r="L26" s="325">
+      <c r="L26" s="324">
         <v>-13.43</v>
       </c>
-      <c r="M26" s="313">
+      <c r="M26" s="316">
         <v>-12.24</v>
       </c>
-      <c r="N26" s="319">
+      <c r="N26" s="317">
         <v>-13.31</v>
       </c>
-      <c r="O26" s="315">
+      <c r="O26" s="322">
         <v>-7.91</v>
       </c>
-      <c r="P26" s="316">
+      <c r="P26" s="320">
         <v>-4.69</v>
       </c>
-      <c r="Q26" s="314">
+      <c r="Q26" s="318">
         <v>-0.32</v>
       </c>
-      <c r="R26" s="317">
+      <c r="R26" s="323">
         <v>-8.55</v>
       </c>
-      <c r="S26" s="320">
+      <c r="S26" s="325">
         <v>-11.88</v>
       </c>
       <c r="T26" s="321">
@@ -8984,7 +8984,7 @@
       <c r="C27" t="str">
         <v>603598</v>
       </c>
-      <c r="D27" s="337" t="str">
+      <c r="D27" s="331" t="str">
         <v>净卖: -958.53万</v>
       </c>
       <c r="E27">
@@ -8999,40 +8999,40 @@
       <c r="H27">
         <v>-10.01</v>
       </c>
-      <c r="I27" s="328">
+      <c r="I27" s="334">
         <v>0</v>
       </c>
-      <c r="J27" s="330">
+      <c r="J27" s="335">
         <v>-5.64</v>
       </c>
-      <c r="K27" s="331">
+      <c r="K27" s="336">
         <v>-1.1</v>
       </c>
-      <c r="L27" s="332">
+      <c r="L27" s="338">
         <v>1.88</v>
       </c>
-      <c r="M27" s="334">
+      <c r="M27" s="326">
         <v>4.9</v>
       </c>
-      <c r="N27" s="335">
+      <c r="N27" s="327">
         <v>3.33</v>
       </c>
-      <c r="O27" s="338">
+      <c r="O27" s="332">
         <v>1.33</v>
       </c>
-      <c r="P27" s="336">
+      <c r="P27" s="333">
         <v>-0.86</v>
       </c>
-      <c r="Q27" s="329">
+      <c r="Q27" s="328">
         <v>4.62</v>
       </c>
-      <c r="R27" s="326">
+      <c r="R27" s="329">
         <v>15.09</v>
       </c>
-      <c r="S27" s="333">
+      <c r="S27" s="330">
         <v>13.64</v>
       </c>
-      <c r="T27" s="327">
+      <c r="T27" s="337">
         <v>-16.81</v>
       </c>
     </row>
@@ -9046,7 +9046,7 @@
       <c r="C28" t="str">
         <v>920368</v>
       </c>
-      <c r="D28" s="344" t="str">
+      <c r="D28" s="345" t="str">
         <v>净买: 2785.37万</v>
       </c>
       <c r="E28">
@@ -9061,40 +9061,40 @@
       <c r="H28">
         <v>6.62</v>
       </c>
-      <c r="I28" s="340">
+      <c r="I28" s="342">
         <v>21.92</v>
       </c>
-      <c r="J28" s="341">
+      <c r="J28" s="346">
         <v>30.07</v>
       </c>
-      <c r="K28" s="345">
+      <c r="K28" s="351">
         <v>52.53</v>
       </c>
-      <c r="L28" s="342">
+      <c r="L28" s="347">
         <v>59.26</v>
       </c>
-      <c r="M28" s="350">
+      <c r="M28" s="348">
         <v>51.53</v>
       </c>
-      <c r="N28" s="351">
+      <c r="N28" s="343">
         <v>48.42</v>
       </c>
-      <c r="O28" s="339">
+      <c r="O28" s="349">
         <v>50.72</v>
       </c>
-      <c r="P28" s="346">
+      <c r="P28" s="339">
         <v>78.13</v>
       </c>
-      <c r="Q28" s="343">
+      <c r="Q28" s="340">
         <v>61.84</v>
       </c>
-      <c r="R28" s="347">
+      <c r="R28" s="350">
         <v>41.93</v>
       </c>
-      <c r="S28" s="348">
+      <c r="S28" s="344">
         <v>52.17</v>
       </c>
-      <c r="T28" s="349">
+      <c r="T28" s="341">
         <v>-2.53</v>
       </c>
     </row>
@@ -9108,7 +9108,7 @@
       <c r="C29" t="str">
         <v>300017</v>
       </c>
-      <c r="D29" s="360" t="str">
+      <c r="D29" s="355" t="str">
         <v>净卖: -8231.84万</v>
       </c>
       <c r="E29">
@@ -9123,40 +9123,40 @@
       <c r="H29">
         <v>1.57</v>
       </c>
-      <c r="I29" s="361">
+      <c r="I29" s="356">
         <v>18.18</v>
       </c>
-      <c r="J29" s="362">
+      <c r="J29" s="361">
         <v>16.12</v>
       </c>
       <c r="K29" s="357">
         <v>33.7</v>
       </c>
-      <c r="L29" s="363">
+      <c r="L29" s="362">
         <v>44.08</v>
       </c>
-      <c r="M29" s="364">
+      <c r="M29" s="358">
         <v>42.02</v>
       </c>
-      <c r="N29" s="352">
+      <c r="N29" s="360">
         <v>44.77</v>
       </c>
-      <c r="O29" s="355">
+      <c r="O29" s="352">
         <v>65.61</v>
       </c>
-      <c r="P29" s="353">
+      <c r="P29" s="359">
         <v>43.4</v>
       </c>
-      <c r="Q29" s="354">
+      <c r="Q29" s="363">
         <v>54.12</v>
       </c>
-      <c r="R29" s="356">
+      <c r="R29" s="364">
         <v>53.77</v>
       </c>
-      <c r="S29" s="358">
+      <c r="S29" s="353">
         <v>62.09</v>
       </c>
-      <c r="T29" s="359">
+      <c r="T29" s="354">
         <v>62.09</v>
       </c>
     </row>
@@ -9170,7 +9170,7 @@
       <c r="C30" t="str">
         <v>603075</v>
       </c>
-      <c r="D30" s="368" t="str">
+      <c r="D30" s="367" t="str">
         <v>净卖: -1295.61万</v>
       </c>
       <c r="E30">
@@ -9188,37 +9188,37 @@
       <c r="I30" s="372">
         <v>1.83</v>
       </c>
-      <c r="J30" s="373">
+      <c r="J30" s="376">
         <v>-4.09</v>
       </c>
-      <c r="K30" s="374">
+      <c r="K30" s="377">
         <v>-6.43</v>
       </c>
-      <c r="L30" s="375">
+      <c r="L30" s="368">
         <v>-7.11</v>
       </c>
-      <c r="M30" s="369">
+      <c r="M30" s="365">
         <v>-5.88</v>
       </c>
-      <c r="N30" s="376">
+      <c r="N30" s="373">
         <v>-7.63</v>
       </c>
-      <c r="O30" s="366">
+      <c r="O30" s="369">
         <v>-5.52</v>
       </c>
-      <c r="P30" s="370">
+      <c r="P30" s="366">
         <v>-4.65</v>
       </c>
-      <c r="Q30" s="367">
+      <c r="Q30" s="374">
         <v>-5.2</v>
       </c>
-      <c r="R30" s="377">
+      <c r="R30" s="370">
         <v>-5.72</v>
       </c>
       <c r="S30" s="371">
         <v>-4.92</v>
       </c>
-      <c r="T30" s="365">
+      <c r="T30" s="375">
         <v>-9.65</v>
       </c>
     </row>
@@ -9250,37 +9250,37 @@
       <c r="I31" s="378">
         <v>-3.25</v>
       </c>
-      <c r="J31" s="389">
+      <c r="J31" s="388">
         <v>13.46</v>
       </c>
-      <c r="K31" s="388">
+      <c r="K31" s="389">
         <v>18.46</v>
       </c>
-      <c r="L31" s="382">
+      <c r="L31" s="379">
         <v>12.71</v>
       </c>
-      <c r="M31" s="383">
+      <c r="M31" s="385">
         <v>10.4</v>
       </c>
-      <c r="N31" s="379">
+      <c r="N31" s="382">
         <v>12.12</v>
       </c>
-      <c r="O31" s="384">
+      <c r="O31" s="390">
         <v>32.5</v>
       </c>
-      <c r="P31" s="390">
+      <c r="P31" s="386">
         <v>20.38</v>
       </c>
-      <c r="Q31" s="385">
+      <c r="Q31" s="383">
         <v>5.58</v>
       </c>
-      <c r="R31" s="386">
+      <c r="R31" s="380">
         <v>13.19</v>
       </c>
       <c r="S31" s="387">
         <v>23.15</v>
       </c>
-      <c r="T31" s="380">
+      <c r="T31" s="384">
         <v>-27.5</v>
       </c>
     </row>
@@ -9294,7 +9294,7 @@
       <c r="C32" t="str">
         <v>600273</v>
       </c>
-      <c r="D32" s="394" t="str">
+      <c r="D32" s="397" t="str">
         <v>净卖: -3657.56万</v>
       </c>
       <c r="E32">
@@ -9309,25 +9309,25 @@
       <c r="H32">
         <v>3.89</v>
       </c>
-      <c r="I32" s="396">
+      <c r="I32" s="398">
         <v>5.92</v>
       </c>
-      <c r="J32" s="397">
+      <c r="J32" s="403">
         <v>2.96</v>
       </c>
-      <c r="K32" s="391">
+      <c r="K32" s="393">
         <v>-4.88</v>
       </c>
-      <c r="L32" s="400">
+      <c r="L32" s="399">
         <v>-3.05</v>
       </c>
-      <c r="M32" s="398">
+      <c r="M32" s="400">
         <v>-1.31</v>
       </c>
-      <c r="N32" s="399">
+      <c r="N32" s="391">
         <v>-4.18</v>
       </c>
-      <c r="O32" s="395">
+      <c r="O32" s="394">
         <v>-1.74</v>
       </c>
       <c r="P32" s="392">
@@ -9336,13 +9336,13 @@
       <c r="Q32" s="401">
         <v>0.78</v>
       </c>
-      <c r="R32" s="402">
+      <c r="R32" s="395">
         <v>1.83</v>
       </c>
-      <c r="S32" s="393">
+      <c r="S32" s="402">
         <v>2.7</v>
       </c>
-      <c r="T32" s="403">
+      <c r="T32" s="396">
         <v>-21.25</v>
       </c>
     </row>
@@ -9356,7 +9356,7 @@
       <c r="C33" t="str">
         <v>300257</v>
       </c>
-      <c r="D33" s="409" t="str">
+      <c r="D33" s="407" t="str">
         <v>净卖: -2507.66万</v>
       </c>
       <c r="E33">
@@ -9371,40 +9371,40 @@
       <c r="H33">
         <v>2.76</v>
       </c>
-      <c r="I33" s="410">
+      <c r="I33" s="408">
         <v>16.77</v>
       </c>
-      <c r="J33" s="405">
+      <c r="J33" s="409">
         <v>17.59</v>
       </c>
-      <c r="K33" s="406">
+      <c r="K33" s="414">
         <v>16.46</v>
       </c>
-      <c r="L33" s="415">
+      <c r="L33" s="404">
         <v>7.35</v>
       </c>
-      <c r="M33" s="416">
+      <c r="M33" s="412">
         <v>14.56</v>
       </c>
-      <c r="N33" s="411">
+      <c r="N33" s="405">
         <v>8.23</v>
       </c>
-      <c r="O33" s="407">
+      <c r="O33" s="415">
         <v>8.64</v>
       </c>
-      <c r="P33" s="412">
+      <c r="P33" s="410">
         <v>8.67</v>
       </c>
-      <c r="Q33" s="413">
+      <c r="Q33" s="416">
         <v>5.17</v>
       </c>
-      <c r="R33" s="404">
+      <c r="R33" s="413">
         <v>1.33</v>
       </c>
-      <c r="S33" s="408">
+      <c r="S33" s="411">
         <v>1.8</v>
       </c>
-      <c r="T33" s="414">
+      <c r="T33" s="406">
         <v>-0.07</v>
       </c>
     </row>
@@ -9467,40 +9467,40 @@
       <c r="F35" t="str"/>
       <c r="G35" t="str"/>
       <c r="H35" t="str"/>
-      <c r="I35" s="424">
+      <c r="I35" s="420">
         <v>68.75</v>
       </c>
-      <c r="J35" s="428">
+      <c r="J35" s="423">
         <v>71.88</v>
       </c>
-      <c r="K35" s="420">
+      <c r="K35" s="424">
         <v>68.75</v>
       </c>
       <c r="L35" s="417">
         <v>68.75</v>
       </c>
-      <c r="M35" s="418">
+      <c r="M35" s="425">
         <v>68.75</v>
       </c>
-      <c r="N35" s="425">
+      <c r="N35" s="421">
         <v>71.88</v>
       </c>
-      <c r="O35" s="419">
+      <c r="O35" s="418">
         <v>71.88</v>
       </c>
-      <c r="P35" s="422">
+      <c r="P35" s="426">
         <v>62.5</v>
       </c>
-      <c r="Q35" s="426">
+      <c r="Q35" s="419">
         <v>65.63</v>
       </c>
-      <c r="R35" s="423">
+      <c r="R35" s="427">
         <v>62.5</v>
       </c>
-      <c r="S35" s="427">
+      <c r="S35" s="422">
         <v>65.63</v>
       </c>
-      <c r="T35" s="421">
+      <c r="T35" s="428">
         <v>34.38</v>
       </c>
     </row>
@@ -9515,40 +9515,40 @@
       <c r="F36" t="str"/>
       <c r="G36" t="str"/>
       <c r="H36" t="str"/>
-      <c r="I36" s="429">
+      <c r="I36" s="433">
         <v>8.56</v>
       </c>
       <c r="J36" s="434">
         <v>10.13</v>
       </c>
-      <c r="K36" s="436">
+      <c r="K36" s="440">
         <v>11.47</v>
       </c>
-      <c r="L36" s="430">
+      <c r="L36" s="429">
         <v>10.84</v>
       </c>
-      <c r="M36" s="431">
+      <c r="M36" s="435">
         <v>11.29</v>
       </c>
       <c r="N36" s="437">
         <v>10.99</v>
       </c>
-      <c r="O36" s="439">
+      <c r="O36" s="438">
         <v>12.53</v>
       </c>
-      <c r="P36" s="432">
+      <c r="P36" s="436">
         <v>11.98</v>
       </c>
-      <c r="Q36" s="438">
+      <c r="Q36" s="430">
         <v>10.83</v>
       </c>
-      <c r="R36" s="433">
+      <c r="R36" s="431">
         <v>10.67</v>
       </c>
-      <c r="S36" s="440">
+      <c r="S36" s="439">
         <v>10.08</v>
       </c>
-      <c r="T36" s="435">
+      <c r="T36" s="432">
         <v>3.14</v>
       </c>
     </row>

--- a/youzi/大小说家/index.xlsx
+++ b/youzi/大小说家/index.xlsx
@@ -39,19 +39,319 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE46370"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7ECA90"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFEA8A93"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1A7330"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9EA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4352"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -63,25 +363,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -93,25 +381,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEAF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46370"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7ECA90"/>
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B25E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -129,2335 +501,2023 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEFF0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBE3C4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB9199"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CDD1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8E1C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91D2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15663"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDE4C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF3F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91D2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBD5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8336"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD75"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3DAF57"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF59BB6F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7833"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF35AC50"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4453"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3948"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAEFDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBD6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF37AD52"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB766"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF73C586"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4BB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD23040"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF7BC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8790"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB4E0BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7E1C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2DA949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9EA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4352"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B25E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEFF0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBE3C4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8E1C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB9199"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CDD1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91D2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15663"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF3F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDE4C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91D2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFEBD5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEB9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEB9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEB9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF59BB6F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3DAF57"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8336"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD75"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7833"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF35AC50"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3948"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4453"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAEFDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFEBD6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF37AD52"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB766"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF73C586"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4BB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2DA949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB4E0BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7BC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8790"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2469,67 +2529,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2547,6 +2553,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFBE2735"/>
         <bgColor/>
       </patternFill>
@@ -2565,43 +2589,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFBE2735"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFCE2F3E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2626,54 +2674,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -7449,40 +7449,40 @@
       <c r="H2">
         <v>-2.13</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="5">
         <v>-8.04</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="10">
         <v>-7</v>
       </c>
-      <c r="K2" s="10">
+      <c r="K2" s="11">
         <v>-0.47</v>
       </c>
-      <c r="L2" s="7">
+      <c r="L2" s="12">
         <v>3.68</v>
       </c>
-      <c r="M2" s="11">
+      <c r="M2" s="6">
         <v>10.89</v>
       </c>
-      <c r="N2" s="12">
+      <c r="N2" s="1">
         <v>3.84</v>
       </c>
-      <c r="O2" s="6">
+      <c r="O2" s="2">
         <v>6.4</v>
       </c>
-      <c r="P2" s="8">
+      <c r="P2" s="13">
         <v>7.52</v>
       </c>
-      <c r="Q2" s="13">
+      <c r="Q2" s="3">
         <v>-2.98</v>
       </c>
-      <c r="R2" s="1">
+      <c r="R2" s="4">
         <v>2.88</v>
       </c>
-      <c r="S2" s="4">
+      <c r="S2" s="7">
         <v>6.19</v>
       </c>
-      <c r="T2" s="2">
+      <c r="T2" s="8">
         <v>-9.36</v>
       </c>
     </row>
@@ -7496,7 +7496,7 @@
       <c r="C3" t="str">
         <v>002923</v>
       </c>
-      <c r="D3" s="20" t="str">
+      <c r="D3" s="17" t="str">
         <v>净卖: -1342.21万</v>
       </c>
       <c r="E3">
@@ -7511,40 +7511,40 @@
       <c r="H3">
         <v>2.17</v>
       </c>
-      <c r="I3" s="25">
+      <c r="I3" s="20">
         <v>7.69</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="21">
         <v>17.63</v>
       </c>
-      <c r="K3" s="18">
+      <c r="K3" s="26">
         <v>5.88</v>
       </c>
-      <c r="L3" s="21">
+      <c r="L3" s="22">
         <v>-4.3</v>
       </c>
-      <c r="M3" s="15">
+      <c r="M3" s="23">
         <v>-13.87</v>
       </c>
-      <c r="N3" s="19">
+      <c r="N3" s="18">
         <v>-11.45</v>
       </c>
-      <c r="O3" s="16">
+      <c r="O3" s="24">
         <v>-15.08</v>
       </c>
-      <c r="P3" s="26">
+      <c r="P3" s="19">
         <v>-14.66</v>
       </c>
-      <c r="Q3" s="22">
+      <c r="Q3" s="16">
         <v>-12.84</v>
       </c>
-      <c r="R3" s="23">
+      <c r="R3" s="14">
         <v>-21.56</v>
       </c>
-      <c r="S3" s="17">
+      <c r="S3" s="15">
         <v>-24.59</v>
       </c>
-      <c r="T3" s="24">
+      <c r="T3" s="25">
         <v>-23.92</v>
       </c>
     </row>
@@ -7558,7 +7558,7 @@
       <c r="C4" t="str">
         <v>002564</v>
       </c>
-      <c r="D4" s="29" t="str">
+      <c r="D4" s="37" t="str">
         <v>净买: 1737.48万</v>
       </c>
       <c r="E4">
@@ -7573,40 +7573,40 @@
       <c r="H4">
         <v>-1.38</v>
       </c>
-      <c r="I4" s="35">
+      <c r="I4" s="38">
         <v>11.55</v>
       </c>
-      <c r="J4" s="36">
+      <c r="J4" s="28">
         <v>2.39</v>
       </c>
-      <c r="K4" s="37">
+      <c r="K4" s="33">
         <v>12.55</v>
       </c>
-      <c r="L4" s="38">
+      <c r="L4" s="34">
         <v>5.58</v>
       </c>
       <c r="M4" s="39">
         <v>16.14</v>
       </c>
-      <c r="N4" s="27">
+      <c r="N4" s="30">
         <v>21.51</v>
       </c>
-      <c r="O4" s="32">
+      <c r="O4" s="31">
         <v>16.14</v>
       </c>
-      <c r="P4" s="28">
+      <c r="P4" s="27">
         <v>19.92</v>
       </c>
-      <c r="Q4" s="30">
+      <c r="Q4" s="35">
         <v>20.72</v>
       </c>
-      <c r="R4" s="31">
+      <c r="R4" s="36">
         <v>15.94</v>
       </c>
-      <c r="S4" s="33">
+      <c r="S4" s="32">
         <v>8.96</v>
       </c>
-      <c r="T4" s="34">
+      <c r="T4" s="29">
         <v>27.09</v>
       </c>
     </row>
@@ -7620,7 +7620,7 @@
       <c r="C5" t="str">
         <v>600735</v>
       </c>
-      <c r="D5" s="43" t="str">
+      <c r="D5" s="52" t="str">
         <v>净买: 1155.67万</v>
       </c>
       <c r="E5">
@@ -7635,40 +7635,40 @@
       <c r="H5">
         <v>1.24</v>
       </c>
-      <c r="I5" s="52">
+      <c r="I5" s="40">
         <v>8.71</v>
       </c>
-      <c r="J5" s="49">
+      <c r="J5" s="41">
         <v>8.84</v>
       </c>
-      <c r="K5" s="40">
+      <c r="K5" s="45">
         <v>7.48</v>
       </c>
-      <c r="L5" s="47">
+      <c r="L5" s="48">
         <v>4.63</v>
       </c>
-      <c r="M5" s="44">
+      <c r="M5" s="42">
         <v>5.71</v>
       </c>
-      <c r="N5" s="41">
+      <c r="N5" s="51">
         <v>11.16</v>
       </c>
-      <c r="O5" s="42">
+      <c r="O5" s="43">
         <v>9.66</v>
       </c>
-      <c r="P5" s="45">
+      <c r="P5" s="46">
         <v>6.8</v>
       </c>
-      <c r="Q5" s="50">
+      <c r="Q5" s="44">
         <v>12.24</v>
       </c>
-      <c r="R5" s="48">
+      <c r="R5" s="49">
         <v>13.88</v>
       </c>
-      <c r="S5" s="46">
+      <c r="S5" s="50">
         <v>10.07</v>
       </c>
-      <c r="T5" s="51">
+      <c r="T5" s="47">
         <v>-8.44</v>
       </c>
     </row>
@@ -7682,7 +7682,7 @@
       <c r="C6" t="str">
         <v>600735</v>
       </c>
-      <c r="D6" s="60" t="str">
+      <c r="D6" s="57" t="str">
         <v>净卖: -1139.95万</v>
       </c>
       <c r="E6">
@@ -7697,37 +7697,37 @@
       <c r="H6">
         <v>-5.01</v>
       </c>
-      <c r="I6" s="57">
+      <c r="I6" s="62">
         <v>5.4</v>
       </c>
-      <c r="J6" s="61">
+      <c r="J6" s="53">
         <v>4.08</v>
       </c>
-      <c r="K6" s="58">
+      <c r="K6" s="63">
         <v>1.32</v>
       </c>
-      <c r="L6" s="62">
+      <c r="L6" s="64">
         <v>2.37</v>
       </c>
-      <c r="M6" s="64">
+      <c r="M6" s="65">
         <v>7.64</v>
       </c>
-      <c r="N6" s="65">
+      <c r="N6" s="54">
         <v>6.19</v>
       </c>
-      <c r="O6" s="63">
+      <c r="O6" s="58">
         <v>3.43</v>
       </c>
       <c r="P6" s="59">
         <v>8.7</v>
       </c>
-      <c r="Q6" s="54">
+      <c r="Q6" s="55">
         <v>10.28</v>
       </c>
-      <c r="R6" s="55">
+      <c r="R6" s="60">
         <v>6.59</v>
       </c>
-      <c r="S6" s="53">
+      <c r="S6" s="61">
         <v>3.43</v>
       </c>
       <c r="T6" s="56">
@@ -7744,7 +7744,7 @@
       <c r="C7" t="str">
         <v>002365</v>
       </c>
-      <c r="D7" s="66" t="str">
+      <c r="D7" s="71" t="str">
         <v>净卖: -2887.03万</v>
       </c>
       <c r="E7">
@@ -7762,37 +7762,37 @@
       <c r="I7" s="67">
         <v>-4.32</v>
       </c>
-      <c r="J7" s="74">
+      <c r="J7" s="68">
         <v>5.25</v>
       </c>
-      <c r="K7" s="71">
+      <c r="K7" s="69">
         <v>15.76</v>
       </c>
-      <c r="L7" s="78">
+      <c r="L7" s="76">
         <v>27.33</v>
       </c>
-      <c r="M7" s="75">
+      <c r="M7" s="78">
         <v>35.58</v>
       </c>
-      <c r="N7" s="68">
+      <c r="N7" s="72">
         <v>40.03</v>
       </c>
-      <c r="O7" s="69">
+      <c r="O7" s="66">
         <v>54.03</v>
       </c>
-      <c r="P7" s="76">
+      <c r="P7" s="73">
         <v>38.65</v>
       </c>
-      <c r="Q7" s="72">
+      <c r="Q7" s="74">
         <v>24.77</v>
       </c>
-      <c r="R7" s="77">
+      <c r="R7" s="75">
         <v>28.27</v>
       </c>
       <c r="S7" s="70">
         <v>22.51</v>
       </c>
-      <c r="T7" s="73">
+      <c r="T7" s="77">
         <v>-14.7</v>
       </c>
     </row>
@@ -7806,7 +7806,7 @@
       <c r="C8" t="str">
         <v>603585</v>
       </c>
-      <c r="D8" s="79" t="str">
+      <c r="D8" s="89" t="str">
         <v>净买: 590.46万</v>
       </c>
       <c r="E8">
@@ -7824,37 +7824,37 @@
       <c r="I8" s="86">
         <v>8.09</v>
       </c>
-      <c r="J8" s="80">
+      <c r="J8" s="90">
         <v>7.12</v>
       </c>
-      <c r="K8" s="89">
+      <c r="K8" s="87">
         <v>17.86</v>
       </c>
-      <c r="L8" s="81">
+      <c r="L8" s="91">
         <v>29.63</v>
       </c>
-      <c r="M8" s="90">
+      <c r="M8" s="83">
         <v>16.68</v>
       </c>
-      <c r="N8" s="82">
+      <c r="N8" s="79">
         <v>5.02</v>
       </c>
-      <c r="O8" s="83">
+      <c r="O8" s="81">
         <v>0.38</v>
       </c>
-      <c r="P8" s="87">
+      <c r="P8" s="88">
         <v>2.75</v>
       </c>
       <c r="Q8" s="84">
         <v>2.05</v>
       </c>
-      <c r="R8" s="85">
+      <c r="R8" s="80">
         <v>-0.32</v>
       </c>
-      <c r="S8" s="91">
+      <c r="S8" s="85">
         <v>-1.57</v>
       </c>
-      <c r="T8" s="88">
+      <c r="T8" s="82">
         <v>29.84</v>
       </c>
     </row>
@@ -7868,7 +7868,7 @@
       <c r="C9" t="str">
         <v>003029</v>
       </c>
-      <c r="D9" s="103" t="str">
+      <c r="D9" s="102" t="str">
         <v>净卖: -1441.18万</v>
       </c>
       <c r="E9">
@@ -7886,37 +7886,37 @@
       <c r="I9" s="104">
         <v>9.96</v>
       </c>
-      <c r="J9" s="95">
+      <c r="J9" s="94">
         <v>14.48</v>
       </c>
-      <c r="K9" s="98">
+      <c r="K9" s="95">
         <v>8.49</v>
       </c>
-      <c r="L9" s="102">
+      <c r="L9" s="96">
         <v>8.99</v>
       </c>
       <c r="M9" s="92">
         <v>7.77</v>
       </c>
-      <c r="N9" s="99">
+      <c r="N9" s="93">
         <v>2.72</v>
       </c>
-      <c r="O9" s="100">
+      <c r="O9" s="97">
         <v>1.22</v>
       </c>
-      <c r="P9" s="93">
+      <c r="P9" s="98">
         <v>-1.33</v>
       </c>
-      <c r="Q9" s="94">
+      <c r="Q9" s="99">
         <v>-1.65</v>
       </c>
-      <c r="R9" s="101">
+      <c r="R9" s="100">
         <v>-1.04</v>
       </c>
-      <c r="S9" s="96">
+      <c r="S9" s="101">
         <v>-2.01</v>
       </c>
-      <c r="T9" s="97">
+      <c r="T9" s="103">
         <v>-22.79</v>
       </c>
     </row>
@@ -7930,7 +7930,7 @@
       <c r="C10" t="str">
         <v>301486</v>
       </c>
-      <c r="D10" s="105" t="str">
+      <c r="D10" s="114" t="str">
         <v>净买: 2150.96万</v>
       </c>
       <c r="E10">
@@ -7945,40 +7945,40 @@
       <c r="H10">
         <v>1.79</v>
       </c>
-      <c r="I10" s="112">
+      <c r="I10" s="107">
         <v>17.9</v>
       </c>
-      <c r="J10" s="106">
+      <c r="J10" s="108">
         <v>21.2</v>
       </c>
-      <c r="K10" s="114">
+      <c r="K10" s="109">
         <v>12.29</v>
       </c>
       <c r="L10" s="115">
         <v>14.55</v>
       </c>
-      <c r="M10" s="107">
+      <c r="M10" s="116">
         <v>21.65</v>
       </c>
-      <c r="N10" s="108">
+      <c r="N10" s="110">
         <v>15.36</v>
       </c>
-      <c r="O10" s="109">
+      <c r="O10" s="117">
         <v>9.81</v>
       </c>
-      <c r="P10" s="116">
+      <c r="P10" s="105">
         <v>10.06</v>
       </c>
-      <c r="Q10" s="117">
+      <c r="Q10" s="106">
         <v>17.68</v>
       </c>
-      <c r="R10" s="113">
+      <c r="R10" s="111">
         <v>24.45</v>
       </c>
-      <c r="S10" s="110">
+      <c r="S10" s="113">
         <v>20.16</v>
       </c>
-      <c r="T10" s="111">
+      <c r="T10" s="112">
         <v>117.52</v>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       <c r="C11" t="str">
         <v>002052</v>
       </c>
-      <c r="D11" s="127" t="str">
+      <c r="D11" s="128" t="str">
         <v>净卖: -1505.16万</v>
       </c>
       <c r="E11">
@@ -8007,40 +8007,40 @@
       <c r="H11">
         <v>10.03</v>
       </c>
-      <c r="I11" s="128">
+      <c r="I11" s="120">
         <v>0</v>
       </c>
-      <c r="J11" s="130">
+      <c r="J11" s="125">
         <v>4.18</v>
       </c>
-      <c r="K11" s="118">
+      <c r="K11" s="126">
         <v>14.59</v>
       </c>
-      <c r="L11" s="119">
+      <c r="L11" s="129">
         <v>26.06</v>
       </c>
-      <c r="M11" s="123">
+      <c r="M11" s="121">
         <v>38.68</v>
       </c>
-      <c r="N11" s="129">
+      <c r="N11" s="127">
         <v>44.38</v>
       </c>
-      <c r="O11" s="124">
+      <c r="O11" s="122">
         <v>45.82</v>
       </c>
-      <c r="P11" s="120">
+      <c r="P11" s="130">
         <v>53.88</v>
       </c>
-      <c r="Q11" s="125">
+      <c r="Q11" s="123">
         <v>45.36</v>
       </c>
-      <c r="R11" s="121">
+      <c r="R11" s="124">
         <v>34.42</v>
       </c>
-      <c r="S11" s="126">
+      <c r="S11" s="118">
         <v>39.06</v>
       </c>
-      <c r="T11" s="122">
+      <c r="T11" s="119">
         <v>-20.36</v>
       </c>
     </row>
@@ -8069,40 +8069,40 @@
       <c r="H12">
         <v>2.2</v>
       </c>
-      <c r="I12" s="137">
+      <c r="I12" s="138">
         <v>27.17</v>
       </c>
       <c r="J12" s="132">
         <v>65.32</v>
       </c>
-      <c r="K12" s="138">
+      <c r="K12" s="140">
         <v>65.69</v>
       </c>
-      <c r="L12" s="133">
+      <c r="L12" s="141">
         <v>47.53</v>
       </c>
-      <c r="M12" s="142">
+      <c r="M12" s="133">
         <v>34.9</v>
       </c>
       <c r="N12" s="134">
         <v>37.51</v>
       </c>
-      <c r="O12" s="139">
+      <c r="O12" s="135">
         <v>35.45</v>
       </c>
-      <c r="P12" s="140">
+      <c r="P12" s="136">
         <v>35.86</v>
       </c>
-      <c r="Q12" s="141">
+      <c r="Q12" s="137">
         <v>29.23</v>
       </c>
-      <c r="R12" s="143">
+      <c r="R12" s="142">
         <v>29.87</v>
       </c>
-      <c r="S12" s="135">
+      <c r="S12" s="143">
         <v>29.96</v>
       </c>
-      <c r="T12" s="136">
+      <c r="T12" s="139">
         <v>14.04</v>
       </c>
     </row>
@@ -8116,7 +8116,7 @@
       <c r="C13" t="str">
         <v>871981</v>
       </c>
-      <c r="D13" s="149" t="str">
+      <c r="D13" s="146" t="str">
         <v>净买: 779.65万</v>
       </c>
       <c r="E13">
@@ -8131,40 +8131,40 @@
       <c r="H13">
         <v>10.55</v>
       </c>
-      <c r="I13" s="146">
+      <c r="I13" s="147">
         <v>17.58</v>
       </c>
-      <c r="J13" s="150">
+      <c r="J13" s="148">
         <v>17.95</v>
       </c>
-      <c r="K13" s="151">
+      <c r="K13" s="154">
         <v>13.64</v>
       </c>
-      <c r="L13" s="145">
+      <c r="L13" s="149">
         <v>14.65</v>
       </c>
       <c r="M13" s="155">
         <v>17.15</v>
       </c>
-      <c r="N13" s="152">
+      <c r="N13" s="150">
         <v>11.72</v>
       </c>
       <c r="O13" s="156">
         <v>6.52</v>
       </c>
-      <c r="P13" s="147">
+      <c r="P13" s="151">
         <v>0.28</v>
       </c>
-      <c r="Q13" s="153">
+      <c r="Q13" s="144">
         <v>1.84</v>
       </c>
-      <c r="R13" s="154">
+      <c r="R13" s="145">
         <v>-1.52</v>
       </c>
-      <c r="S13" s="144">
+      <c r="S13" s="152">
         <v>0.2</v>
       </c>
-      <c r="T13" s="148">
+      <c r="T13" s="153">
         <v>-6.54</v>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       <c r="C14" t="str">
         <v>871981</v>
       </c>
-      <c r="D14" s="159" t="str">
+      <c r="D14" s="164" t="str">
         <v>净卖: -825.29万</v>
       </c>
       <c r="E14">
@@ -8193,40 +8193,40 @@
       <c r="H14">
         <v>7.39</v>
       </c>
-      <c r="I14" s="160">
+      <c r="I14" s="169">
         <v>-6.58</v>
       </c>
-      <c r="J14" s="162">
+      <c r="J14" s="157">
         <v>-10</v>
       </c>
-      <c r="K14" s="165">
+      <c r="K14" s="161">
         <v>-9.2</v>
       </c>
-      <c r="L14" s="166">
+      <c r="L14" s="167">
         <v>-7.22</v>
       </c>
-      <c r="M14" s="157">
+      <c r="M14" s="162">
         <v>-11.52</v>
       </c>
-      <c r="N14" s="167">
+      <c r="N14" s="158">
         <v>-15.64</v>
       </c>
-      <c r="O14" s="168">
+      <c r="O14" s="163">
         <v>-20.58</v>
       </c>
-      <c r="P14" s="169">
+      <c r="P14" s="168">
         <v>-19.34</v>
       </c>
-      <c r="Q14" s="158">
+      <c r="Q14" s="165">
         <v>-22</v>
       </c>
-      <c r="R14" s="161">
+      <c r="R14" s="159">
         <v>-20.64</v>
       </c>
-      <c r="S14" s="163">
+      <c r="S14" s="160">
         <v>-21.32</v>
       </c>
-      <c r="T14" s="164">
+      <c r="T14" s="166">
         <v>-25.98</v>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       <c r="C15" t="str">
         <v>301389</v>
       </c>
-      <c r="D15" s="177" t="str">
+      <c r="D15" s="171" t="str">
         <v>净买: 4127.06万</v>
       </c>
       <c r="E15">
@@ -8255,40 +8255,40 @@
       <c r="H15">
         <v>0.95</v>
       </c>
-      <c r="I15" s="178">
+      <c r="I15" s="181">
         <v>18.87</v>
       </c>
-      <c r="J15" s="179">
+      <c r="J15" s="172">
         <v>42.65</v>
       </c>
-      <c r="K15" s="170">
+      <c r="K15" s="182">
         <v>49.96</v>
       </c>
-      <c r="L15" s="172">
+      <c r="L15" s="177">
         <v>46.52</v>
       </c>
-      <c r="M15" s="174">
+      <c r="M15" s="178">
         <v>28.73</v>
       </c>
-      <c r="N15" s="175">
+      <c r="N15" s="173">
         <v>24.55</v>
       </c>
-      <c r="O15" s="171">
+      <c r="O15" s="174">
         <v>17.98</v>
       </c>
-      <c r="P15" s="180">
+      <c r="P15" s="179">
         <v>30.5</v>
       </c>
-      <c r="Q15" s="181">
+      <c r="Q15" s="175">
         <v>23.88</v>
       </c>
       <c r="R15" s="176">
         <v>19.89</v>
       </c>
-      <c r="S15" s="182">
+      <c r="S15" s="170">
         <v>21.91</v>
       </c>
-      <c r="T15" s="173">
+      <c r="T15" s="180">
         <v>13.99</v>
       </c>
     </row>
@@ -8302,7 +8302,7 @@
       <c r="C16" t="str">
         <v>301389</v>
       </c>
-      <c r="D16" s="190" t="str">
+      <c r="D16" s="187" t="str">
         <v>净买: 932.40万</v>
       </c>
       <c r="E16">
@@ -8317,40 +8317,40 @@
       <c r="H16">
         <v>-5.75</v>
       </c>
-      <c r="I16" s="191">
+      <c r="I16" s="188">
         <v>27.33</v>
       </c>
-      <c r="J16" s="195">
+      <c r="J16" s="189">
         <v>33.86</v>
       </c>
-      <c r="K16" s="183">
+      <c r="K16" s="190">
         <v>30.79</v>
       </c>
-      <c r="L16" s="192">
+      <c r="L16" s="191">
         <v>14.91</v>
       </c>
-      <c r="M16" s="193">
+      <c r="M16" s="184">
         <v>11.18</v>
       </c>
-      <c r="N16" s="185">
+      <c r="N16" s="192">
         <v>5.32</v>
       </c>
-      <c r="O16" s="186">
+      <c r="O16" s="193">
         <v>16.49</v>
       </c>
-      <c r="P16" s="187">
+      <c r="P16" s="185">
         <v>10.58</v>
       </c>
-      <c r="Q16" s="188">
+      <c r="Q16" s="186">
         <v>7.02</v>
       </c>
       <c r="R16" s="194">
         <v>8.82</v>
       </c>
-      <c r="S16" s="189">
+      <c r="S16" s="195">
         <v>15.05</v>
       </c>
-      <c r="T16" s="184">
+      <c r="T16" s="183">
         <v>1.75</v>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       <c r="C17" t="str">
         <v>300450</v>
       </c>
-      <c r="D17" s="207" t="str">
+      <c r="D17" s="202" t="str">
         <v>净卖: -4644.14万</v>
       </c>
       <c r="E17">
@@ -8379,40 +8379,40 @@
       <c r="H17">
         <v>5.71</v>
       </c>
-      <c r="I17" s="199">
+      <c r="I17" s="203">
         <v>13.52</v>
       </c>
-      <c r="J17" s="208">
+      <c r="J17" s="204">
         <v>30.12</v>
       </c>
-      <c r="K17" s="198">
+      <c r="K17" s="208">
         <v>40.03</v>
       </c>
-      <c r="L17" s="204">
+      <c r="L17" s="196">
         <v>40.54</v>
       </c>
-      <c r="M17" s="200">
+      <c r="M17" s="205">
         <v>43.32</v>
       </c>
-      <c r="N17" s="201">
+      <c r="N17" s="200">
         <v>71.99</v>
       </c>
-      <c r="O17" s="202">
+      <c r="O17" s="197">
         <v>83.47</v>
       </c>
-      <c r="P17" s="196">
+      <c r="P17" s="206">
         <v>79.22</v>
       </c>
-      <c r="Q17" s="203">
+      <c r="Q17" s="201">
         <v>87.37</v>
       </c>
-      <c r="R17" s="205">
+      <c r="R17" s="198">
         <v>92.23</v>
       </c>
-      <c r="S17" s="206">
+      <c r="S17" s="199">
         <v>75.19</v>
       </c>
-      <c r="T17" s="197">
+      <c r="T17" s="207">
         <v>79.03</v>
       </c>
     </row>
@@ -8426,7 +8426,7 @@
       <c r="C18" t="str">
         <v>301389</v>
       </c>
-      <c r="D18" s="210" t="str">
+      <c r="D18" s="212" t="str">
         <v>净卖: -3733.12万</v>
       </c>
       <c r="E18">
@@ -8441,40 +8441,40 @@
       <c r="H18">
         <v>2.9</v>
       </c>
-      <c r="I18" s="217">
+      <c r="I18" s="210">
         <v>-5.04</v>
       </c>
-      <c r="J18" s="211">
+      <c r="J18" s="213">
         <v>-16.57</v>
       </c>
-      <c r="K18" s="218">
+      <c r="K18" s="214">
         <v>-19.28</v>
       </c>
-      <c r="L18" s="219">
+      <c r="L18" s="215">
         <v>-23.54</v>
       </c>
-      <c r="M18" s="212">
+      <c r="M18" s="218">
         <v>-15.42</v>
       </c>
-      <c r="N18" s="213">
+      <c r="N18" s="219">
         <v>-19.72</v>
       </c>
-      <c r="O18" s="214">
+      <c r="O18" s="216">
         <v>-22.3</v>
       </c>
       <c r="P18" s="220">
         <v>-20.99</v>
       </c>
-      <c r="Q18" s="209">
+      <c r="Q18" s="221">
         <v>-16.47</v>
       </c>
-      <c r="R18" s="215">
+      <c r="R18" s="209">
         <v>-13.65</v>
       </c>
-      <c r="S18" s="221">
+      <c r="S18" s="211">
         <v>-15.93</v>
       </c>
-      <c r="T18" s="216">
+      <c r="T18" s="217">
         <v>-26.12</v>
       </c>
     </row>
@@ -8488,7 +8488,7 @@
       <c r="C19" t="str">
         <v>833580</v>
       </c>
-      <c r="D19" s="228" t="str">
+      <c r="D19" s="223" t="str">
         <v>净买: 656.67万</v>
       </c>
       <c r="E19">
@@ -8503,40 +8503,40 @@
       <c r="H19">
         <v>-1.6</v>
       </c>
-      <c r="I19" s="229">
+      <c r="I19" s="227">
         <v>32.07</v>
       </c>
-      <c r="J19" s="230">
+      <c r="J19" s="234">
         <v>19.86</v>
       </c>
-      <c r="K19" s="222">
+      <c r="K19" s="230">
         <v>10.83</v>
       </c>
       <c r="L19" s="231">
         <v>7.1</v>
       </c>
-      <c r="M19" s="223">
+      <c r="M19" s="224">
         <v>12.21</v>
       </c>
-      <c r="N19" s="233">
+      <c r="N19" s="228">
         <v>19.07</v>
       </c>
-      <c r="O19" s="224">
+      <c r="O19" s="232">
         <v>16.13</v>
       </c>
-      <c r="P19" s="232">
+      <c r="P19" s="225">
         <v>10.95</v>
       </c>
-      <c r="Q19" s="225">
+      <c r="Q19" s="222">
         <v>8.72</v>
       </c>
-      <c r="R19" s="226">
+      <c r="R19" s="233">
         <v>8.78</v>
       </c>
-      <c r="S19" s="227">
+      <c r="S19" s="226">
         <v>9.81</v>
       </c>
-      <c r="T19" s="234">
+      <c r="T19" s="229">
         <v>-2.53</v>
       </c>
     </row>
@@ -8550,7 +8550,7 @@
       <c r="C20" t="str">
         <v>833580</v>
       </c>
-      <c r="D20" s="245" t="str">
+      <c r="D20" s="238" t="str">
         <v>净卖: -782.72万</v>
       </c>
       <c r="E20">
@@ -8565,40 +8565,40 @@
       <c r="H20">
         <v>8.88</v>
       </c>
-      <c r="I20" s="246">
+      <c r="I20" s="235">
         <v>-16.65</v>
       </c>
-      <c r="J20" s="243">
+      <c r="J20" s="239">
         <v>-22.93</v>
       </c>
-      <c r="K20" s="241">
+      <c r="K20" s="236">
         <v>-25.52</v>
       </c>
-      <c r="L20" s="247">
+      <c r="L20" s="240">
         <v>-21.97</v>
       </c>
-      <c r="M20" s="235">
+      <c r="M20" s="243">
         <v>-17.2</v>
       </c>
-      <c r="N20" s="239">
+      <c r="N20" s="244">
         <v>-19.25</v>
       </c>
-      <c r="O20" s="236">
+      <c r="O20" s="241">
         <v>-22.85</v>
       </c>
-      <c r="P20" s="237">
+      <c r="P20" s="242">
         <v>-24.39</v>
       </c>
-      <c r="Q20" s="240">
+      <c r="Q20" s="245">
         <v>-24.35</v>
       </c>
-      <c r="R20" s="244">
+      <c r="R20" s="246">
         <v>-23.64</v>
       </c>
-      <c r="S20" s="242">
+      <c r="S20" s="247">
         <v>-28.45</v>
       </c>
-      <c r="T20" s="238">
+      <c r="T20" s="237">
         <v>-32.22</v>
       </c>
     </row>
@@ -8612,7 +8612,7 @@
       <c r="C21" t="str">
         <v>601068</v>
       </c>
-      <c r="D21" s="254" t="str">
+      <c r="D21" s="260" t="str">
         <v>净买: 656.95万</v>
       </c>
       <c r="E21">
@@ -8627,40 +8627,40 @@
       <c r="H21">
         <v>0</v>
       </c>
-      <c r="I21" s="255">
+      <c r="I21" s="256">
         <v>10.02</v>
       </c>
-      <c r="J21" s="258">
+      <c r="J21" s="257">
         <v>5.75</v>
       </c>
-      <c r="K21" s="256">
+      <c r="K21" s="248">
         <v>0.37</v>
       </c>
-      <c r="L21" s="250">
+      <c r="L21" s="253">
         <v>0</v>
       </c>
-      <c r="M21" s="257">
+      <c r="M21" s="259">
         <v>-1.86</v>
       </c>
-      <c r="N21" s="251">
+      <c r="N21" s="249">
         <v>0.19</v>
       </c>
-      <c r="O21" s="259">
+      <c r="O21" s="250">
         <v>0.37</v>
       </c>
-      <c r="P21" s="260">
+      <c r="P21" s="254">
         <v>-1.86</v>
       </c>
-      <c r="Q21" s="248">
+      <c r="Q21" s="251">
         <v>-1.11</v>
       </c>
       <c r="R21" s="252">
         <v>-1.86</v>
       </c>
-      <c r="S21" s="253">
+      <c r="S21" s="258">
         <v>-0.74</v>
       </c>
-      <c r="T21" s="249">
+      <c r="T21" s="255">
         <v>16.51</v>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       <c r="C22" t="str">
         <v>688146</v>
       </c>
-      <c r="D22" s="270" t="str">
+      <c r="D22" s="272" t="str">
         <v>净买: 1029.87万</v>
       </c>
       <c r="E22">
@@ -8689,40 +8689,40 @@
       <c r="H22">
         <v>-0.49</v>
       </c>
-      <c r="I22" s="271">
+      <c r="I22" s="262">
         <v>16.28</v>
       </c>
-      <c r="J22" s="272">
+      <c r="J22" s="271">
         <v>21.96</v>
       </c>
-      <c r="K22" s="263">
+      <c r="K22" s="273">
         <v>26.12</v>
       </c>
-      <c r="L22" s="273">
+      <c r="L22" s="266">
         <v>18.55</v>
       </c>
-      <c r="M22" s="264">
+      <c r="M22" s="263">
         <v>21.14</v>
       </c>
-      <c r="N22" s="265">
+      <c r="N22" s="267">
         <v>18.6</v>
       </c>
-      <c r="O22" s="267">
+      <c r="O22" s="268">
         <v>17.6</v>
       </c>
       <c r="P22" s="261">
         <v>15.63</v>
       </c>
-      <c r="Q22" s="268">
+      <c r="Q22" s="269">
         <v>18.84</v>
       </c>
-      <c r="R22" s="262">
+      <c r="R22" s="264">
         <v>17.44</v>
       </c>
-      <c r="S22" s="269">
+      <c r="S22" s="270">
         <v>15.25</v>
       </c>
-      <c r="T22" s="266">
+      <c r="T22" s="265">
         <v>66.18</v>
       </c>
     </row>
@@ -8736,7 +8736,7 @@
       <c r="C23" t="str">
         <v>600678</v>
       </c>
-      <c r="D23" s="280" t="str">
+      <c r="D23" s="285" t="str">
         <v>净卖: -1248.78万</v>
       </c>
       <c r="E23">
@@ -8751,40 +8751,40 @@
       <c r="H23">
         <v>-7.51</v>
       </c>
-      <c r="I23" s="275">
+      <c r="I23" s="278">
         <v>-2.71</v>
       </c>
-      <c r="J23" s="279">
+      <c r="J23" s="282">
         <v>-7.69</v>
       </c>
-      <c r="K23" s="276">
+      <c r="K23" s="279">
         <v>-3.85</v>
       </c>
-      <c r="L23" s="277">
+      <c r="L23" s="283">
         <v>-4.99</v>
       </c>
-      <c r="M23" s="281">
+      <c r="M23" s="280">
         <v>-9.33</v>
       </c>
-      <c r="N23" s="282">
+      <c r="N23" s="274">
         <v>-8.05</v>
       </c>
-      <c r="O23" s="283">
+      <c r="O23" s="275">
         <v>-3.7</v>
       </c>
-      <c r="P23" s="284">
+      <c r="P23" s="276">
         <v>-5.98</v>
       </c>
-      <c r="Q23" s="285">
+      <c r="Q23" s="286">
         <v>-8.9</v>
       </c>
-      <c r="R23" s="278">
+      <c r="R23" s="277">
         <v>-4.49</v>
       </c>
-      <c r="S23" s="286">
+      <c r="S23" s="281">
         <v>-2.49</v>
       </c>
-      <c r="T23" s="274">
+      <c r="T23" s="284">
         <v>-25.43</v>
       </c>
     </row>
@@ -8798,7 +8798,7 @@
       <c r="C24" t="str">
         <v>301449</v>
       </c>
-      <c r="D24" s="290" t="str">
+      <c r="D24" s="291" t="str">
         <v>净卖: -1931.35万</v>
       </c>
       <c r="E24">
@@ -8813,40 +8813,40 @@
       <c r="H24">
         <v>-7.39</v>
       </c>
-      <c r="I24" s="297">
+      <c r="I24" s="292">
         <v>-10.16</v>
       </c>
-      <c r="J24" s="298">
+      <c r="J24" s="296">
         <v>-12.52</v>
       </c>
-      <c r="K24" s="294">
+      <c r="K24" s="288">
         <v>-14.52</v>
       </c>
-      <c r="L24" s="291">
+      <c r="L24" s="289">
         <v>-15.32</v>
       </c>
-      <c r="M24" s="299">
+      <c r="M24" s="290">
         <v>-9.86</v>
       </c>
-      <c r="N24" s="292">
+      <c r="N24" s="297">
         <v>-11.91</v>
       </c>
       <c r="O24" s="293">
         <v>-12.71</v>
       </c>
-      <c r="P24" s="287">
+      <c r="P24" s="298">
         <v>-12.71</v>
       </c>
-      <c r="Q24" s="288">
+      <c r="Q24" s="294">
         <v>-16.26</v>
       </c>
-      <c r="R24" s="289">
+      <c r="R24" s="299">
         <v>-10.13</v>
       </c>
-      <c r="S24" s="295">
+      <c r="S24" s="287">
         <v>-12.25</v>
       </c>
-      <c r="T24" s="296">
+      <c r="T24" s="295">
         <v>-17.11</v>
       </c>
     </row>
@@ -8860,7 +8860,7 @@
       <c r="C25" t="str">
         <v>688137</v>
       </c>
-      <c r="D25" s="304" t="str">
+      <c r="D25" s="305" t="str">
         <v>净买: 809.16万</v>
       </c>
       <c r="E25">
@@ -8875,40 +8875,40 @@
       <c r="H25">
         <v>-0.09</v>
       </c>
-      <c r="I25" s="311">
+      <c r="I25" s="306">
         <v>15.54</v>
       </c>
-      <c r="J25" s="305">
+      <c r="J25" s="301">
         <v>13.21</v>
       </c>
       <c r="K25" s="308">
         <v>11.95</v>
       </c>
-      <c r="L25" s="309">
+      <c r="L25" s="302">
         <v>9.95</v>
       </c>
-      <c r="M25" s="300">
+      <c r="M25" s="307">
         <v>6.85</v>
       </c>
-      <c r="N25" s="301">
+      <c r="N25" s="303">
         <v>6.78</v>
       </c>
-      <c r="O25" s="312">
+      <c r="O25" s="309">
         <v>13.58</v>
       </c>
-      <c r="P25" s="306">
+      <c r="P25" s="310">
         <v>14.61</v>
       </c>
-      <c r="Q25" s="302">
+      <c r="Q25" s="311">
         <v>16.47</v>
       </c>
-      <c r="R25" s="303">
+      <c r="R25" s="312">
         <v>23.92</v>
       </c>
-      <c r="S25" s="310">
+      <c r="S25" s="300">
         <v>15.3</v>
       </c>
-      <c r="T25" s="307">
+      <c r="T25" s="304">
         <v>16.63</v>
       </c>
     </row>
@@ -8922,7 +8922,7 @@
       <c r="C26" t="str">
         <v>301408</v>
       </c>
-      <c r="D26" s="313" t="str">
+      <c r="D26" s="317" t="str">
         <v>净卖: -2207.20万</v>
       </c>
       <c r="E26">
@@ -8937,40 +8937,40 @@
       <c r="H26">
         <v>1.45</v>
       </c>
-      <c r="I26" s="319">
+      <c r="I26" s="322">
         <v>18.28</v>
       </c>
-      <c r="J26" s="314">
+      <c r="J26" s="321">
         <v>-5.37</v>
       </c>
-      <c r="K26" s="315">
+      <c r="K26" s="313">
         <v>-14.43</v>
       </c>
-      <c r="L26" s="324">
+      <c r="L26" s="323">
         <v>-13.43</v>
       </c>
-      <c r="M26" s="316">
+      <c r="M26" s="318">
         <v>-12.24</v>
       </c>
-      <c r="N26" s="317">
+      <c r="N26" s="314">
         <v>-13.31</v>
       </c>
-      <c r="O26" s="322">
+      <c r="O26" s="315">
         <v>-7.91</v>
       </c>
-      <c r="P26" s="320">
+      <c r="P26" s="324">
         <v>-4.69</v>
       </c>
-      <c r="Q26" s="318">
+      <c r="Q26" s="319">
         <v>-0.32</v>
       </c>
-      <c r="R26" s="323">
+      <c r="R26" s="325">
         <v>-8.55</v>
       </c>
-      <c r="S26" s="325">
+      <c r="S26" s="320">
         <v>-11.88</v>
       </c>
-      <c r="T26" s="321">
+      <c r="T26" s="316">
         <v>-19.67</v>
       </c>
     </row>
@@ -8984,7 +8984,7 @@
       <c r="C27" t="str">
         <v>603598</v>
       </c>
-      <c r="D27" s="331" t="str">
+      <c r="D27" s="335" t="str">
         <v>净卖: -958.53万</v>
       </c>
       <c r="E27">
@@ -8999,40 +8999,40 @@
       <c r="H27">
         <v>-10.01</v>
       </c>
-      <c r="I27" s="334">
+      <c r="I27" s="337">
         <v>0</v>
       </c>
-      <c r="J27" s="335">
+      <c r="J27" s="329">
         <v>-5.64</v>
       </c>
-      <c r="K27" s="336">
+      <c r="K27" s="338">
         <v>-1.1</v>
       </c>
-      <c r="L27" s="338">
+      <c r="L27" s="336">
         <v>1.88</v>
       </c>
-      <c r="M27" s="326">
+      <c r="M27" s="330">
         <v>4.9</v>
       </c>
-      <c r="N27" s="327">
+      <c r="N27" s="326">
         <v>3.33</v>
       </c>
-      <c r="O27" s="332">
+      <c r="O27" s="334">
         <v>1.33</v>
       </c>
-      <c r="P27" s="333">
+      <c r="P27" s="331">
         <v>-0.86</v>
       </c>
-      <c r="Q27" s="328">
+      <c r="Q27" s="327">
         <v>4.62</v>
       </c>
-      <c r="R27" s="329">
+      <c r="R27" s="328">
         <v>15.09</v>
       </c>
-      <c r="S27" s="330">
+      <c r="S27" s="332">
         <v>13.64</v>
       </c>
-      <c r="T27" s="337">
+      <c r="T27" s="333">
         <v>-16.81</v>
       </c>
     </row>
@@ -9046,7 +9046,7 @@
       <c r="C28" t="str">
         <v>920368</v>
       </c>
-      <c r="D28" s="345" t="str">
+      <c r="D28" s="341" t="str">
         <v>净买: 2785.37万</v>
       </c>
       <c r="E28">
@@ -9061,40 +9061,40 @@
       <c r="H28">
         <v>6.62</v>
       </c>
-      <c r="I28" s="342">
+      <c r="I28" s="344">
         <v>21.92</v>
       </c>
-      <c r="J28" s="346">
+      <c r="J28" s="345">
         <v>30.07</v>
       </c>
       <c r="K28" s="351">
         <v>52.53</v>
       </c>
-      <c r="L28" s="347">
+      <c r="L28" s="346">
         <v>59.26</v>
       </c>
-      <c r="M28" s="348">
+      <c r="M28" s="339">
         <v>51.53</v>
       </c>
-      <c r="N28" s="343">
+      <c r="N28" s="347">
         <v>48.42</v>
       </c>
-      <c r="O28" s="349">
+      <c r="O28" s="348">
         <v>50.72</v>
       </c>
-      <c r="P28" s="339">
+      <c r="P28" s="349">
         <v>78.13</v>
       </c>
       <c r="Q28" s="340">
         <v>61.84</v>
       </c>
-      <c r="R28" s="350">
+      <c r="R28" s="343">
         <v>41.93</v>
       </c>
-      <c r="S28" s="344">
+      <c r="S28" s="350">
         <v>52.17</v>
       </c>
-      <c r="T28" s="341">
+      <c r="T28" s="342">
         <v>-2.53</v>
       </c>
     </row>
@@ -9108,7 +9108,7 @@
       <c r="C29" t="str">
         <v>300017</v>
       </c>
-      <c r="D29" s="355" t="str">
+      <c r="D29" s="353" t="str">
         <v>净卖: -8231.84万</v>
       </c>
       <c r="E29">
@@ -9123,40 +9123,40 @@
       <c r="H29">
         <v>1.57</v>
       </c>
-      <c r="I29" s="356">
+      <c r="I29" s="357">
         <v>18.18</v>
       </c>
-      <c r="J29" s="361">
+      <c r="J29" s="359">
         <v>16.12</v>
       </c>
-      <c r="K29" s="357">
+      <c r="K29" s="360">
         <v>33.7</v>
       </c>
-      <c r="L29" s="362">
+      <c r="L29" s="361">
         <v>44.08</v>
       </c>
-      <c r="M29" s="358">
+      <c r="M29" s="354">
         <v>42.02</v>
       </c>
-      <c r="N29" s="360">
+      <c r="N29" s="355">
         <v>44.77</v>
       </c>
-      <c r="O29" s="352">
+      <c r="O29" s="364">
         <v>65.61</v>
       </c>
-      <c r="P29" s="359">
+      <c r="P29" s="362">
         <v>43.4</v>
       </c>
       <c r="Q29" s="363">
         <v>54.12</v>
       </c>
-      <c r="R29" s="364">
+      <c r="R29" s="358">
         <v>53.77</v>
       </c>
-      <c r="S29" s="353">
+      <c r="S29" s="356">
         <v>62.09</v>
       </c>
-      <c r="T29" s="354">
+      <c r="T29" s="352">
         <v>62.09</v>
       </c>
     </row>
@@ -9170,7 +9170,7 @@
       <c r="C30" t="str">
         <v>603075</v>
       </c>
-      <c r="D30" s="367" t="str">
+      <c r="D30" s="377" t="str">
         <v>净卖: -1295.61万</v>
       </c>
       <c r="E30">
@@ -9185,40 +9185,40 @@
       <c r="H30">
         <v>-0.04</v>
       </c>
-      <c r="I30" s="372">
+      <c r="I30" s="367">
         <v>1.83</v>
       </c>
-      <c r="J30" s="376">
+      <c r="J30" s="374">
         <v>-4.09</v>
       </c>
-      <c r="K30" s="377">
+      <c r="K30" s="365">
         <v>-6.43</v>
       </c>
-      <c r="L30" s="368">
+      <c r="L30" s="366">
         <v>-7.11</v>
       </c>
-      <c r="M30" s="365">
+      <c r="M30" s="370">
         <v>-5.88</v>
       </c>
-      <c r="N30" s="373">
+      <c r="N30" s="371">
         <v>-7.63</v>
       </c>
-      <c r="O30" s="369">
+      <c r="O30" s="368">
         <v>-5.52</v>
       </c>
-      <c r="P30" s="366">
+      <c r="P30" s="372">
         <v>-4.65</v>
       </c>
-      <c r="Q30" s="374">
+      <c r="Q30" s="375">
         <v>-5.2</v>
       </c>
-      <c r="R30" s="370">
+      <c r="R30" s="376">
         <v>-5.72</v>
       </c>
-      <c r="S30" s="371">
+      <c r="S30" s="373">
         <v>-4.92</v>
       </c>
-      <c r="T30" s="375">
+      <c r="T30" s="369">
         <v>-9.65</v>
       </c>
     </row>
@@ -9232,7 +9232,7 @@
       <c r="C31" t="str">
         <v>920368</v>
       </c>
-      <c r="D31" s="381" t="str">
+      <c r="D31" s="386" t="str">
         <v>净卖: -476.30万</v>
       </c>
       <c r="E31">
@@ -9247,40 +9247,40 @@
       <c r="H31">
         <v>10.26</v>
       </c>
-      <c r="I31" s="378">
+      <c r="I31" s="382">
         <v>-3.25</v>
       </c>
-      <c r="J31" s="388">
+      <c r="J31" s="387">
         <v>13.46</v>
       </c>
-      <c r="K31" s="389">
+      <c r="K31" s="388">
         <v>18.46</v>
       </c>
-      <c r="L31" s="379">
+      <c r="L31" s="378">
         <v>12.71</v>
       </c>
-      <c r="M31" s="385">
+      <c r="M31" s="389">
         <v>10.4</v>
       </c>
-      <c r="N31" s="382">
+      <c r="N31" s="383">
         <v>12.12</v>
       </c>
-      <c r="O31" s="390">
+      <c r="O31" s="379">
         <v>32.5</v>
       </c>
-      <c r="P31" s="386">
+      <c r="P31" s="384">
         <v>20.38</v>
       </c>
-      <c r="Q31" s="383">
+      <c r="Q31" s="390">
         <v>5.58</v>
       </c>
-      <c r="R31" s="380">
+      <c r="R31" s="385">
         <v>13.19</v>
       </c>
-      <c r="S31" s="387">
+      <c r="S31" s="380">
         <v>23.15</v>
       </c>
-      <c r="T31" s="384">
+      <c r="T31" s="381">
         <v>-27.5</v>
       </c>
     </row>
@@ -9294,7 +9294,7 @@
       <c r="C32" t="str">
         <v>600273</v>
       </c>
-      <c r="D32" s="397" t="str">
+      <c r="D32" s="392" t="str">
         <v>净卖: -3657.56万</v>
       </c>
       <c r="E32">
@@ -9309,40 +9309,40 @@
       <c r="H32">
         <v>3.89</v>
       </c>
-      <c r="I32" s="398">
+      <c r="I32" s="393">
         <v>5.92</v>
       </c>
-      <c r="J32" s="403">
+      <c r="J32" s="396">
         <v>2.96</v>
       </c>
-      <c r="K32" s="393">
+      <c r="K32" s="401">
         <v>-4.88</v>
       </c>
-      <c r="L32" s="399">
+      <c r="L32" s="394">
         <v>-3.05</v>
       </c>
-      <c r="M32" s="400">
+      <c r="M32" s="397">
         <v>-1.31</v>
       </c>
       <c r="N32" s="391">
         <v>-4.18</v>
       </c>
-      <c r="O32" s="394">
+      <c r="O32" s="398">
         <v>-1.74</v>
       </c>
-      <c r="P32" s="392">
+      <c r="P32" s="399">
         <v>-1.66</v>
       </c>
-      <c r="Q32" s="401">
+      <c r="Q32" s="395">
         <v>0.78</v>
       </c>
-      <c r="R32" s="395">
+      <c r="R32" s="402">
         <v>1.83</v>
       </c>
-      <c r="S32" s="402">
+      <c r="S32" s="400">
         <v>2.7</v>
       </c>
-      <c r="T32" s="396">
+      <c r="T32" s="403">
         <v>-21.25</v>
       </c>
     </row>
@@ -9356,7 +9356,7 @@
       <c r="C33" t="str">
         <v>300257</v>
       </c>
-      <c r="D33" s="407" t="str">
+      <c r="D33" s="413" t="str">
         <v>净卖: -2507.66万</v>
       </c>
       <c r="E33">
@@ -9371,40 +9371,40 @@
       <c r="H33">
         <v>2.76</v>
       </c>
-      <c r="I33" s="408">
+      <c r="I33" s="416">
         <v>16.77</v>
       </c>
-      <c r="J33" s="409">
+      <c r="J33" s="412">
         <v>17.59</v>
       </c>
       <c r="K33" s="414">
         <v>16.46</v>
       </c>
-      <c r="L33" s="404">
+      <c r="L33" s="407">
         <v>7.35</v>
       </c>
-      <c r="M33" s="412">
+      <c r="M33" s="404">
         <v>14.56</v>
       </c>
-      <c r="N33" s="405">
+      <c r="N33" s="415">
         <v>8.23</v>
       </c>
-      <c r="O33" s="415">
+      <c r="O33" s="408">
         <v>8.64</v>
       </c>
-      <c r="P33" s="410">
+      <c r="P33" s="405">
         <v>8.67</v>
       </c>
-      <c r="Q33" s="416">
+      <c r="Q33" s="409">
         <v>5.17</v>
       </c>
-      <c r="R33" s="413">
+      <c r="R33" s="406">
         <v>1.33</v>
       </c>
-      <c r="S33" s="411">
+      <c r="S33" s="410">
         <v>1.8</v>
       </c>
-      <c r="T33" s="406">
+      <c r="T33" s="411">
         <v>-0.07</v>
       </c>
     </row>
@@ -9467,40 +9467,40 @@
       <c r="F35" t="str"/>
       <c r="G35" t="str"/>
       <c r="H35" t="str"/>
-      <c r="I35" s="420">
+      <c r="I35" s="418">
         <v>68.75</v>
       </c>
-      <c r="J35" s="423">
+      <c r="J35" s="419">
         <v>71.88</v>
       </c>
-      <c r="K35" s="424">
+      <c r="K35" s="420">
         <v>68.75</v>
       </c>
-      <c r="L35" s="417">
+      <c r="L35" s="424">
         <v>68.75</v>
       </c>
-      <c r="M35" s="425">
+      <c r="M35" s="421">
         <v>68.75</v>
       </c>
-      <c r="N35" s="421">
+      <c r="N35" s="422">
         <v>71.88</v>
       </c>
-      <c r="O35" s="418">
+      <c r="O35" s="425">
         <v>71.88</v>
       </c>
       <c r="P35" s="426">
         <v>62.5</v>
       </c>
-      <c r="Q35" s="419">
+      <c r="Q35" s="427">
         <v>65.63</v>
       </c>
-      <c r="R35" s="427">
+      <c r="R35" s="428">
         <v>62.5</v>
       </c>
-      <c r="S35" s="422">
+      <c r="S35" s="423">
         <v>65.63</v>
       </c>
-      <c r="T35" s="428">
+      <c r="T35" s="417">
         <v>34.38</v>
       </c>
     </row>
@@ -9515,40 +9515,40 @@
       <c r="F36" t="str"/>
       <c r="G36" t="str"/>
       <c r="H36" t="str"/>
-      <c r="I36" s="433">
+      <c r="I36" s="439">
         <v>8.56</v>
       </c>
-      <c r="J36" s="434">
+      <c r="J36" s="435">
         <v>10.13</v>
       </c>
-      <c r="K36" s="440">
+      <c r="K36" s="429">
         <v>11.47</v>
       </c>
-      <c r="L36" s="429">
+      <c r="L36" s="430">
         <v>10.84</v>
       </c>
-      <c r="M36" s="435">
+      <c r="M36" s="436">
         <v>11.29</v>
       </c>
-      <c r="N36" s="437">
+      <c r="N36" s="431">
         <v>10.99</v>
       </c>
-      <c r="O36" s="438">
+      <c r="O36" s="432">
         <v>12.53</v>
       </c>
-      <c r="P36" s="436">
+      <c r="P36" s="433">
         <v>11.98</v>
       </c>
-      <c r="Q36" s="430">
+      <c r="Q36" s="434">
         <v>10.83</v>
       </c>
-      <c r="R36" s="431">
+      <c r="R36" s="437">
         <v>10.67</v>
       </c>
-      <c r="S36" s="439">
+      <c r="S36" s="438">
         <v>10.08</v>
       </c>
-      <c r="T36" s="432">
+      <c r="T36" s="440">
         <v>3.14</v>
       </c>
     </row>

--- a/youzi/大小说家/index.xlsx
+++ b/youzi/大小说家/index.xlsx
@@ -39,19 +39,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7ECA90"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE46370"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7ECA90"/>
+        <fgColor rgb="FFC12837"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -63,25 +111,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFCF2F3E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -93,25 +147,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEAF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
+        <fgColor rgb="FFBF2836"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -135,37 +171,475 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9EA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4352"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
+        <fgColor rgb="FF45B25E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEFF0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBE3C4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB9199"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -177,199 +651,1867 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF6CDD1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8E1C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91D2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE15663"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF3F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDE4C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91D2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBD5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7833"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8336"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3DAF57"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF59BB6F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD75"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF35AC50"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBD6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAEFDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3948"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4453"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BEC3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB766"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF37AD52"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF73C586"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7E1C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD23040"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9EA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4352"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFEA8790"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2DA949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7BC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4BB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB4E0BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -381,2161 +2523,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B25E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEFF0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBE3C4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB9199"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CDD1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8E1C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91D2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15663"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDE4C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF3F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91D2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFEBD5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEB9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEB9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEB9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8336"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD75"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3DAF57"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF59BB6F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7833"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF35AC50"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4453"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3948"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAEFDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFEBD6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF37AD52"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB766"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF73C586"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4BB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7BC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8790"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB4E0BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2DA949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2547,12 +2553,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFAD202D"/>
         <bgColor/>
       </patternFill>
@@ -2565,12 +2565,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFBE2735"/>
         <bgColor/>
       </patternFill>
@@ -2589,6 +2583,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFCE2F3E"/>
         <bgColor/>
       </patternFill>
@@ -2673,7 +2673,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -7434,7 +7434,7 @@
       <c r="C2" t="str">
         <v>603319</v>
       </c>
-      <c r="D2" s="9" t="str">
+      <c r="D2" s="5" t="str">
         <v>净卖: -4050.11万</v>
       </c>
       <c r="E2">
@@ -7449,41 +7449,41 @@
       <c r="H2">
         <v>-2.13</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="1">
         <v>-8.04</v>
       </c>
-      <c r="J2" s="10">
+      <c r="J2" s="6">
         <v>-7</v>
       </c>
-      <c r="K2" s="11">
+      <c r="K2" s="2">
         <v>-0.47</v>
       </c>
-      <c r="L2" s="12">
+      <c r="L2" s="3">
         <v>3.68</v>
       </c>
-      <c r="M2" s="6">
+      <c r="M2" s="9">
         <v>10.89</v>
       </c>
-      <c r="N2" s="1">
+      <c r="N2" s="10">
         <v>3.84</v>
       </c>
-      <c r="O2" s="2">
+      <c r="O2" s="7">
         <v>6.4</v>
       </c>
-      <c r="P2" s="13">
+      <c r="P2" s="11">
         <v>7.52</v>
       </c>
-      <c r="Q2" s="3">
+      <c r="Q2" s="8">
         <v>-2.98</v>
       </c>
-      <c r="R2" s="4">
+      <c r="R2" s="12">
         <v>2.88</v>
       </c>
-      <c r="S2" s="7">
+      <c r="S2" s="13">
         <v>6.19</v>
       </c>
-      <c r="T2" s="8">
-        <v>-9.36</v>
+      <c r="T2" s="4">
+        <v>-12.05</v>
       </c>
     </row>
     <row r="3">
@@ -7496,7 +7496,7 @@
       <c r="C3" t="str">
         <v>002923</v>
       </c>
-      <c r="D3" s="17" t="str">
+      <c r="D3" s="18" t="str">
         <v>净卖: -1342.21万</v>
       </c>
       <c r="E3">
@@ -7511,41 +7511,41 @@
       <c r="H3">
         <v>2.17</v>
       </c>
-      <c r="I3" s="20">
+      <c r="I3" s="19">
         <v>7.69</v>
       </c>
-      <c r="J3" s="21">
+      <c r="J3" s="24">
         <v>17.63</v>
       </c>
-      <c r="K3" s="26">
+      <c r="K3" s="23">
         <v>5.88</v>
       </c>
-      <c r="L3" s="22">
+      <c r="L3" s="15">
         <v>-4.3</v>
       </c>
-      <c r="M3" s="23">
+      <c r="M3" s="16">
         <v>-13.87</v>
       </c>
-      <c r="N3" s="18">
+      <c r="N3" s="20">
         <v>-11.45</v>
       </c>
-      <c r="O3" s="24">
+      <c r="O3" s="25">
         <v>-15.08</v>
       </c>
-      <c r="P3" s="19">
+      <c r="P3" s="17">
         <v>-14.66</v>
       </c>
-      <c r="Q3" s="16">
+      <c r="Q3" s="26">
         <v>-12.84</v>
       </c>
-      <c r="R3" s="14">
+      <c r="R3" s="21">
         <v>-21.56</v>
       </c>
-      <c r="S3" s="15">
+      <c r="S3" s="22">
         <v>-24.59</v>
       </c>
-      <c r="T3" s="25">
-        <v>-23.92</v>
+      <c r="T3" s="14">
+        <v>-24.29</v>
       </c>
     </row>
     <row r="4">
@@ -7573,41 +7573,41 @@
       <c r="H4">
         <v>-1.38</v>
       </c>
-      <c r="I4" s="38">
+      <c r="I4" s="31">
         <v>11.55</v>
       </c>
-      <c r="J4" s="28">
+      <c r="J4" s="39">
         <v>2.39</v>
       </c>
-      <c r="K4" s="33">
+      <c r="K4" s="35">
         <v>12.55</v>
       </c>
-      <c r="L4" s="34">
+      <c r="L4" s="27">
         <v>5.58</v>
       </c>
-      <c r="M4" s="39">
+      <c r="M4" s="36">
         <v>16.14</v>
       </c>
-      <c r="N4" s="30">
+      <c r="N4" s="32">
         <v>21.51</v>
       </c>
-      <c r="O4" s="31">
+      <c r="O4" s="33">
         <v>16.14</v>
       </c>
-      <c r="P4" s="27">
+      <c r="P4" s="28">
         <v>19.92</v>
       </c>
-      <c r="Q4" s="35">
+      <c r="Q4" s="29">
         <v>20.72</v>
       </c>
-      <c r="R4" s="36">
+      <c r="R4" s="30">
         <v>15.94</v>
       </c>
-      <c r="S4" s="32">
+      <c r="S4" s="34">
         <v>8.96</v>
       </c>
-      <c r="T4" s="29">
-        <v>27.09</v>
+      <c r="T4" s="38">
+        <v>24.5</v>
       </c>
     </row>
     <row r="5">
@@ -7620,7 +7620,7 @@
       <c r="C5" t="str">
         <v>600735</v>
       </c>
-      <c r="D5" s="52" t="str">
+      <c r="D5" s="51" t="str">
         <v>净买: 1155.67万</v>
       </c>
       <c r="E5">
@@ -7635,40 +7635,40 @@
       <c r="H5">
         <v>1.24</v>
       </c>
-      <c r="I5" s="40">
+      <c r="I5" s="52">
         <v>8.71</v>
       </c>
-      <c r="J5" s="41">
+      <c r="J5" s="45">
         <v>8.84</v>
       </c>
-      <c r="K5" s="45">
+      <c r="K5" s="48">
         <v>7.48</v>
       </c>
-      <c r="L5" s="48">
+      <c r="L5" s="46">
         <v>4.63</v>
       </c>
-      <c r="M5" s="42">
+      <c r="M5" s="49">
         <v>5.71</v>
       </c>
-      <c r="N5" s="51">
+      <c r="N5" s="40">
         <v>11.16</v>
       </c>
-      <c r="O5" s="43">
+      <c r="O5" s="47">
         <v>9.66</v>
       </c>
-      <c r="P5" s="46">
+      <c r="P5" s="41">
         <v>6.8</v>
       </c>
-      <c r="Q5" s="44">
+      <c r="Q5" s="42">
         <v>12.24</v>
       </c>
-      <c r="R5" s="49">
+      <c r="R5" s="50">
         <v>13.88</v>
       </c>
-      <c r="S5" s="50">
+      <c r="S5" s="43">
         <v>10.07</v>
       </c>
-      <c r="T5" s="47">
+      <c r="T5" s="44">
         <v>-8.44</v>
       </c>
     </row>
@@ -7697,40 +7697,40 @@
       <c r="H6">
         <v>-5.01</v>
       </c>
-      <c r="I6" s="62">
+      <c r="I6" s="58">
         <v>5.4</v>
       </c>
       <c r="J6" s="53">
         <v>4.08</v>
       </c>
-      <c r="K6" s="63">
+      <c r="K6" s="54">
         <v>1.32</v>
       </c>
       <c r="L6" s="64">
         <v>2.37</v>
       </c>
-      <c r="M6" s="65">
+      <c r="M6" s="59">
         <v>7.64</v>
       </c>
-      <c r="N6" s="54">
+      <c r="N6" s="60">
         <v>6.19</v>
       </c>
-      <c r="O6" s="58">
+      <c r="O6" s="55">
         <v>3.43</v>
       </c>
-      <c r="P6" s="59">
+      <c r="P6" s="61">
         <v>8.7</v>
       </c>
-      <c r="Q6" s="55">
+      <c r="Q6" s="65">
         <v>10.28</v>
       </c>
-      <c r="R6" s="60">
+      <c r="R6" s="56">
         <v>6.59</v>
       </c>
-      <c r="S6" s="61">
+      <c r="S6" s="62">
         <v>3.43</v>
       </c>
-      <c r="T6" s="56">
+      <c r="T6" s="63">
         <v>-11.33</v>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       <c r="C7" t="str">
         <v>002365</v>
       </c>
-      <c r="D7" s="71" t="str">
+      <c r="D7" s="78" t="str">
         <v>净卖: -2887.03万</v>
       </c>
       <c r="E7">
@@ -7759,41 +7759,41 @@
       <c r="H7">
         <v>3.76</v>
       </c>
-      <c r="I7" s="67">
+      <c r="I7" s="73">
         <v>-4.32</v>
       </c>
-      <c r="J7" s="68">
+      <c r="J7" s="69">
         <v>5.25</v>
       </c>
-      <c r="K7" s="69">
+      <c r="K7" s="74">
         <v>15.76</v>
       </c>
-      <c r="L7" s="76">
+      <c r="L7" s="66">
         <v>27.33</v>
       </c>
-      <c r="M7" s="78">
+      <c r="M7" s="70">
         <v>35.58</v>
       </c>
-      <c r="N7" s="72">
+      <c r="N7" s="75">
         <v>40.03</v>
       </c>
-      <c r="O7" s="66">
+      <c r="O7" s="67">
         <v>54.03</v>
       </c>
-      <c r="P7" s="73">
+      <c r="P7" s="76">
         <v>38.65</v>
       </c>
-      <c r="Q7" s="74">
+      <c r="Q7" s="68">
         <v>24.77</v>
       </c>
-      <c r="R7" s="75">
+      <c r="R7" s="71">
         <v>28.27</v>
       </c>
-      <c r="S7" s="70">
+      <c r="S7" s="77">
         <v>22.51</v>
       </c>
-      <c r="T7" s="77">
-        <v>-14.7</v>
+      <c r="T7" s="72">
+        <v>-14.45</v>
       </c>
     </row>
     <row r="8">
@@ -7806,7 +7806,7 @@
       <c r="C8" t="str">
         <v>603585</v>
       </c>
-      <c r="D8" s="89" t="str">
+      <c r="D8" s="81" t="str">
         <v>净买: 590.46万</v>
       </c>
       <c r="E8">
@@ -7821,41 +7821,41 @@
       <c r="H8">
         <v>-2.32</v>
       </c>
-      <c r="I8" s="86">
+      <c r="I8" s="82">
         <v>8.09</v>
       </c>
-      <c r="J8" s="90">
+      <c r="J8" s="88">
         <v>7.12</v>
       </c>
-      <c r="K8" s="87">
+      <c r="K8" s="83">
         <v>17.86</v>
       </c>
-      <c r="L8" s="91">
+      <c r="L8" s="89">
         <v>29.63</v>
       </c>
-      <c r="M8" s="83">
+      <c r="M8" s="90">
         <v>16.68</v>
       </c>
-      <c r="N8" s="79">
+      <c r="N8" s="84">
         <v>5.02</v>
       </c>
-      <c r="O8" s="81">
+      <c r="O8" s="79">
         <v>0.38</v>
       </c>
-      <c r="P8" s="88">
+      <c r="P8" s="91">
         <v>2.75</v>
       </c>
-      <c r="Q8" s="84">
+      <c r="Q8" s="86">
         <v>2.05</v>
       </c>
-      <c r="R8" s="80">
+      <c r="R8" s="87">
         <v>-0.32</v>
       </c>
       <c r="S8" s="85">
         <v>-1.57</v>
       </c>
-      <c r="T8" s="82">
-        <v>29.84</v>
+      <c r="T8" s="80">
+        <v>27.31</v>
       </c>
     </row>
     <row r="9">
@@ -7868,7 +7868,7 @@
       <c r="C9" t="str">
         <v>003029</v>
       </c>
-      <c r="D9" s="102" t="str">
+      <c r="D9" s="92" t="str">
         <v>净卖: -1441.18万</v>
       </c>
       <c r="E9">
@@ -7883,41 +7883,41 @@
       <c r="H9">
         <v>0.04</v>
       </c>
-      <c r="I9" s="104">
+      <c r="I9" s="98">
         <v>9.96</v>
       </c>
-      <c r="J9" s="94">
+      <c r="J9" s="95">
         <v>14.48</v>
       </c>
-      <c r="K9" s="95">
+      <c r="K9" s="99">
         <v>8.49</v>
       </c>
-      <c r="L9" s="96">
+      <c r="L9" s="93">
         <v>8.99</v>
       </c>
-      <c r="M9" s="92">
+      <c r="M9" s="96">
         <v>7.77</v>
       </c>
-      <c r="N9" s="93">
+      <c r="N9" s="100">
         <v>2.72</v>
       </c>
-      <c r="O9" s="97">
+      <c r="O9" s="103">
         <v>1.22</v>
       </c>
-      <c r="P9" s="98">
+      <c r="P9" s="101">
         <v>-1.33</v>
       </c>
-      <c r="Q9" s="99">
+      <c r="Q9" s="104">
         <v>-1.65</v>
       </c>
-      <c r="R9" s="100">
+      <c r="R9" s="97">
         <v>-1.04</v>
       </c>
-      <c r="S9" s="101">
+      <c r="S9" s="94">
         <v>-2.01</v>
       </c>
-      <c r="T9" s="103">
-        <v>-22.79</v>
+      <c r="T9" s="102">
+        <v>-22.72</v>
       </c>
     </row>
     <row r="10">
@@ -7945,13 +7945,13 @@
       <c r="H10">
         <v>1.79</v>
       </c>
-      <c r="I10" s="107">
+      <c r="I10" s="109">
         <v>17.9</v>
       </c>
-      <c r="J10" s="108">
+      <c r="J10" s="112">
         <v>21.2</v>
       </c>
-      <c r="K10" s="109">
+      <c r="K10" s="106">
         <v>12.29</v>
       </c>
       <c r="L10" s="115">
@@ -7963,23 +7963,23 @@
       <c r="N10" s="110">
         <v>15.36</v>
       </c>
-      <c r="O10" s="117">
+      <c r="O10" s="113">
         <v>9.81</v>
       </c>
-      <c r="P10" s="105">
+      <c r="P10" s="107">
         <v>10.06</v>
       </c>
-      <c r="Q10" s="106">
+      <c r="Q10" s="117">
         <v>17.68</v>
       </c>
       <c r="R10" s="111">
         <v>24.45</v>
       </c>
-      <c r="S10" s="113">
+      <c r="S10" s="108">
         <v>20.16</v>
       </c>
-      <c r="T10" s="112">
-        <v>117.52</v>
+      <c r="T10" s="105">
+        <v>123.33</v>
       </c>
     </row>
     <row r="11">
@@ -7992,7 +7992,7 @@
       <c r="C11" t="str">
         <v>002052</v>
       </c>
-      <c r="D11" s="128" t="str">
+      <c r="D11" s="124" t="str">
         <v>净卖: -1505.16万</v>
       </c>
       <c r="E11">
@@ -8007,41 +8007,41 @@
       <c r="H11">
         <v>10.03</v>
       </c>
-      <c r="I11" s="120">
+      <c r="I11" s="130">
         <v>0</v>
       </c>
-      <c r="J11" s="125">
+      <c r="J11" s="121">
         <v>4.18</v>
       </c>
-      <c r="K11" s="126">
+      <c r="K11" s="122">
         <v>14.59</v>
       </c>
-      <c r="L11" s="129">
+      <c r="L11" s="127">
         <v>26.06</v>
       </c>
-      <c r="M11" s="121">
+      <c r="M11" s="118">
         <v>38.68</v>
       </c>
-      <c r="N11" s="127">
+      <c r="N11" s="128">
         <v>44.38</v>
       </c>
-      <c r="O11" s="122">
+      <c r="O11" s="119">
         <v>45.82</v>
       </c>
-      <c r="P11" s="130">
+      <c r="P11" s="125">
         <v>53.88</v>
       </c>
-      <c r="Q11" s="123">
+      <c r="Q11" s="126">
         <v>45.36</v>
       </c>
-      <c r="R11" s="124">
+      <c r="R11" s="123">
         <v>34.42</v>
       </c>
-      <c r="S11" s="118">
+      <c r="S11" s="129">
         <v>39.06</v>
       </c>
-      <c r="T11" s="119">
-        <v>-20.36</v>
+      <c r="T11" s="120">
+        <v>-20.52</v>
       </c>
     </row>
     <row r="12">
@@ -8054,7 +8054,7 @@
       <c r="C12" t="str">
         <v>430476</v>
       </c>
-      <c r="D12" s="131" t="str">
+      <c r="D12" s="141" t="str">
         <v>净买: 566.61万</v>
       </c>
       <c r="E12">
@@ -8069,40 +8069,40 @@
       <c r="H12">
         <v>2.2</v>
       </c>
-      <c r="I12" s="138">
+      <c r="I12" s="134">
         <v>27.17</v>
       </c>
-      <c r="J12" s="132">
+      <c r="J12" s="138">
         <v>65.32</v>
       </c>
-      <c r="K12" s="140">
+      <c r="K12" s="142">
         <v>65.69</v>
       </c>
-      <c r="L12" s="141">
+      <c r="L12" s="139">
         <v>47.53</v>
       </c>
-      <c r="M12" s="133">
+      <c r="M12" s="135">
         <v>34.9</v>
       </c>
-      <c r="N12" s="134">
+      <c r="N12" s="136">
         <v>37.51</v>
       </c>
-      <c r="O12" s="135">
+      <c r="O12" s="140">
         <v>35.45</v>
       </c>
-      <c r="P12" s="136">
+      <c r="P12" s="143">
         <v>35.86</v>
       </c>
       <c r="Q12" s="137">
         <v>29.23</v>
       </c>
-      <c r="R12" s="142">
+      <c r="R12" s="131">
         <v>29.87</v>
       </c>
-      <c r="S12" s="143">
+      <c r="S12" s="132">
         <v>29.96</v>
       </c>
-      <c r="T12" s="139">
+      <c r="T12" s="133">
         <v>14.04</v>
       </c>
     </row>
@@ -8116,7 +8116,7 @@
       <c r="C13" t="str">
         <v>871981</v>
       </c>
-      <c r="D13" s="146" t="str">
+      <c r="D13" s="153" t="str">
         <v>净买: 779.65万</v>
       </c>
       <c r="E13">
@@ -8131,40 +8131,40 @@
       <c r="H13">
         <v>10.55</v>
       </c>
-      <c r="I13" s="147">
+      <c r="I13" s="150">
         <v>17.58</v>
       </c>
-      <c r="J13" s="148">
+      <c r="J13" s="154">
         <v>17.95</v>
       </c>
-      <c r="K13" s="154">
+      <c r="K13" s="155">
         <v>13.64</v>
       </c>
-      <c r="L13" s="149">
+      <c r="L13" s="144">
         <v>14.65</v>
       </c>
-      <c r="M13" s="155">
+      <c r="M13" s="156">
         <v>17.15</v>
       </c>
-      <c r="N13" s="150">
+      <c r="N13" s="151">
         <v>11.72</v>
       </c>
-      <c r="O13" s="156">
+      <c r="O13" s="145">
         <v>6.52</v>
       </c>
-      <c r="P13" s="151">
+      <c r="P13" s="146">
         <v>0.28</v>
       </c>
-      <c r="Q13" s="144">
+      <c r="Q13" s="147">
         <v>1.84</v>
       </c>
-      <c r="R13" s="145">
+      <c r="R13" s="148">
         <v>-1.52</v>
       </c>
       <c r="S13" s="152">
         <v>0.2</v>
       </c>
-      <c r="T13" s="153">
+      <c r="T13" s="149">
         <v>-6.54</v>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       <c r="C14" t="str">
         <v>871981</v>
       </c>
-      <c r="D14" s="164" t="str">
+      <c r="D14" s="160" t="str">
         <v>净卖: -825.29万</v>
       </c>
       <c r="E14">
@@ -8193,28 +8193,28 @@
       <c r="H14">
         <v>7.39</v>
       </c>
-      <c r="I14" s="169">
+      <c r="I14" s="161">
         <v>-6.58</v>
       </c>
-      <c r="J14" s="157">
+      <c r="J14" s="167">
         <v>-10</v>
       </c>
-      <c r="K14" s="161">
+      <c r="K14" s="157">
         <v>-9.2</v>
       </c>
-      <c r="L14" s="167">
+      <c r="L14" s="162">
         <v>-7.22</v>
       </c>
-      <c r="M14" s="162">
+      <c r="M14" s="158">
         <v>-11.52</v>
       </c>
-      <c r="N14" s="158">
+      <c r="N14" s="168">
         <v>-15.64</v>
       </c>
       <c r="O14" s="163">
         <v>-20.58</v>
       </c>
-      <c r="P14" s="168">
+      <c r="P14" s="164">
         <v>-19.34</v>
       </c>
       <c r="Q14" s="165">
@@ -8223,10 +8223,10 @@
       <c r="R14" s="159">
         <v>-20.64</v>
       </c>
-      <c r="S14" s="160">
+      <c r="S14" s="166">
         <v>-21.32</v>
       </c>
-      <c r="T14" s="166">
+      <c r="T14" s="169">
         <v>-25.98</v>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       <c r="C15" t="str">
         <v>301389</v>
       </c>
-      <c r="D15" s="171" t="str">
+      <c r="D15" s="172" t="str">
         <v>净买: 4127.06万</v>
       </c>
       <c r="E15">
@@ -8255,41 +8255,41 @@
       <c r="H15">
         <v>0.95</v>
       </c>
-      <c r="I15" s="181">
+      <c r="I15" s="173">
         <v>18.87</v>
       </c>
-      <c r="J15" s="172">
+      <c r="J15" s="177">
         <v>42.65</v>
       </c>
-      <c r="K15" s="182">
+      <c r="K15" s="170">
         <v>49.96</v>
       </c>
-      <c r="L15" s="177">
+      <c r="L15" s="171">
         <v>46.52</v>
       </c>
-      <c r="M15" s="178">
+      <c r="M15" s="174">
         <v>28.73</v>
       </c>
-      <c r="N15" s="173">
+      <c r="N15" s="178">
         <v>24.55</v>
       </c>
-      <c r="O15" s="174">
+      <c r="O15" s="175">
         <v>17.98</v>
       </c>
-      <c r="P15" s="179">
+      <c r="P15" s="182">
         <v>30.5</v>
       </c>
-      <c r="Q15" s="175">
+      <c r="Q15" s="179">
         <v>23.88</v>
       </c>
-      <c r="R15" s="176">
+      <c r="R15" s="180">
         <v>19.89</v>
       </c>
-      <c r="S15" s="170">
+      <c r="S15" s="181">
         <v>21.91</v>
       </c>
-      <c r="T15" s="180">
-        <v>13.99</v>
+      <c r="T15" s="176">
+        <v>15.94</v>
       </c>
     </row>
     <row r="16">
@@ -8302,7 +8302,7 @@
       <c r="C16" t="str">
         <v>301389</v>
       </c>
-      <c r="D16" s="187" t="str">
+      <c r="D16" s="193" t="str">
         <v>净买: 932.40万</v>
       </c>
       <c r="E16">
@@ -8317,41 +8317,41 @@
       <c r="H16">
         <v>-5.75</v>
       </c>
-      <c r="I16" s="188">
+      <c r="I16" s="183">
         <v>27.33</v>
       </c>
-      <c r="J16" s="189">
+      <c r="J16" s="194">
         <v>33.86</v>
       </c>
-      <c r="K16" s="190">
+      <c r="K16" s="184">
         <v>30.79</v>
       </c>
-      <c r="L16" s="191">
+      <c r="L16" s="187">
         <v>14.91</v>
       </c>
-      <c r="M16" s="184">
+      <c r="M16" s="185">
         <v>11.18</v>
       </c>
-      <c r="N16" s="192">
+      <c r="N16" s="186">
         <v>5.32</v>
       </c>
-      <c r="O16" s="193">
+      <c r="O16" s="188">
         <v>16.49</v>
       </c>
-      <c r="P16" s="185">
+      <c r="P16" s="191">
         <v>10.58</v>
       </c>
-      <c r="Q16" s="186">
+      <c r="Q16" s="195">
         <v>7.02</v>
       </c>
-      <c r="R16" s="194">
+      <c r="R16" s="192">
         <v>8.82</v>
       </c>
-      <c r="S16" s="195">
+      <c r="S16" s="189">
         <v>15.05</v>
       </c>
-      <c r="T16" s="183">
-        <v>1.75</v>
+      <c r="T16" s="190">
+        <v>3.49</v>
       </c>
     </row>
     <row r="17">
@@ -8364,7 +8364,7 @@
       <c r="C17" t="str">
         <v>300450</v>
       </c>
-      <c r="D17" s="202" t="str">
+      <c r="D17" s="201" t="str">
         <v>净卖: -4644.14万</v>
       </c>
       <c r="E17">
@@ -8379,41 +8379,41 @@
       <c r="H17">
         <v>5.71</v>
       </c>
-      <c r="I17" s="203">
+      <c r="I17" s="207">
         <v>13.52</v>
       </c>
-      <c r="J17" s="204">
+      <c r="J17" s="202">
         <v>30.12</v>
       </c>
-      <c r="K17" s="208">
+      <c r="K17" s="196">
         <v>40.03</v>
       </c>
-      <c r="L17" s="196">
+      <c r="L17" s="208">
         <v>40.54</v>
       </c>
-      <c r="M17" s="205">
+      <c r="M17" s="203">
         <v>43.32</v>
       </c>
-      <c r="N17" s="200">
+      <c r="N17" s="199">
         <v>71.99</v>
       </c>
-      <c r="O17" s="197">
+      <c r="O17" s="200">
         <v>83.47</v>
       </c>
-      <c r="P17" s="206">
+      <c r="P17" s="204">
         <v>79.22</v>
       </c>
-      <c r="Q17" s="201">
+      <c r="Q17" s="205">
         <v>87.37</v>
       </c>
-      <c r="R17" s="198">
+      <c r="R17" s="197">
         <v>92.23</v>
       </c>
-      <c r="S17" s="199">
+      <c r="S17" s="198">
         <v>75.19</v>
       </c>
-      <c r="T17" s="207">
-        <v>79.03</v>
+      <c r="T17" s="206">
+        <v>81.27</v>
       </c>
     </row>
     <row r="18">
@@ -8426,7 +8426,7 @@
       <c r="C18" t="str">
         <v>301389</v>
       </c>
-      <c r="D18" s="212" t="str">
+      <c r="D18" s="218" t="str">
         <v>净卖: -3733.12万</v>
       </c>
       <c r="E18">
@@ -8441,28 +8441,28 @@
       <c r="H18">
         <v>2.9</v>
       </c>
-      <c r="I18" s="210">
+      <c r="I18" s="219">
         <v>-5.04</v>
       </c>
-      <c r="J18" s="213">
+      <c r="J18" s="215">
         <v>-16.57</v>
       </c>
-      <c r="K18" s="214">
+      <c r="K18" s="220">
         <v>-19.28</v>
       </c>
-      <c r="L18" s="215">
+      <c r="L18" s="213">
         <v>-23.54</v>
       </c>
-      <c r="M18" s="218">
+      <c r="M18" s="216">
         <v>-15.42</v>
       </c>
-      <c r="N18" s="219">
+      <c r="N18" s="217">
         <v>-19.72</v>
       </c>
-      <c r="O18" s="216">
+      <c r="O18" s="211">
         <v>-22.3</v>
       </c>
-      <c r="P18" s="220">
+      <c r="P18" s="212">
         <v>-20.99</v>
       </c>
       <c r="Q18" s="221">
@@ -8471,11 +8471,11 @@
       <c r="R18" s="209">
         <v>-13.65</v>
       </c>
-      <c r="S18" s="211">
+      <c r="S18" s="210">
         <v>-15.93</v>
       </c>
-      <c r="T18" s="217">
-        <v>-26.12</v>
+      <c r="T18" s="214">
+        <v>-24.86</v>
       </c>
     </row>
     <row r="19">
@@ -8488,7 +8488,7 @@
       <c r="C19" t="str">
         <v>833580</v>
       </c>
-      <c r="D19" s="223" t="str">
+      <c r="D19" s="224" t="str">
         <v>净买: 656.67万</v>
       </c>
       <c r="E19">
@@ -8503,40 +8503,40 @@
       <c r="H19">
         <v>-1.6</v>
       </c>
-      <c r="I19" s="227">
+      <c r="I19" s="228">
         <v>32.07</v>
       </c>
-      <c r="J19" s="234">
+      <c r="J19" s="232">
         <v>19.86</v>
       </c>
-      <c r="K19" s="230">
+      <c r="K19" s="225">
         <v>10.83</v>
       </c>
-      <c r="L19" s="231">
+      <c r="L19" s="229">
         <v>7.1</v>
       </c>
-      <c r="M19" s="224">
+      <c r="M19" s="233">
         <v>12.21</v>
       </c>
-      <c r="N19" s="228">
+      <c r="N19" s="234">
         <v>19.07</v>
       </c>
-      <c r="O19" s="232">
+      <c r="O19" s="222">
         <v>16.13</v>
       </c>
-      <c r="P19" s="225">
+      <c r="P19" s="226">
         <v>10.95</v>
       </c>
-      <c r="Q19" s="222">
+      <c r="Q19" s="227">
         <v>8.72</v>
       </c>
-      <c r="R19" s="233">
+      <c r="R19" s="230">
         <v>8.78</v>
       </c>
-      <c r="S19" s="226">
+      <c r="S19" s="223">
         <v>9.81</v>
       </c>
-      <c r="T19" s="229">
+      <c r="T19" s="231">
         <v>-2.53</v>
       </c>
     </row>
@@ -8565,37 +8565,37 @@
       <c r="H20">
         <v>8.88</v>
       </c>
-      <c r="I20" s="235">
+      <c r="I20" s="239">
         <v>-16.65</v>
       </c>
-      <c r="J20" s="239">
+      <c r="J20" s="245">
         <v>-22.93</v>
       </c>
-      <c r="K20" s="236">
+      <c r="K20" s="240">
         <v>-25.52</v>
       </c>
-      <c r="L20" s="240">
+      <c r="L20" s="247">
         <v>-21.97</v>
       </c>
-      <c r="M20" s="243">
+      <c r="M20" s="241">
         <v>-17.2</v>
       </c>
-      <c r="N20" s="244">
+      <c r="N20" s="235">
         <v>-19.25</v>
       </c>
-      <c r="O20" s="241">
+      <c r="O20" s="242">
         <v>-22.85</v>
       </c>
-      <c r="P20" s="242">
+      <c r="P20" s="243">
         <v>-24.39</v>
       </c>
-      <c r="Q20" s="245">
+      <c r="Q20" s="246">
         <v>-24.35</v>
       </c>
-      <c r="R20" s="246">
+      <c r="R20" s="244">
         <v>-23.64</v>
       </c>
-      <c r="S20" s="247">
+      <c r="S20" s="236">
         <v>-28.45</v>
       </c>
       <c r="T20" s="237">
@@ -8612,7 +8612,7 @@
       <c r="C21" t="str">
         <v>601068</v>
       </c>
-      <c r="D21" s="260" t="str">
+      <c r="D21" s="251" t="str">
         <v>净买: 656.95万</v>
       </c>
       <c r="E21">
@@ -8627,41 +8627,41 @@
       <c r="H21">
         <v>0</v>
       </c>
-      <c r="I21" s="256">
+      <c r="I21" s="255">
         <v>10.02</v>
       </c>
-      <c r="J21" s="257">
+      <c r="J21" s="250">
         <v>5.75</v>
       </c>
-      <c r="K21" s="248">
+      <c r="K21" s="260">
         <v>0.37</v>
       </c>
-      <c r="L21" s="253">
+      <c r="L21" s="256">
         <v>0</v>
       </c>
-      <c r="M21" s="259">
+      <c r="M21" s="252">
         <v>-1.86</v>
       </c>
-      <c r="N21" s="249">
+      <c r="N21" s="253">
         <v>0.19</v>
       </c>
-      <c r="O21" s="250">
+      <c r="O21" s="257">
         <v>0.37</v>
       </c>
-      <c r="P21" s="254">
+      <c r="P21" s="258">
         <v>-1.86</v>
       </c>
-      <c r="Q21" s="251">
+      <c r="Q21" s="248">
         <v>-1.11</v>
       </c>
-      <c r="R21" s="252">
+      <c r="R21" s="254">
         <v>-1.86</v>
       </c>
-      <c r="S21" s="258">
+      <c r="S21" s="259">
         <v>-0.74</v>
       </c>
-      <c r="T21" s="255">
-        <v>16.51</v>
+      <c r="T21" s="249">
+        <v>18.18</v>
       </c>
     </row>
     <row r="22">
@@ -8674,7 +8674,7 @@
       <c r="C22" t="str">
         <v>688146</v>
       </c>
-      <c r="D22" s="272" t="str">
+      <c r="D22" s="267" t="str">
         <v>净买: 1029.87万</v>
       </c>
       <c r="E22">
@@ -8689,41 +8689,41 @@
       <c r="H22">
         <v>-0.49</v>
       </c>
-      <c r="I22" s="262">
+      <c r="I22" s="268">
         <v>16.28</v>
       </c>
-      <c r="J22" s="271">
+      <c r="J22" s="270">
         <v>21.96</v>
       </c>
-      <c r="K22" s="273">
+      <c r="K22" s="271">
         <v>26.12</v>
       </c>
-      <c r="L22" s="266">
+      <c r="L22" s="263">
         <v>18.55</v>
       </c>
-      <c r="M22" s="263">
+      <c r="M22" s="264">
         <v>21.14</v>
       </c>
-      <c r="N22" s="267">
+      <c r="N22" s="272">
         <v>18.6</v>
       </c>
-      <c r="O22" s="268">
+      <c r="O22" s="273">
         <v>17.6</v>
       </c>
-      <c r="P22" s="261">
+      <c r="P22" s="269">
         <v>15.63</v>
       </c>
-      <c r="Q22" s="269">
+      <c r="Q22" s="261">
         <v>18.84</v>
       </c>
-      <c r="R22" s="264">
+      <c r="R22" s="265">
         <v>17.44</v>
       </c>
-      <c r="S22" s="270">
+      <c r="S22" s="262">
         <v>15.25</v>
       </c>
-      <c r="T22" s="265">
-        <v>66.18</v>
+      <c r="T22" s="266">
+        <v>74.6</v>
       </c>
     </row>
     <row r="23">
@@ -8736,7 +8736,7 @@
       <c r="C23" t="str">
         <v>600678</v>
       </c>
-      <c r="D23" s="285" t="str">
+      <c r="D23" s="276" t="str">
         <v>净卖: -1248.78万</v>
       </c>
       <c r="E23">
@@ -8751,41 +8751,41 @@
       <c r="H23">
         <v>-7.51</v>
       </c>
-      <c r="I23" s="278">
+      <c r="I23" s="281">
         <v>-2.71</v>
       </c>
       <c r="J23" s="282">
         <v>-7.69</v>
       </c>
-      <c r="K23" s="279">
+      <c r="K23" s="285">
         <v>-3.85</v>
       </c>
-      <c r="L23" s="283">
+      <c r="L23" s="277">
         <v>-4.99</v>
       </c>
-      <c r="M23" s="280">
+      <c r="M23" s="283">
         <v>-9.33</v>
       </c>
-      <c r="N23" s="274">
+      <c r="N23" s="278">
         <v>-8.05</v>
       </c>
-      <c r="O23" s="275">
+      <c r="O23" s="286">
         <v>-3.7</v>
       </c>
-      <c r="P23" s="276">
+      <c r="P23" s="274">
         <v>-5.98</v>
       </c>
-      <c r="Q23" s="286">
+      <c r="Q23" s="275">
         <v>-8.9</v>
       </c>
-      <c r="R23" s="277">
+      <c r="R23" s="284">
         <v>-4.49</v>
       </c>
-      <c r="S23" s="281">
+      <c r="S23" s="279">
         <v>-2.49</v>
       </c>
-      <c r="T23" s="284">
-        <v>-25.43</v>
+      <c r="T23" s="280">
+        <v>-23.15</v>
       </c>
     </row>
     <row r="24">
@@ -8798,7 +8798,7 @@
       <c r="C24" t="str">
         <v>301449</v>
       </c>
-      <c r="D24" s="291" t="str">
+      <c r="D24" s="288" t="str">
         <v>净卖: -1931.35万</v>
       </c>
       <c r="E24">
@@ -8813,41 +8813,41 @@
       <c r="H24">
         <v>-7.39</v>
       </c>
-      <c r="I24" s="292">
+      <c r="I24" s="289">
         <v>-10.16</v>
       </c>
-      <c r="J24" s="296">
+      <c r="J24" s="298">
         <v>-12.52</v>
       </c>
-      <c r="K24" s="288">
+      <c r="K24" s="294">
         <v>-14.52</v>
       </c>
-      <c r="L24" s="289">
+      <c r="L24" s="295">
         <v>-15.32</v>
       </c>
       <c r="M24" s="290">
         <v>-9.86</v>
       </c>
-      <c r="N24" s="297">
+      <c r="N24" s="299">
         <v>-11.91</v>
       </c>
-      <c r="O24" s="293">
+      <c r="O24" s="287">
         <v>-12.71</v>
       </c>
-      <c r="P24" s="298">
+      <c r="P24" s="291">
         <v>-12.71</v>
       </c>
-      <c r="Q24" s="294">
+      <c r="Q24" s="292">
         <v>-16.26</v>
       </c>
-      <c r="R24" s="299">
+      <c r="R24" s="293">
         <v>-10.13</v>
       </c>
-      <c r="S24" s="287">
+      <c r="S24" s="296">
         <v>-12.25</v>
       </c>
-      <c r="T24" s="295">
-        <v>-17.11</v>
+      <c r="T24" s="297">
+        <v>-16.58</v>
       </c>
     </row>
     <row r="25">
@@ -8860,7 +8860,7 @@
       <c r="C25" t="str">
         <v>688137</v>
       </c>
-      <c r="D25" s="305" t="str">
+      <c r="D25" s="307" t="str">
         <v>净买: 809.16万</v>
       </c>
       <c r="E25">
@@ -8875,41 +8875,41 @@
       <c r="H25">
         <v>-0.09</v>
       </c>
-      <c r="I25" s="306">
+      <c r="I25" s="308">
         <v>15.54</v>
       </c>
-      <c r="J25" s="301">
+      <c r="J25" s="300">
         <v>13.21</v>
       </c>
-      <c r="K25" s="308">
+      <c r="K25" s="309">
         <v>11.95</v>
       </c>
-      <c r="L25" s="302">
+      <c r="L25" s="310">
         <v>9.95</v>
       </c>
-      <c r="M25" s="307">
+      <c r="M25" s="301">
         <v>6.85</v>
       </c>
       <c r="N25" s="303">
         <v>6.78</v>
       </c>
-      <c r="O25" s="309">
+      <c r="O25" s="304">
         <v>13.58</v>
       </c>
-      <c r="P25" s="310">
+      <c r="P25" s="302">
         <v>14.61</v>
       </c>
-      <c r="Q25" s="311">
+      <c r="Q25" s="305">
         <v>16.47</v>
       </c>
-      <c r="R25" s="312">
+      <c r="R25" s="311">
         <v>23.92</v>
       </c>
-      <c r="S25" s="300">
+      <c r="S25" s="306">
         <v>15.3</v>
       </c>
-      <c r="T25" s="304">
-        <v>16.63</v>
+      <c r="T25" s="312">
+        <v>17.17</v>
       </c>
     </row>
     <row r="26">
@@ -8922,7 +8922,7 @@
       <c r="C26" t="str">
         <v>301408</v>
       </c>
-      <c r="D26" s="317" t="str">
+      <c r="D26" s="316" t="str">
         <v>净卖: -2207.20万</v>
       </c>
       <c r="E26">
@@ -8937,41 +8937,41 @@
       <c r="H26">
         <v>1.45</v>
       </c>
-      <c r="I26" s="322">
+      <c r="I26" s="317">
         <v>18.28</v>
       </c>
-      <c r="J26" s="321">
+      <c r="J26" s="318">
         <v>-5.37</v>
       </c>
-      <c r="K26" s="313">
+      <c r="K26" s="321">
         <v>-14.43</v>
       </c>
       <c r="L26" s="323">
         <v>-13.43</v>
       </c>
-      <c r="M26" s="318">
+      <c r="M26" s="319">
         <v>-12.24</v>
       </c>
       <c r="N26" s="314">
         <v>-13.31</v>
       </c>
-      <c r="O26" s="315">
+      <c r="O26" s="324">
         <v>-7.91</v>
       </c>
-      <c r="P26" s="324">
+      <c r="P26" s="322">
         <v>-4.69</v>
       </c>
-      <c r="Q26" s="319">
+      <c r="Q26" s="325">
         <v>-0.32</v>
       </c>
-      <c r="R26" s="325">
+      <c r="R26" s="313">
         <v>-8.55</v>
       </c>
-      <c r="S26" s="320">
+      <c r="S26" s="315">
         <v>-11.88</v>
       </c>
-      <c r="T26" s="316">
-        <v>-19.67</v>
+      <c r="T26" s="320">
+        <v>-17.61</v>
       </c>
     </row>
     <row r="27">
@@ -8984,7 +8984,7 @@
       <c r="C27" t="str">
         <v>603598</v>
       </c>
-      <c r="D27" s="335" t="str">
+      <c r="D27" s="337" t="str">
         <v>净卖: -958.53万</v>
       </c>
       <c r="E27">
@@ -8999,41 +8999,41 @@
       <c r="H27">
         <v>-10.01</v>
       </c>
-      <c r="I27" s="337">
+      <c r="I27" s="329">
         <v>0</v>
       </c>
-      <c r="J27" s="329">
+      <c r="J27" s="338">
         <v>-5.64</v>
       </c>
-      <c r="K27" s="338">
+      <c r="K27" s="326">
         <v>-1.1</v>
       </c>
-      <c r="L27" s="336">
+      <c r="L27" s="330">
         <v>1.88</v>
       </c>
-      <c r="M27" s="330">
+      <c r="M27" s="331">
         <v>4.9</v>
       </c>
-      <c r="N27" s="326">
+      <c r="N27" s="334">
         <v>3.33</v>
       </c>
-      <c r="O27" s="334">
+      <c r="O27" s="335">
         <v>1.33</v>
       </c>
-      <c r="P27" s="331">
+      <c r="P27" s="327">
         <v>-0.86</v>
       </c>
-      <c r="Q27" s="327">
+      <c r="Q27" s="332">
         <v>4.62</v>
       </c>
-      <c r="R27" s="328">
+      <c r="R27" s="336">
         <v>15.09</v>
       </c>
-      <c r="S27" s="332">
+      <c r="S27" s="328">
         <v>13.64</v>
       </c>
       <c r="T27" s="333">
-        <v>-16.81</v>
+        <v>-13.68</v>
       </c>
     </row>
     <row r="28">
@@ -9046,7 +9046,7 @@
       <c r="C28" t="str">
         <v>920368</v>
       </c>
-      <c r="D28" s="341" t="str">
+      <c r="D28" s="340" t="str">
         <v>净买: 2785.37万</v>
       </c>
       <c r="E28">
@@ -9061,41 +9061,41 @@
       <c r="H28">
         <v>6.62</v>
       </c>
-      <c r="I28" s="344">
+      <c r="I28" s="351">
         <v>21.92</v>
       </c>
-      <c r="J28" s="345">
+      <c r="J28" s="343">
         <v>30.07</v>
       </c>
-      <c r="K28" s="351">
+      <c r="K28" s="344">
         <v>52.53</v>
       </c>
-      <c r="L28" s="346">
+      <c r="L28" s="347">
         <v>59.26</v>
       </c>
-      <c r="M28" s="339">
+      <c r="M28" s="348">
         <v>51.53</v>
       </c>
-      <c r="N28" s="347">
+      <c r="N28" s="345">
         <v>48.42</v>
       </c>
-      <c r="O28" s="348">
+      <c r="O28" s="341">
         <v>50.72</v>
       </c>
-      <c r="P28" s="349">
+      <c r="P28" s="346">
         <v>78.13</v>
       </c>
-      <c r="Q28" s="340">
+      <c r="Q28" s="342">
         <v>61.84</v>
       </c>
-      <c r="R28" s="343">
+      <c r="R28" s="339">
         <v>41.93</v>
       </c>
-      <c r="S28" s="350">
+      <c r="S28" s="349">
         <v>52.17</v>
       </c>
-      <c r="T28" s="342">
-        <v>-2.53</v>
+      <c r="T28" s="350">
+        <v>1.6</v>
       </c>
     </row>
     <row r="29">
@@ -9108,7 +9108,7 @@
       <c r="C29" t="str">
         <v>300017</v>
       </c>
-      <c r="D29" s="353" t="str">
+      <c r="D29" s="358" t="str">
         <v>净卖: -8231.84万</v>
       </c>
       <c r="E29">
@@ -9123,41 +9123,41 @@
       <c r="H29">
         <v>1.57</v>
       </c>
-      <c r="I29" s="357">
+      <c r="I29" s="364">
         <v>18.18</v>
       </c>
-      <c r="J29" s="359">
+      <c r="J29" s="362">
         <v>16.12</v>
       </c>
-      <c r="K29" s="360">
+      <c r="K29" s="359">
         <v>33.7</v>
       </c>
-      <c r="L29" s="361">
+      <c r="L29" s="360">
         <v>44.08</v>
       </c>
-      <c r="M29" s="354">
+      <c r="M29" s="352">
         <v>42.02</v>
       </c>
       <c r="N29" s="355">
         <v>44.77</v>
       </c>
-      <c r="O29" s="364">
+      <c r="O29" s="363">
         <v>65.61</v>
       </c>
-      <c r="P29" s="362">
+      <c r="P29" s="356">
         <v>43.4</v>
       </c>
-      <c r="Q29" s="363">
+      <c r="Q29" s="361">
         <v>54.12</v>
       </c>
-      <c r="R29" s="358">
+      <c r="R29" s="357">
         <v>53.77</v>
       </c>
-      <c r="S29" s="356">
+      <c r="S29" s="353">
         <v>62.09</v>
       </c>
-      <c r="T29" s="352">
-        <v>62.09</v>
+      <c r="T29" s="354">
+        <v>60.03</v>
       </c>
     </row>
     <row r="30">
@@ -9170,7 +9170,7 @@
       <c r="C30" t="str">
         <v>603075</v>
       </c>
-      <c r="D30" s="377" t="str">
+      <c r="D30" s="371" t="str">
         <v>净卖: -1295.61万</v>
       </c>
       <c r="E30">
@@ -9185,41 +9185,41 @@
       <c r="H30">
         <v>-0.04</v>
       </c>
-      <c r="I30" s="367">
+      <c r="I30" s="372">
         <v>1.83</v>
       </c>
-      <c r="J30" s="374">
+      <c r="J30" s="365">
         <v>-4.09</v>
       </c>
-      <c r="K30" s="365">
+      <c r="K30" s="368">
         <v>-6.43</v>
       </c>
-      <c r="L30" s="366">
+      <c r="L30" s="377">
         <v>-7.11</v>
       </c>
-      <c r="M30" s="370">
+      <c r="M30" s="373">
         <v>-5.88</v>
       </c>
-      <c r="N30" s="371">
+      <c r="N30" s="366">
         <v>-7.63</v>
       </c>
-      <c r="O30" s="368">
+      <c r="O30" s="369">
         <v>-5.52</v>
       </c>
-      <c r="P30" s="372">
+      <c r="P30" s="374">
         <v>-4.65</v>
       </c>
-      <c r="Q30" s="375">
+      <c r="Q30" s="367">
         <v>-5.2</v>
       </c>
-      <c r="R30" s="376">
+      <c r="R30" s="375">
         <v>-5.72</v>
       </c>
-      <c r="S30" s="373">
+      <c r="S30" s="376">
         <v>-4.92</v>
       </c>
-      <c r="T30" s="369">
-        <v>-9.65</v>
+      <c r="T30" s="370">
+        <v>-8.7</v>
       </c>
     </row>
     <row r="31">
@@ -9232,7 +9232,7 @@
       <c r="C31" t="str">
         <v>920368</v>
       </c>
-      <c r="D31" s="386" t="str">
+      <c r="D31" s="378" t="str">
         <v>净卖: -476.30万</v>
       </c>
       <c r="E31">
@@ -9253,35 +9253,35 @@
       <c r="J31" s="387">
         <v>13.46</v>
       </c>
-      <c r="K31" s="388">
+      <c r="K31" s="383">
         <v>18.46</v>
       </c>
-      <c r="L31" s="378">
+      <c r="L31" s="384">
         <v>12.71</v>
       </c>
-      <c r="M31" s="389">
+      <c r="M31" s="379">
         <v>10.4</v>
       </c>
-      <c r="N31" s="383">
+      <c r="N31" s="388">
         <v>12.12</v>
       </c>
-      <c r="O31" s="379">
+      <c r="O31" s="385">
         <v>32.5</v>
       </c>
-      <c r="P31" s="384">
+      <c r="P31" s="386">
         <v>20.38</v>
       </c>
-      <c r="Q31" s="390">
+      <c r="Q31" s="380">
         <v>5.58</v>
       </c>
-      <c r="R31" s="385">
+      <c r="R31" s="389">
         <v>13.19</v>
       </c>
-      <c r="S31" s="380">
+      <c r="S31" s="381">
         <v>23.15</v>
       </c>
-      <c r="T31" s="381">
-        <v>-27.5</v>
+      <c r="T31" s="390">
+        <v>-24.42</v>
       </c>
     </row>
     <row r="32">
@@ -9309,41 +9309,41 @@
       <c r="H32">
         <v>3.89</v>
       </c>
-      <c r="I32" s="393">
+      <c r="I32" s="395">
         <v>5.92</v>
       </c>
       <c r="J32" s="396">
         <v>2.96</v>
       </c>
-      <c r="K32" s="401">
+      <c r="K32" s="397">
         <v>-4.88</v>
       </c>
-      <c r="L32" s="394">
+      <c r="L32" s="401">
         <v>-3.05</v>
       </c>
-      <c r="M32" s="397">
+      <c r="M32" s="398">
         <v>-1.31</v>
       </c>
-      <c r="N32" s="391">
+      <c r="N32" s="402">
         <v>-4.18</v>
       </c>
-      <c r="O32" s="398">
+      <c r="O32" s="403">
         <v>-1.74</v>
       </c>
-      <c r="P32" s="399">
+      <c r="P32" s="391">
         <v>-1.66</v>
       </c>
-      <c r="Q32" s="395">
+      <c r="Q32" s="399">
         <v>0.78</v>
       </c>
-      <c r="R32" s="402">
+      <c r="R32" s="400">
         <v>1.83</v>
       </c>
-      <c r="S32" s="400">
+      <c r="S32" s="393">
         <v>2.7</v>
       </c>
-      <c r="T32" s="403">
-        <v>-21.25</v>
+      <c r="T32" s="394">
+        <v>-22.39</v>
       </c>
     </row>
     <row r="33">
@@ -9356,7 +9356,7 @@
       <c r="C33" t="str">
         <v>300257</v>
       </c>
-      <c r="D33" s="413" t="str">
+      <c r="D33" s="414" t="str">
         <v>净卖: -2507.66万</v>
       </c>
       <c r="E33">
@@ -9371,41 +9371,41 @@
       <c r="H33">
         <v>2.76</v>
       </c>
-      <c r="I33" s="416">
+      <c r="I33" s="415">
         <v>16.77</v>
       </c>
-      <c r="J33" s="412">
+      <c r="J33" s="416">
         <v>17.59</v>
       </c>
-      <c r="K33" s="414">
+      <c r="K33" s="410">
         <v>16.46</v>
       </c>
-      <c r="L33" s="407">
+      <c r="L33" s="411">
         <v>7.35</v>
       </c>
       <c r="M33" s="404">
         <v>14.56</v>
       </c>
-      <c r="N33" s="415">
+      <c r="N33" s="405">
         <v>8.23</v>
       </c>
-      <c r="O33" s="408">
+      <c r="O33" s="413">
         <v>8.64</v>
       </c>
-      <c r="P33" s="405">
+      <c r="P33" s="406">
         <v>8.67</v>
       </c>
-      <c r="Q33" s="409">
+      <c r="Q33" s="407">
         <v>5.17</v>
       </c>
-      <c r="R33" s="406">
+      <c r="R33" s="412">
         <v>1.33</v>
       </c>
-      <c r="S33" s="410">
+      <c r="S33" s="408">
         <v>1.8</v>
       </c>
-      <c r="T33" s="411">
-        <v>-0.07</v>
+      <c r="T33" s="409">
+        <v>-0.44</v>
       </c>
     </row>
     <row r="34">
@@ -9467,25 +9467,25 @@
       <c r="F35" t="str"/>
       <c r="G35" t="str"/>
       <c r="H35" t="str"/>
-      <c r="I35" s="418">
+      <c r="I35" s="423">
         <v>68.75</v>
       </c>
-      <c r="J35" s="419">
+      <c r="J35" s="424">
         <v>71.88</v>
       </c>
-      <c r="K35" s="420">
+      <c r="K35" s="419">
         <v>68.75</v>
       </c>
-      <c r="L35" s="424">
+      <c r="L35" s="420">
         <v>68.75</v>
       </c>
       <c r="M35" s="421">
         <v>68.75</v>
       </c>
-      <c r="N35" s="422">
+      <c r="N35" s="425">
         <v>71.88</v>
       </c>
-      <c r="O35" s="425">
+      <c r="O35" s="417">
         <v>71.88</v>
       </c>
       <c r="P35" s="426">
@@ -9497,11 +9497,11 @@
       <c r="R35" s="428">
         <v>62.5</v>
       </c>
-      <c r="S35" s="423">
+      <c r="S35" s="422">
         <v>65.63</v>
       </c>
-      <c r="T35" s="417">
-        <v>34.38</v>
+      <c r="T35" s="418">
+        <v>37.5</v>
       </c>
     </row>
     <row r="36">
@@ -9515,41 +9515,41 @@
       <c r="F36" t="str"/>
       <c r="G36" t="str"/>
       <c r="H36" t="str"/>
-      <c r="I36" s="439">
+      <c r="I36" s="436">
         <v>8.56</v>
       </c>
-      <c r="J36" s="435">
+      <c r="J36" s="437">
         <v>10.13</v>
       </c>
-      <c r="K36" s="429">
+      <c r="K36" s="438">
         <v>11.47</v>
       </c>
-      <c r="L36" s="430">
+      <c r="L36" s="432">
         <v>10.84</v>
       </c>
-      <c r="M36" s="436">
+      <c r="M36" s="430">
         <v>11.29</v>
       </c>
-      <c r="N36" s="431">
+      <c r="N36" s="439">
         <v>10.99</v>
       </c>
-      <c r="O36" s="432">
+      <c r="O36" s="433">
         <v>12.53</v>
       </c>
-      <c r="P36" s="433">
+      <c r="P36" s="440">
         <v>11.98</v>
       </c>
       <c r="Q36" s="434">
         <v>10.83</v>
       </c>
-      <c r="R36" s="437">
+      <c r="R36" s="431">
         <v>10.67</v>
       </c>
-      <c r="S36" s="438">
+      <c r="S36" s="435">
         <v>10.08</v>
       </c>
-      <c r="T36" s="440">
-        <v>3.14</v>
+      <c r="T36" s="429">
+        <v>4.02</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/大小说家/index.xlsx
+++ b/youzi/大小说家/index.xlsx
@@ -39,12 +39,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFEA8A93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1E8337"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFEAF6ED"/>
         <bgColor/>
       </patternFill>
@@ -57,6 +81,54 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46370"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7ECA90"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -69,43 +141,283 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7ECA90"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46370"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8A93"/>
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9EA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4352"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -117,13 +429,223 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B25E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEFF0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBE3C4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CDD1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB9199"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8E1C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2736"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -135,6 +657,96 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91D2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -147,7 +759,217 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15663"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF3F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDE4C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -159,6 +981,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -171,187 +1005,1483 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91D2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBD5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF59BB6F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8336"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD75"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7833"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3DAF57"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF35AC50"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBD6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAEFDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3948"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4453"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF82CB93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF37AD52"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB766"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF73C586"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB4E0BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7E1C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8790"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7BC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD23040"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9EA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4352"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
+        <fgColor rgb="FF2DA949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4BB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -363,2107 +2493,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B25E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEFF0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBE3C4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB9199"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CDD1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8E1C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91D2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15663"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF3F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDE4C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91D2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFEBD5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEB9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEB9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEB9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7833"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8336"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3DAF57"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF59BB6F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD75"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF35AC50"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFEBD6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAEFDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3948"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4453"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BEC3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB766"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF37AD52"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF73C586"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8790"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2DA949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7BC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4BB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB4E0BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2475,73 +2529,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFB52331"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2553,6 +2553,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFAD202D"/>
         <bgColor/>
       </patternFill>
@@ -2565,43 +2577,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFBE2735"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -7434,7 +7434,7 @@
       <c r="C2" t="str">
         <v>603319</v>
       </c>
-      <c r="D2" s="5" t="str">
+      <c r="D2" s="3" t="str">
         <v>净卖: -4050.11万</v>
       </c>
       <c r="E2">
@@ -7449,41 +7449,41 @@
       <c r="H2">
         <v>-2.13</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2" s="4">
         <v>-8.04</v>
       </c>
-      <c r="J2" s="6">
+      <c r="J2" s="5">
         <v>-7</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2" s="6">
         <v>-0.47</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" s="7">
         <v>3.68</v>
       </c>
-      <c r="M2" s="9">
+      <c r="M2" s="8">
         <v>10.89</v>
       </c>
       <c r="N2" s="10">
         <v>3.84</v>
       </c>
-      <c r="O2" s="7">
+      <c r="O2" s="11">
         <v>6.4</v>
       </c>
-      <c r="P2" s="11">
+      <c r="P2" s="12">
         <v>7.52</v>
       </c>
-      <c r="Q2" s="8">
+      <c r="Q2" s="13">
         <v>-2.98</v>
       </c>
-      <c r="R2" s="12">
+      <c r="R2" s="1">
         <v>2.88</v>
       </c>
-      <c r="S2" s="13">
+      <c r="S2" s="9">
         <v>6.19</v>
       </c>
-      <c r="T2" s="4">
-        <v>-12.05</v>
+      <c r="T2" s="2">
+        <v>-7.08</v>
       </c>
     </row>
     <row r="3">
@@ -7496,7 +7496,7 @@
       <c r="C3" t="str">
         <v>002923</v>
       </c>
-      <c r="D3" s="18" t="str">
+      <c r="D3" s="17" t="str">
         <v>净卖: -1342.21万</v>
       </c>
       <c r="E3">
@@ -7511,41 +7511,41 @@
       <c r="H3">
         <v>2.17</v>
       </c>
-      <c r="I3" s="19">
+      <c r="I3" s="18">
         <v>7.69</v>
       </c>
-      <c r="J3" s="24">
+      <c r="J3" s="19">
         <v>17.63</v>
       </c>
-      <c r="K3" s="23">
+      <c r="K3" s="15">
         <v>5.88</v>
       </c>
-      <c r="L3" s="15">
+      <c r="L3" s="14">
         <v>-4.3</v>
       </c>
-      <c r="M3" s="16">
+      <c r="M3" s="25">
         <v>-13.87</v>
       </c>
-      <c r="N3" s="20">
+      <c r="N3" s="26">
         <v>-11.45</v>
       </c>
-      <c r="O3" s="25">
+      <c r="O3" s="20">
         <v>-15.08</v>
       </c>
-      <c r="P3" s="17">
+      <c r="P3" s="21">
         <v>-14.66</v>
       </c>
-      <c r="Q3" s="26">
+      <c r="Q3" s="22">
         <v>-12.84</v>
       </c>
-      <c r="R3" s="21">
+      <c r="R3" s="23">
         <v>-21.56</v>
       </c>
-      <c r="S3" s="22">
+      <c r="S3" s="16">
         <v>-24.59</v>
       </c>
-      <c r="T3" s="14">
-        <v>-24.29</v>
+      <c r="T3" s="24">
+        <v>-25.5</v>
       </c>
     </row>
     <row r="4">
@@ -7558,7 +7558,7 @@
       <c r="C4" t="str">
         <v>002564</v>
       </c>
-      <c r="D4" s="37" t="str">
+      <c r="D4" s="38" t="str">
         <v>净买: 1737.48万</v>
       </c>
       <c r="E4">
@@ -7573,41 +7573,41 @@
       <c r="H4">
         <v>-1.38</v>
       </c>
-      <c r="I4" s="31">
+      <c r="I4" s="39">
         <v>11.55</v>
       </c>
-      <c r="J4" s="39">
+      <c r="J4" s="29">
         <v>2.39</v>
       </c>
-      <c r="K4" s="35">
+      <c r="K4" s="31">
         <v>12.55</v>
       </c>
-      <c r="L4" s="27">
+      <c r="L4" s="36">
         <v>5.58</v>
       </c>
-      <c r="M4" s="36">
+      <c r="M4" s="32">
         <v>16.14</v>
       </c>
-      <c r="N4" s="32">
+      <c r="N4" s="37">
         <v>21.51</v>
       </c>
       <c r="O4" s="33">
         <v>16.14</v>
       </c>
-      <c r="P4" s="28">
+      <c r="P4" s="30">
         <v>19.92</v>
       </c>
-      <c r="Q4" s="29">
+      <c r="Q4" s="34">
         <v>20.72</v>
       </c>
-      <c r="R4" s="30">
+      <c r="R4" s="27">
         <v>15.94</v>
       </c>
-      <c r="S4" s="34">
+      <c r="S4" s="28">
         <v>8.96</v>
       </c>
-      <c r="T4" s="38">
-        <v>24.5</v>
+      <c r="T4" s="35">
+        <v>22.51</v>
       </c>
     </row>
     <row r="5">
@@ -7620,7 +7620,7 @@
       <c r="C5" t="str">
         <v>600735</v>
       </c>
-      <c r="D5" s="51" t="str">
+      <c r="D5" s="46" t="str">
         <v>净买: 1155.67万</v>
       </c>
       <c r="E5">
@@ -7635,40 +7635,40 @@
       <c r="H5">
         <v>1.24</v>
       </c>
-      <c r="I5" s="52">
+      <c r="I5" s="42">
         <v>8.71</v>
       </c>
-      <c r="J5" s="45">
+      <c r="J5" s="47">
         <v>8.84</v>
       </c>
-      <c r="K5" s="48">
+      <c r="K5" s="50">
         <v>7.48</v>
       </c>
-      <c r="L5" s="46">
+      <c r="L5" s="43">
         <v>4.63</v>
       </c>
-      <c r="M5" s="49">
+      <c r="M5" s="44">
         <v>5.71</v>
       </c>
-      <c r="N5" s="40">
+      <c r="N5" s="52">
         <v>11.16</v>
       </c>
-      <c r="O5" s="47">
+      <c r="O5" s="51">
         <v>9.66</v>
       </c>
-      <c r="P5" s="41">
+      <c r="P5" s="48">
         <v>6.8</v>
       </c>
-      <c r="Q5" s="42">
+      <c r="Q5" s="49">
         <v>12.24</v>
       </c>
-      <c r="R5" s="50">
+      <c r="R5" s="40">
         <v>13.88</v>
       </c>
-      <c r="S5" s="43">
+      <c r="S5" s="41">
         <v>10.07</v>
       </c>
-      <c r="T5" s="44">
+      <c r="T5" s="45">
         <v>-8.44</v>
       </c>
     </row>
@@ -7682,7 +7682,7 @@
       <c r="C6" t="str">
         <v>600735</v>
       </c>
-      <c r="D6" s="57" t="str">
+      <c r="D6" s="55" t="str">
         <v>净卖: -1139.95万</v>
       </c>
       <c r="E6">
@@ -7697,37 +7697,37 @@
       <c r="H6">
         <v>-5.01</v>
       </c>
-      <c r="I6" s="58">
+      <c r="I6" s="61">
         <v>5.4</v>
       </c>
-      <c r="J6" s="53">
+      <c r="J6" s="56">
         <v>4.08</v>
       </c>
-      <c r="K6" s="54">
+      <c r="K6" s="59">
         <v>1.32</v>
       </c>
-      <c r="L6" s="64">
+      <c r="L6" s="57">
         <v>2.37</v>
       </c>
-      <c r="M6" s="59">
+      <c r="M6" s="64">
         <v>7.64</v>
       </c>
-      <c r="N6" s="60">
+      <c r="N6" s="65">
         <v>6.19</v>
       </c>
-      <c r="O6" s="55">
+      <c r="O6" s="53">
         <v>3.43</v>
       </c>
-      <c r="P6" s="61">
+      <c r="P6" s="54">
         <v>8.7</v>
       </c>
-      <c r="Q6" s="65">
+      <c r="Q6" s="62">
         <v>10.28</v>
       </c>
-      <c r="R6" s="56">
+      <c r="R6" s="60">
         <v>6.59</v>
       </c>
-      <c r="S6" s="62">
+      <c r="S6" s="58">
         <v>3.43</v>
       </c>
       <c r="T6" s="63">
@@ -7744,7 +7744,7 @@
       <c r="C7" t="str">
         <v>002365</v>
       </c>
-      <c r="D7" s="78" t="str">
+      <c r="D7" s="67" t="str">
         <v>净卖: -2887.03万</v>
       </c>
       <c r="E7">
@@ -7759,41 +7759,41 @@
       <c r="H7">
         <v>3.76</v>
       </c>
-      <c r="I7" s="73">
+      <c r="I7" s="68">
         <v>-4.32</v>
       </c>
-      <c r="J7" s="69">
+      <c r="J7" s="78">
         <v>5.25</v>
       </c>
-      <c r="K7" s="74">
+      <c r="K7" s="75">
         <v>15.76</v>
       </c>
-      <c r="L7" s="66">
+      <c r="L7" s="76">
         <v>27.33</v>
       </c>
-      <c r="M7" s="70">
+      <c r="M7" s="69">
         <v>35.58</v>
       </c>
-      <c r="N7" s="75">
+      <c r="N7" s="70">
         <v>40.03</v>
       </c>
-      <c r="O7" s="67">
+      <c r="O7" s="73">
         <v>54.03</v>
       </c>
-      <c r="P7" s="76">
+      <c r="P7" s="74">
         <v>38.65</v>
       </c>
-      <c r="Q7" s="68">
+      <c r="Q7" s="66">
         <v>24.77</v>
       </c>
-      <c r="R7" s="71">
+      <c r="R7" s="77">
         <v>28.27</v>
       </c>
-      <c r="S7" s="77">
+      <c r="S7" s="71">
         <v>22.51</v>
       </c>
       <c r="T7" s="72">
-        <v>-14.45</v>
+        <v>-15.82</v>
       </c>
     </row>
     <row r="8">
@@ -7806,7 +7806,7 @@
       <c r="C8" t="str">
         <v>603585</v>
       </c>
-      <c r="D8" s="81" t="str">
+      <c r="D8" s="80" t="str">
         <v>净买: 590.46万</v>
       </c>
       <c r="E8">
@@ -7821,16 +7821,16 @@
       <c r="H8">
         <v>-2.32</v>
       </c>
-      <c r="I8" s="82">
+      <c r="I8" s="81">
         <v>8.09</v>
       </c>
-      <c r="J8" s="88">
+      <c r="J8" s="82">
         <v>7.12</v>
       </c>
-      <c r="K8" s="83">
+      <c r="K8" s="85">
         <v>17.86</v>
       </c>
-      <c r="L8" s="89">
+      <c r="L8" s="83">
         <v>29.63</v>
       </c>
       <c r="M8" s="90">
@@ -7839,23 +7839,23 @@
       <c r="N8" s="84">
         <v>5.02</v>
       </c>
-      <c r="O8" s="79">
+      <c r="O8" s="86">
         <v>0.38</v>
       </c>
-      <c r="P8" s="91">
+      <c r="P8" s="87">
         <v>2.75</v>
       </c>
-      <c r="Q8" s="86">
+      <c r="Q8" s="91">
         <v>2.05</v>
       </c>
-      <c r="R8" s="87">
+      <c r="R8" s="79">
         <v>-0.32</v>
       </c>
-      <c r="S8" s="85">
+      <c r="S8" s="88">
         <v>-1.57</v>
       </c>
-      <c r="T8" s="80">
-        <v>27.31</v>
+      <c r="T8" s="89">
+        <v>25.9</v>
       </c>
     </row>
     <row r="9">
@@ -7868,7 +7868,7 @@
       <c r="C9" t="str">
         <v>003029</v>
       </c>
-      <c r="D9" s="92" t="str">
+      <c r="D9" s="100" t="str">
         <v>净卖: -1441.18万</v>
       </c>
       <c r="E9">
@@ -7883,41 +7883,41 @@
       <c r="H9">
         <v>0.04</v>
       </c>
-      <c r="I9" s="98">
+      <c r="I9" s="96">
         <v>9.96</v>
       </c>
-      <c r="J9" s="95">
+      <c r="J9" s="92">
         <v>14.48</v>
       </c>
-      <c r="K9" s="99">
+      <c r="K9" s="97">
         <v>8.49</v>
       </c>
-      <c r="L9" s="93">
+      <c r="L9" s="101">
         <v>8.99</v>
       </c>
-      <c r="M9" s="96">
+      <c r="M9" s="102">
         <v>7.77</v>
       </c>
-      <c r="N9" s="100">
+      <c r="N9" s="98">
         <v>2.72</v>
       </c>
-      <c r="O9" s="103">
+      <c r="O9" s="93">
         <v>1.22</v>
       </c>
-      <c r="P9" s="101">
+      <c r="P9" s="94">
         <v>-1.33</v>
       </c>
-      <c r="Q9" s="104">
+      <c r="Q9" s="99">
         <v>-1.65</v>
       </c>
-      <c r="R9" s="97">
+      <c r="R9" s="95">
         <v>-1.04</v>
       </c>
-      <c r="S9" s="94">
+      <c r="S9" s="104">
         <v>-2.01</v>
       </c>
-      <c r="T9" s="102">
-        <v>-22.72</v>
+      <c r="T9" s="103">
+        <v>-24.79</v>
       </c>
     </row>
     <row r="10">
@@ -7945,41 +7945,41 @@
       <c r="H10">
         <v>1.79</v>
       </c>
-      <c r="I10" s="109">
+      <c r="I10" s="106">
         <v>17.9</v>
       </c>
-      <c r="J10" s="112">
+      <c r="J10" s="115">
         <v>21.2</v>
       </c>
-      <c r="K10" s="106">
+      <c r="K10" s="116">
         <v>12.29</v>
       </c>
-      <c r="L10" s="115">
+      <c r="L10" s="107">
         <v>14.55</v>
       </c>
-      <c r="M10" s="116">
+      <c r="M10" s="105">
         <v>21.65</v>
       </c>
-      <c r="N10" s="110">
+      <c r="N10" s="111">
         <v>15.36</v>
       </c>
-      <c r="O10" s="113">
+      <c r="O10" s="108">
         <v>9.81</v>
       </c>
-      <c r="P10" s="107">
+      <c r="P10" s="117">
         <v>10.06</v>
       </c>
-      <c r="Q10" s="117">
+      <c r="Q10" s="112">
         <v>17.68</v>
       </c>
-      <c r="R10" s="111">
+      <c r="R10" s="109">
         <v>24.45</v>
       </c>
-      <c r="S10" s="108">
+      <c r="S10" s="113">
         <v>20.16</v>
       </c>
-      <c r="T10" s="105">
-        <v>123.33</v>
+      <c r="T10" s="110">
+        <v>167.99</v>
       </c>
     </row>
     <row r="11">
@@ -7992,7 +7992,7 @@
       <c r="C11" t="str">
         <v>002052</v>
       </c>
-      <c r="D11" s="124" t="str">
+      <c r="D11" s="120" t="str">
         <v>净卖: -1505.16万</v>
       </c>
       <c r="E11">
@@ -8007,41 +8007,41 @@
       <c r="H11">
         <v>10.03</v>
       </c>
-      <c r="I11" s="130">
+      <c r="I11" s="125">
         <v>0</v>
       </c>
-      <c r="J11" s="121">
+      <c r="J11" s="127">
         <v>4.18</v>
       </c>
-      <c r="K11" s="122">
+      <c r="K11" s="121">
         <v>14.59</v>
       </c>
-      <c r="L11" s="127">
+      <c r="L11" s="128">
         <v>26.06</v>
       </c>
-      <c r="M11" s="118">
+      <c r="M11" s="122">
         <v>38.68</v>
       </c>
-      <c r="N11" s="128">
+      <c r="N11" s="123">
         <v>44.38</v>
       </c>
-      <c r="O11" s="119">
+      <c r="O11" s="129">
         <v>45.82</v>
       </c>
-      <c r="P11" s="125">
+      <c r="P11" s="118">
         <v>53.88</v>
       </c>
-      <c r="Q11" s="126">
+      <c r="Q11" s="130">
         <v>45.36</v>
       </c>
-      <c r="R11" s="123">
+      <c r="R11" s="124">
         <v>34.42</v>
       </c>
-      <c r="S11" s="129">
+      <c r="S11" s="126">
         <v>39.06</v>
       </c>
-      <c r="T11" s="120">
-        <v>-20.52</v>
+      <c r="T11" s="119">
+        <v>-22.64</v>
       </c>
     </row>
     <row r="12">
@@ -8054,7 +8054,7 @@
       <c r="C12" t="str">
         <v>430476</v>
       </c>
-      <c r="D12" s="141" t="str">
+      <c r="D12" s="135" t="str">
         <v>净买: 566.61万</v>
       </c>
       <c r="E12">
@@ -8069,40 +8069,40 @@
       <c r="H12">
         <v>2.2</v>
       </c>
-      <c r="I12" s="134">
+      <c r="I12" s="132">
         <v>27.17</v>
       </c>
-      <c r="J12" s="138">
+      <c r="J12" s="136">
         <v>65.32</v>
       </c>
-      <c r="K12" s="142">
+      <c r="K12" s="133">
         <v>65.69</v>
       </c>
-      <c r="L12" s="139">
+      <c r="L12" s="137">
         <v>47.53</v>
       </c>
-      <c r="M12" s="135">
+      <c r="M12" s="140">
         <v>34.9</v>
       </c>
-      <c r="N12" s="136">
+      <c r="N12" s="141">
         <v>37.51</v>
       </c>
-      <c r="O12" s="140">
+      <c r="O12" s="138">
         <v>35.45</v>
       </c>
-      <c r="P12" s="143">
+      <c r="P12" s="134">
         <v>35.86</v>
       </c>
-      <c r="Q12" s="137">
+      <c r="Q12" s="139">
         <v>29.23</v>
       </c>
       <c r="R12" s="131">
         <v>29.87</v>
       </c>
-      <c r="S12" s="132">
+      <c r="S12" s="142">
         <v>29.96</v>
       </c>
-      <c r="T12" s="133">
+      <c r="T12" s="143">
         <v>14.04</v>
       </c>
     </row>
@@ -8116,7 +8116,7 @@
       <c r="C13" t="str">
         <v>871981</v>
       </c>
-      <c r="D13" s="153" t="str">
+      <c r="D13" s="148" t="str">
         <v>净买: 779.65万</v>
       </c>
       <c r="E13">
@@ -8131,40 +8131,40 @@
       <c r="H13">
         <v>10.55</v>
       </c>
-      <c r="I13" s="150">
+      <c r="I13" s="149">
         <v>17.58</v>
       </c>
-      <c r="J13" s="154">
+      <c r="J13" s="155">
         <v>17.95</v>
       </c>
-      <c r="K13" s="155">
+      <c r="K13" s="146">
         <v>13.64</v>
       </c>
-      <c r="L13" s="144">
+      <c r="L13" s="150">
         <v>14.65</v>
       </c>
       <c r="M13" s="156">
         <v>17.15</v>
       </c>
-      <c r="N13" s="151">
+      <c r="N13" s="144">
         <v>11.72</v>
       </c>
-      <c r="O13" s="145">
+      <c r="O13" s="153">
         <v>6.52</v>
       </c>
-      <c r="P13" s="146">
+      <c r="P13" s="145">
         <v>0.28</v>
       </c>
-      <c r="Q13" s="147">
+      <c r="Q13" s="154">
         <v>1.84</v>
       </c>
-      <c r="R13" s="148">
+      <c r="R13" s="147">
         <v>-1.52</v>
       </c>
-      <c r="S13" s="152">
+      <c r="S13" s="151">
         <v>0.2</v>
       </c>
-      <c r="T13" s="149">
+      <c r="T13" s="152">
         <v>-6.54</v>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       <c r="C14" t="str">
         <v>871981</v>
       </c>
-      <c r="D14" s="160" t="str">
+      <c r="D14" s="158" t="str">
         <v>净卖: -825.29万</v>
       </c>
       <c r="E14">
@@ -8193,40 +8193,40 @@
       <c r="H14">
         <v>7.39</v>
       </c>
-      <c r="I14" s="161">
+      <c r="I14" s="168">
         <v>-6.58</v>
       </c>
-      <c r="J14" s="167">
+      <c r="J14" s="162">
         <v>-10</v>
       </c>
-      <c r="K14" s="157">
+      <c r="K14" s="159">
         <v>-9.2</v>
       </c>
-      <c r="L14" s="162">
+      <c r="L14" s="164">
         <v>-7.22</v>
       </c>
-      <c r="M14" s="158">
+      <c r="M14" s="160">
         <v>-11.52</v>
       </c>
-      <c r="N14" s="168">
+      <c r="N14" s="169">
         <v>-15.64</v>
       </c>
       <c r="O14" s="163">
         <v>-20.58</v>
       </c>
-      <c r="P14" s="164">
+      <c r="P14" s="165">
         <v>-19.34</v>
       </c>
-      <c r="Q14" s="165">
+      <c r="Q14" s="166">
         <v>-22</v>
       </c>
-      <c r="R14" s="159">
+      <c r="R14" s="161">
         <v>-20.64</v>
       </c>
-      <c r="S14" s="166">
+      <c r="S14" s="167">
         <v>-21.32</v>
       </c>
-      <c r="T14" s="169">
+      <c r="T14" s="157">
         <v>-25.98</v>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       <c r="C15" t="str">
         <v>301389</v>
       </c>
-      <c r="D15" s="172" t="str">
+      <c r="D15" s="181" t="str">
         <v>净买: 4127.06万</v>
       </c>
       <c r="E15">
@@ -8255,41 +8255,41 @@
       <c r="H15">
         <v>0.95</v>
       </c>
-      <c r="I15" s="173">
+      <c r="I15" s="178">
         <v>18.87</v>
       </c>
-      <c r="J15" s="177">
+      <c r="J15" s="172">
         <v>42.65</v>
       </c>
-      <c r="K15" s="170">
+      <c r="K15" s="175">
         <v>49.96</v>
       </c>
-      <c r="L15" s="171">
+      <c r="L15" s="176">
         <v>46.52</v>
       </c>
-      <c r="M15" s="174">
+      <c r="M15" s="182">
         <v>28.73</v>
       </c>
-      <c r="N15" s="178">
+      <c r="N15" s="179">
         <v>24.55</v>
       </c>
-      <c r="O15" s="175">
+      <c r="O15" s="173">
         <v>17.98</v>
       </c>
-      <c r="P15" s="182">
+      <c r="P15" s="177">
         <v>30.5</v>
       </c>
-      <c r="Q15" s="179">
+      <c r="Q15" s="180">
         <v>23.88</v>
       </c>
-      <c r="R15" s="180">
+      <c r="R15" s="170">
         <v>19.89</v>
       </c>
-      <c r="S15" s="181">
+      <c r="S15" s="171">
         <v>21.91</v>
       </c>
-      <c r="T15" s="176">
-        <v>15.94</v>
+      <c r="T15" s="174">
+        <v>23.41</v>
       </c>
     </row>
     <row r="16">
@@ -8302,7 +8302,7 @@
       <c r="C16" t="str">
         <v>301389</v>
       </c>
-      <c r="D16" s="193" t="str">
+      <c r="D16" s="183" t="str">
         <v>净买: 932.40万</v>
       </c>
       <c r="E16">
@@ -8317,41 +8317,41 @@
       <c r="H16">
         <v>-5.75</v>
       </c>
-      <c r="I16" s="183">
+      <c r="I16" s="184">
         <v>27.33</v>
       </c>
-      <c r="J16" s="194">
+      <c r="J16" s="185">
         <v>33.86</v>
       </c>
-      <c r="K16" s="184">
+      <c r="K16" s="194">
         <v>30.79</v>
       </c>
-      <c r="L16" s="187">
+      <c r="L16" s="189">
         <v>14.91</v>
       </c>
-      <c r="M16" s="185">
+      <c r="M16" s="186">
         <v>11.18</v>
       </c>
-      <c r="N16" s="186">
+      <c r="N16" s="192">
         <v>5.32</v>
       </c>
-      <c r="O16" s="188">
+      <c r="O16" s="187">
         <v>16.49</v>
       </c>
-      <c r="P16" s="191">
+      <c r="P16" s="193">
         <v>10.58</v>
       </c>
-      <c r="Q16" s="195">
+      <c r="Q16" s="190">
         <v>7.02</v>
       </c>
-      <c r="R16" s="192">
+      <c r="R16" s="188">
         <v>8.82</v>
       </c>
-      <c r="S16" s="189">
+      <c r="S16" s="191">
         <v>15.05</v>
       </c>
-      <c r="T16" s="190">
-        <v>3.49</v>
+      <c r="T16" s="195">
+        <v>10.16</v>
       </c>
     </row>
     <row r="17">
@@ -8364,7 +8364,7 @@
       <c r="C17" t="str">
         <v>300450</v>
       </c>
-      <c r="D17" s="201" t="str">
+      <c r="D17" s="202" t="str">
         <v>净卖: -4644.14万</v>
       </c>
       <c r="E17">
@@ -8379,41 +8379,41 @@
       <c r="H17">
         <v>5.71</v>
       </c>
-      <c r="I17" s="207">
+      <c r="I17" s="196">
         <v>13.52</v>
       </c>
-      <c r="J17" s="202">
+      <c r="J17" s="203">
         <v>30.12</v>
       </c>
-      <c r="K17" s="196">
+      <c r="K17" s="204">
         <v>40.03</v>
       </c>
-      <c r="L17" s="208">
+      <c r="L17" s="197">
         <v>40.54</v>
       </c>
-      <c r="M17" s="203">
+      <c r="M17" s="206">
         <v>43.32</v>
       </c>
-      <c r="N17" s="199">
+      <c r="N17" s="198">
         <v>71.99</v>
       </c>
-      <c r="O17" s="200">
+      <c r="O17" s="199">
         <v>83.47</v>
       </c>
-      <c r="P17" s="204">
+      <c r="P17" s="207">
         <v>79.22</v>
       </c>
-      <c r="Q17" s="205">
+      <c r="Q17" s="200">
         <v>87.37</v>
       </c>
-      <c r="R17" s="197">
+      <c r="R17" s="205">
         <v>92.23</v>
       </c>
-      <c r="S17" s="198">
+      <c r="S17" s="208">
         <v>75.19</v>
       </c>
-      <c r="T17" s="206">
-        <v>81.27</v>
+      <c r="T17" s="201">
+        <v>87.28</v>
       </c>
     </row>
     <row r="18">
@@ -8426,7 +8426,7 @@
       <c r="C18" t="str">
         <v>301389</v>
       </c>
-      <c r="D18" s="218" t="str">
+      <c r="D18" s="210" t="str">
         <v>净卖: -3733.12万</v>
       </c>
       <c r="E18">
@@ -8441,41 +8441,41 @@
       <c r="H18">
         <v>2.9</v>
       </c>
-      <c r="I18" s="219">
+      <c r="I18" s="211">
         <v>-5.04</v>
       </c>
-      <c r="J18" s="215">
+      <c r="J18" s="212">
         <v>-16.57</v>
       </c>
-      <c r="K18" s="220">
+      <c r="K18" s="218">
         <v>-19.28</v>
       </c>
-      <c r="L18" s="213">
+      <c r="L18" s="215">
         <v>-23.54</v>
       </c>
       <c r="M18" s="216">
         <v>-15.42</v>
       </c>
-      <c r="N18" s="217">
+      <c r="N18" s="209">
         <v>-19.72</v>
       </c>
-      <c r="O18" s="211">
+      <c r="O18" s="219">
         <v>-22.3</v>
       </c>
-      <c r="P18" s="212">
+      <c r="P18" s="217">
         <v>-20.99</v>
       </c>
-      <c r="Q18" s="221">
+      <c r="Q18" s="213">
         <v>-16.47</v>
       </c>
-      <c r="R18" s="209">
+      <c r="R18" s="214">
         <v>-13.65</v>
       </c>
-      <c r="S18" s="210">
+      <c r="S18" s="220">
         <v>-15.93</v>
       </c>
-      <c r="T18" s="214">
-        <v>-24.86</v>
+      <c r="T18" s="221">
+        <v>-20.02</v>
       </c>
     </row>
     <row r="19">
@@ -8488,7 +8488,7 @@
       <c r="C19" t="str">
         <v>833580</v>
       </c>
-      <c r="D19" s="224" t="str">
+      <c r="D19" s="231" t="str">
         <v>净买: 656.67万</v>
       </c>
       <c r="E19">
@@ -8503,40 +8503,40 @@
       <c r="H19">
         <v>-1.6</v>
       </c>
-      <c r="I19" s="228">
+      <c r="I19" s="232">
         <v>32.07</v>
       </c>
-      <c r="J19" s="232">
+      <c r="J19" s="233">
         <v>19.86</v>
       </c>
-      <c r="K19" s="225">
+      <c r="K19" s="234">
         <v>10.83</v>
       </c>
-      <c r="L19" s="229">
+      <c r="L19" s="222">
         <v>7.1</v>
       </c>
-      <c r="M19" s="233">
+      <c r="M19" s="224">
         <v>12.21</v>
       </c>
-      <c r="N19" s="234">
+      <c r="N19" s="227">
         <v>19.07</v>
       </c>
-      <c r="O19" s="222">
+      <c r="O19" s="229">
         <v>16.13</v>
       </c>
-      <c r="P19" s="226">
+      <c r="P19" s="223">
         <v>10.95</v>
       </c>
-      <c r="Q19" s="227">
+      <c r="Q19" s="230">
         <v>8.72</v>
       </c>
-      <c r="R19" s="230">
+      <c r="R19" s="228">
         <v>8.78</v>
       </c>
-      <c r="S19" s="223">
+      <c r="S19" s="225">
         <v>9.81</v>
       </c>
-      <c r="T19" s="231">
+      <c r="T19" s="226">
         <v>-2.53</v>
       </c>
     </row>
@@ -8550,7 +8550,7 @@
       <c r="C20" t="str">
         <v>833580</v>
       </c>
-      <c r="D20" s="238" t="str">
+      <c r="D20" s="247" t="str">
         <v>净卖: -782.72万</v>
       </c>
       <c r="E20">
@@ -8565,40 +8565,40 @@
       <c r="H20">
         <v>8.88</v>
       </c>
-      <c r="I20" s="239">
+      <c r="I20" s="237">
         <v>-16.65</v>
       </c>
-      <c r="J20" s="245">
+      <c r="J20" s="235">
         <v>-22.93</v>
       </c>
-      <c r="K20" s="240">
+      <c r="K20" s="238">
         <v>-25.52</v>
       </c>
-      <c r="L20" s="247">
+      <c r="L20" s="236">
         <v>-21.97</v>
       </c>
-      <c r="M20" s="241">
+      <c r="M20" s="240">
         <v>-17.2</v>
       </c>
-      <c r="N20" s="235">
+      <c r="N20" s="243">
         <v>-19.25</v>
       </c>
-      <c r="O20" s="242">
+      <c r="O20" s="244">
         <v>-22.85</v>
       </c>
-      <c r="P20" s="243">
+      <c r="P20" s="245">
         <v>-24.39</v>
       </c>
-      <c r="Q20" s="246">
+      <c r="Q20" s="241">
         <v>-24.35</v>
       </c>
-      <c r="R20" s="244">
+      <c r="R20" s="246">
         <v>-23.64</v>
       </c>
-      <c r="S20" s="236">
+      <c r="S20" s="239">
         <v>-28.45</v>
       </c>
-      <c r="T20" s="237">
+      <c r="T20" s="242">
         <v>-32.22</v>
       </c>
     </row>
@@ -8612,7 +8612,7 @@
       <c r="C21" t="str">
         <v>601068</v>
       </c>
-      <c r="D21" s="251" t="str">
+      <c r="D21" s="255" t="str">
         <v>净买: 656.95万</v>
       </c>
       <c r="E21">
@@ -8627,41 +8627,41 @@
       <c r="H21">
         <v>0</v>
       </c>
-      <c r="I21" s="255">
+      <c r="I21" s="258">
         <v>10.02</v>
       </c>
-      <c r="J21" s="250">
+      <c r="J21" s="252">
         <v>5.75</v>
       </c>
-      <c r="K21" s="260">
+      <c r="K21" s="253">
         <v>0.37</v>
       </c>
-      <c r="L21" s="256">
+      <c r="L21" s="259">
         <v>0</v>
       </c>
-      <c r="M21" s="252">
+      <c r="M21" s="249">
         <v>-1.86</v>
       </c>
-      <c r="N21" s="253">
+      <c r="N21" s="256">
         <v>0.19</v>
       </c>
-      <c r="O21" s="257">
+      <c r="O21" s="250">
         <v>0.37</v>
       </c>
-      <c r="P21" s="258">
+      <c r="P21" s="260">
         <v>-1.86</v>
       </c>
-      <c r="Q21" s="248">
+      <c r="Q21" s="254">
         <v>-1.11</v>
       </c>
-      <c r="R21" s="254">
+      <c r="R21" s="248">
         <v>-1.86</v>
       </c>
-      <c r="S21" s="259">
+      <c r="S21" s="257">
         <v>-0.74</v>
       </c>
-      <c r="T21" s="249">
-        <v>18.18</v>
+      <c r="T21" s="251">
+        <v>17.81</v>
       </c>
     </row>
     <row r="22">
@@ -8674,7 +8674,7 @@
       <c r="C22" t="str">
         <v>688146</v>
       </c>
-      <c r="D22" s="267" t="str">
+      <c r="D22" s="269" t="str">
         <v>净买: 1029.87万</v>
       </c>
       <c r="E22">
@@ -8689,41 +8689,41 @@
       <c r="H22">
         <v>-0.49</v>
       </c>
-      <c r="I22" s="268">
+      <c r="I22" s="262">
         <v>16.28</v>
       </c>
       <c r="J22" s="270">
         <v>21.96</v>
       </c>
-      <c r="K22" s="271">
+      <c r="K22" s="272">
         <v>26.12</v>
       </c>
-      <c r="L22" s="263">
+      <c r="L22" s="271">
         <v>18.55</v>
       </c>
-      <c r="M22" s="264">
+      <c r="M22" s="268">
         <v>21.14</v>
       </c>
-      <c r="N22" s="272">
+      <c r="N22" s="273">
         <v>18.6</v>
       </c>
-      <c r="O22" s="273">
+      <c r="O22" s="263">
         <v>17.6</v>
       </c>
-      <c r="P22" s="269">
+      <c r="P22" s="264">
         <v>15.63</v>
       </c>
-      <c r="Q22" s="261">
+      <c r="Q22" s="265">
         <v>18.84</v>
       </c>
-      <c r="R22" s="265">
+      <c r="R22" s="266">
         <v>17.44</v>
       </c>
-      <c r="S22" s="262">
+      <c r="S22" s="267">
         <v>15.25</v>
       </c>
-      <c r="T22" s="266">
-        <v>74.6</v>
+      <c r="T22" s="261">
+        <v>79.07</v>
       </c>
     </row>
     <row r="23">
@@ -8736,7 +8736,7 @@
       <c r="C23" t="str">
         <v>600678</v>
       </c>
-      <c r="D23" s="276" t="str">
+      <c r="D23" s="279" t="str">
         <v>净卖: -1248.78万</v>
       </c>
       <c r="E23">
@@ -8751,41 +8751,41 @@
       <c r="H23">
         <v>-7.51</v>
       </c>
-      <c r="I23" s="281">
+      <c r="I23" s="283">
         <v>-2.71</v>
       </c>
-      <c r="J23" s="282">
+      <c r="J23" s="274">
         <v>-7.69</v>
       </c>
-      <c r="K23" s="285">
+      <c r="K23" s="275">
         <v>-3.85</v>
       </c>
-      <c r="L23" s="277">
+      <c r="L23" s="280">
         <v>-4.99</v>
       </c>
-      <c r="M23" s="283">
+      <c r="M23" s="284">
         <v>-9.33</v>
       </c>
-      <c r="N23" s="278">
+      <c r="N23" s="276">
         <v>-8.05</v>
       </c>
-      <c r="O23" s="286">
+      <c r="O23" s="277">
         <v>-3.7</v>
       </c>
-      <c r="P23" s="274">
+      <c r="P23" s="281">
         <v>-5.98</v>
       </c>
-      <c r="Q23" s="275">
+      <c r="Q23" s="278">
         <v>-8.9</v>
       </c>
-      <c r="R23" s="284">
+      <c r="R23" s="285">
         <v>-4.49</v>
       </c>
-      <c r="S23" s="279">
+      <c r="S23" s="286">
         <v>-2.49</v>
       </c>
-      <c r="T23" s="280">
-        <v>-23.15</v>
+      <c r="T23" s="282">
+        <v>-15.46</v>
       </c>
     </row>
     <row r="24">
@@ -8798,7 +8798,7 @@
       <c r="C24" t="str">
         <v>301449</v>
       </c>
-      <c r="D24" s="288" t="str">
+      <c r="D24" s="297" t="str">
         <v>净卖: -1931.35万</v>
       </c>
       <c r="E24">
@@ -8813,41 +8813,41 @@
       <c r="H24">
         <v>-7.39</v>
       </c>
-      <c r="I24" s="289">
+      <c r="I24" s="291">
         <v>-10.16</v>
       </c>
       <c r="J24" s="298">
         <v>-12.52</v>
       </c>
-      <c r="K24" s="294">
+      <c r="K24" s="299">
         <v>-14.52</v>
       </c>
-      <c r="L24" s="295">
+      <c r="L24" s="294">
         <v>-15.32</v>
       </c>
-      <c r="M24" s="290">
+      <c r="M24" s="292">
         <v>-9.86</v>
       </c>
-      <c r="N24" s="299">
+      <c r="N24" s="287">
         <v>-11.91</v>
       </c>
-      <c r="O24" s="287">
+      <c r="O24" s="288">
         <v>-12.71</v>
       </c>
-      <c r="P24" s="291">
+      <c r="P24" s="293">
         <v>-12.71</v>
       </c>
-      <c r="Q24" s="292">
+      <c r="Q24" s="295">
         <v>-16.26</v>
       </c>
-      <c r="R24" s="293">
+      <c r="R24" s="289">
         <v>-10.13</v>
       </c>
       <c r="S24" s="296">
         <v>-12.25</v>
       </c>
-      <c r="T24" s="297">
-        <v>-16.58</v>
+      <c r="T24" s="290">
+        <v>-14.35</v>
       </c>
     </row>
     <row r="25">
@@ -8860,7 +8860,7 @@
       <c r="C25" t="str">
         <v>688137</v>
       </c>
-      <c r="D25" s="307" t="str">
+      <c r="D25" s="309" t="str">
         <v>净买: 809.16万</v>
       </c>
       <c r="E25">
@@ -8875,41 +8875,41 @@
       <c r="H25">
         <v>-0.09</v>
       </c>
-      <c r="I25" s="308">
+      <c r="I25" s="310">
         <v>15.54</v>
       </c>
-      <c r="J25" s="300">
+      <c r="J25" s="312">
         <v>13.21</v>
       </c>
-      <c r="K25" s="309">
+      <c r="K25" s="306">
         <v>11.95</v>
       </c>
-      <c r="L25" s="310">
+      <c r="L25" s="300">
         <v>9.95</v>
       </c>
-      <c r="M25" s="301">
+      <c r="M25" s="303">
         <v>6.85</v>
       </c>
-      <c r="N25" s="303">
+      <c r="N25" s="311">
         <v>6.78</v>
       </c>
-      <c r="O25" s="304">
+      <c r="O25" s="301">
         <v>13.58</v>
       </c>
       <c r="P25" s="302">
         <v>14.61</v>
       </c>
-      <c r="Q25" s="305">
+      <c r="Q25" s="307">
         <v>16.47</v>
       </c>
-      <c r="R25" s="311">
+      <c r="R25" s="308">
         <v>23.92</v>
       </c>
-      <c r="S25" s="306">
+      <c r="S25" s="304">
         <v>15.3</v>
       </c>
-      <c r="T25" s="312">
-        <v>17.17</v>
+      <c r="T25" s="305">
+        <v>15.4</v>
       </c>
     </row>
     <row r="26">
@@ -8922,7 +8922,7 @@
       <c r="C26" t="str">
         <v>301408</v>
       </c>
-      <c r="D26" s="316" t="str">
+      <c r="D26" s="325" t="str">
         <v>净卖: -2207.20万</v>
       </c>
       <c r="E26">
@@ -8937,41 +8937,41 @@
       <c r="H26">
         <v>1.45</v>
       </c>
-      <c r="I26" s="317">
+      <c r="I26" s="314">
         <v>18.28</v>
       </c>
-      <c r="J26" s="318">
+      <c r="J26" s="317">
         <v>-5.37</v>
       </c>
-      <c r="K26" s="321">
+      <c r="K26" s="318">
         <v>-14.43</v>
       </c>
-      <c r="L26" s="323">
+      <c r="L26" s="319">
         <v>-13.43</v>
       </c>
-      <c r="M26" s="319">
+      <c r="M26" s="323">
         <v>-12.24</v>
       </c>
-      <c r="N26" s="314">
+      <c r="N26" s="320">
         <v>-13.31</v>
       </c>
       <c r="O26" s="324">
         <v>-7.91</v>
       </c>
-      <c r="P26" s="322">
+      <c r="P26" s="321">
         <v>-4.69</v>
       </c>
-      <c r="Q26" s="325">
+      <c r="Q26" s="313">
         <v>-0.32</v>
       </c>
-      <c r="R26" s="313">
+      <c r="R26" s="315">
         <v>-8.55</v>
       </c>
-      <c r="S26" s="315">
+      <c r="S26" s="322">
         <v>-11.88</v>
       </c>
-      <c r="T26" s="320">
-        <v>-17.61</v>
+      <c r="T26" s="316">
+        <v>-19.63</v>
       </c>
     </row>
     <row r="27">
@@ -8984,7 +8984,7 @@
       <c r="C27" t="str">
         <v>603598</v>
       </c>
-      <c r="D27" s="337" t="str">
+      <c r="D27" s="334" t="str">
         <v>净卖: -958.53万</v>
       </c>
       <c r="E27">
@@ -8999,41 +8999,41 @@
       <c r="H27">
         <v>-10.01</v>
       </c>
-      <c r="I27" s="329">
+      <c r="I27" s="327">
         <v>0</v>
       </c>
-      <c r="J27" s="338">
+      <c r="J27" s="331">
         <v>-5.64</v>
       </c>
-      <c r="K27" s="326">
+      <c r="K27" s="328">
         <v>-1.1</v>
       </c>
-      <c r="L27" s="330">
+      <c r="L27" s="329">
         <v>1.88</v>
       </c>
-      <c r="M27" s="331">
+      <c r="M27" s="332">
         <v>4.9</v>
       </c>
-      <c r="N27" s="334">
+      <c r="N27" s="333">
         <v>3.33</v>
       </c>
       <c r="O27" s="335">
         <v>1.33</v>
       </c>
-      <c r="P27" s="327">
+      <c r="P27" s="330">
         <v>-0.86</v>
       </c>
-      <c r="Q27" s="332">
+      <c r="Q27" s="336">
         <v>4.62</v>
       </c>
-      <c r="R27" s="336">
+      <c r="R27" s="337">
         <v>15.09</v>
       </c>
-      <c r="S27" s="328">
+      <c r="S27" s="338">
         <v>13.64</v>
       </c>
-      <c r="T27" s="333">
-        <v>-13.68</v>
+      <c r="T27" s="326">
+        <v>-15.24</v>
       </c>
     </row>
     <row r="28">
@@ -9046,7 +9046,7 @@
       <c r="C28" t="str">
         <v>920368</v>
       </c>
-      <c r="D28" s="340" t="str">
+      <c r="D28" s="346" t="str">
         <v>净买: 2785.37万</v>
       </c>
       <c r="E28">
@@ -9061,41 +9061,41 @@
       <c r="H28">
         <v>6.62</v>
       </c>
-      <c r="I28" s="351">
+      <c r="I28" s="347">
         <v>21.92</v>
       </c>
-      <c r="J28" s="343">
+      <c r="J28" s="348">
         <v>30.07</v>
       </c>
-      <c r="K28" s="344">
+      <c r="K28" s="345">
         <v>52.53</v>
       </c>
-      <c r="L28" s="347">
+      <c r="L28" s="342">
         <v>59.26</v>
       </c>
-      <c r="M28" s="348">
+      <c r="M28" s="349">
         <v>51.53</v>
       </c>
-      <c r="N28" s="345">
+      <c r="N28" s="350">
         <v>48.42</v>
       </c>
-      <c r="O28" s="341">
+      <c r="O28" s="343">
         <v>50.72</v>
       </c>
-      <c r="P28" s="346">
+      <c r="P28" s="351">
         <v>78.13</v>
       </c>
-      <c r="Q28" s="342">
+      <c r="Q28" s="339">
         <v>61.84</v>
       </c>
-      <c r="R28" s="339">
+      <c r="R28" s="344">
         <v>41.93</v>
       </c>
-      <c r="S28" s="349">
+      <c r="S28" s="340">
         <v>52.17</v>
       </c>
-      <c r="T28" s="350">
-        <v>1.6</v>
+      <c r="T28" s="341">
+        <v>-2.9</v>
       </c>
     </row>
     <row r="29">
@@ -9108,7 +9108,7 @@
       <c r="C29" t="str">
         <v>300017</v>
       </c>
-      <c r="D29" s="358" t="str">
+      <c r="D29" s="355" t="str">
         <v>净卖: -8231.84万</v>
       </c>
       <c r="E29">
@@ -9123,41 +9123,41 @@
       <c r="H29">
         <v>1.57</v>
       </c>
-      <c r="I29" s="364">
+      <c r="I29" s="363">
         <v>18.18</v>
       </c>
-      <c r="J29" s="362">
+      <c r="J29" s="364">
         <v>16.12</v>
       </c>
-      <c r="K29" s="359">
+      <c r="K29" s="360">
         <v>33.7</v>
       </c>
-      <c r="L29" s="360">
+      <c r="L29" s="361">
         <v>44.08</v>
       </c>
-      <c r="M29" s="352">
+      <c r="M29" s="356">
         <v>42.02</v>
       </c>
-      <c r="N29" s="355">
+      <c r="N29" s="354">
         <v>44.77</v>
       </c>
-      <c r="O29" s="363">
+      <c r="O29" s="352">
         <v>65.61</v>
       </c>
-      <c r="P29" s="356">
+      <c r="P29" s="357">
         <v>43.4</v>
       </c>
-      <c r="Q29" s="361">
+      <c r="Q29" s="353">
         <v>54.12</v>
       </c>
-      <c r="R29" s="357">
+      <c r="R29" s="358">
         <v>53.77</v>
       </c>
-      <c r="S29" s="353">
+      <c r="S29" s="359">
         <v>62.09</v>
       </c>
-      <c r="T29" s="354">
-        <v>60.03</v>
+      <c r="T29" s="362">
+        <v>54.2</v>
       </c>
     </row>
     <row r="30">
@@ -9185,41 +9185,41 @@
       <c r="H30">
         <v>-0.04</v>
       </c>
-      <c r="I30" s="372">
+      <c r="I30" s="369">
         <v>1.83</v>
       </c>
-      <c r="J30" s="365">
+      <c r="J30" s="373">
         <v>-4.09</v>
       </c>
-      <c r="K30" s="368">
+      <c r="K30" s="372">
         <v>-6.43</v>
       </c>
-      <c r="L30" s="377">
+      <c r="L30" s="374">
         <v>-7.11</v>
       </c>
-      <c r="M30" s="373">
+      <c r="M30" s="375">
         <v>-5.88</v>
       </c>
-      <c r="N30" s="366">
+      <c r="N30" s="370">
         <v>-7.63</v>
       </c>
-      <c r="O30" s="369">
+      <c r="O30" s="376">
         <v>-5.52</v>
       </c>
-      <c r="P30" s="374">
+      <c r="P30" s="365">
         <v>-4.65</v>
       </c>
-      <c r="Q30" s="367">
+      <c r="Q30" s="366">
         <v>-5.2</v>
       </c>
-      <c r="R30" s="375">
+      <c r="R30" s="377">
         <v>-5.72</v>
       </c>
-      <c r="S30" s="376">
+      <c r="S30" s="367">
         <v>-4.92</v>
       </c>
-      <c r="T30" s="370">
-        <v>-8.7</v>
+      <c r="T30" s="368">
+        <v>-8.02</v>
       </c>
     </row>
     <row r="31">
@@ -9232,7 +9232,7 @@
       <c r="C31" t="str">
         <v>920368</v>
       </c>
-      <c r="D31" s="378" t="str">
+      <c r="D31" s="388" t="str">
         <v>净卖: -476.30万</v>
       </c>
       <c r="E31">
@@ -9247,41 +9247,41 @@
       <c r="H31">
         <v>10.26</v>
       </c>
-      <c r="I31" s="382">
+      <c r="I31" s="381">
         <v>-3.25</v>
       </c>
-      <c r="J31" s="387">
+      <c r="J31" s="384">
         <v>13.46</v>
       </c>
-      <c r="K31" s="383">
+      <c r="K31" s="387">
         <v>18.46</v>
       </c>
-      <c r="L31" s="384">
+      <c r="L31" s="389">
         <v>12.71</v>
       </c>
-      <c r="M31" s="379">
+      <c r="M31" s="390">
         <v>10.4</v>
       </c>
-      <c r="N31" s="388">
+      <c r="N31" s="378">
         <v>12.12</v>
       </c>
       <c r="O31" s="385">
         <v>32.5</v>
       </c>
-      <c r="P31" s="386">
+      <c r="P31" s="379">
         <v>20.38</v>
       </c>
-      <c r="Q31" s="380">
+      <c r="Q31" s="386">
         <v>5.58</v>
       </c>
-      <c r="R31" s="389">
+      <c r="R31" s="382">
         <v>13.19</v>
       </c>
-      <c r="S31" s="381">
+      <c r="S31" s="383">
         <v>23.15</v>
       </c>
-      <c r="T31" s="390">
-        <v>-24.42</v>
+      <c r="T31" s="380">
+        <v>-27.77</v>
       </c>
     </row>
     <row r="32">
@@ -9294,7 +9294,7 @@
       <c r="C32" t="str">
         <v>600273</v>
       </c>
-      <c r="D32" s="392" t="str">
+      <c r="D32" s="403" t="str">
         <v>净卖: -3657.56万</v>
       </c>
       <c r="E32">
@@ -9309,41 +9309,41 @@
       <c r="H32">
         <v>3.89</v>
       </c>
-      <c r="I32" s="395">
+      <c r="I32" s="398">
         <v>5.92</v>
       </c>
-      <c r="J32" s="396">
+      <c r="J32" s="395">
         <v>2.96</v>
       </c>
-      <c r="K32" s="397">
+      <c r="K32" s="399">
         <v>-4.88</v>
       </c>
-      <c r="L32" s="401">
+      <c r="L32" s="396">
         <v>-3.05</v>
       </c>
-      <c r="M32" s="398">
+      <c r="M32" s="402">
         <v>-1.31</v>
       </c>
-      <c r="N32" s="402">
+      <c r="N32" s="400">
         <v>-4.18</v>
       </c>
-      <c r="O32" s="403">
+      <c r="O32" s="391">
         <v>-1.74</v>
       </c>
-      <c r="P32" s="391">
+      <c r="P32" s="392">
         <v>-1.66</v>
       </c>
-      <c r="Q32" s="399">
+      <c r="Q32" s="401">
         <v>0.78</v>
       </c>
-      <c r="R32" s="400">
+      <c r="R32" s="397">
         <v>1.83</v>
       </c>
       <c r="S32" s="393">
         <v>2.7</v>
       </c>
       <c r="T32" s="394">
-        <v>-22.39</v>
+        <v>-22.3</v>
       </c>
     </row>
     <row r="33">
@@ -9356,7 +9356,7 @@
       <c r="C33" t="str">
         <v>300257</v>
       </c>
-      <c r="D33" s="414" t="str">
+      <c r="D33" s="406" t="str">
         <v>净卖: -2507.66万</v>
       </c>
       <c r="E33">
@@ -9371,41 +9371,41 @@
       <c r="H33">
         <v>2.76</v>
       </c>
-      <c r="I33" s="415">
+      <c r="I33" s="412">
         <v>16.77</v>
       </c>
-      <c r="J33" s="416">
+      <c r="J33" s="407">
         <v>17.59</v>
       </c>
       <c r="K33" s="410">
         <v>16.46</v>
       </c>
-      <c r="L33" s="411">
+      <c r="L33" s="413">
         <v>7.35</v>
       </c>
-      <c r="M33" s="404">
+      <c r="M33" s="414">
         <v>14.56</v>
       </c>
-      <c r="N33" s="405">
+      <c r="N33" s="408">
         <v>8.23</v>
       </c>
-      <c r="O33" s="413">
+      <c r="O33" s="415">
         <v>8.64</v>
       </c>
-      <c r="P33" s="406">
+      <c r="P33" s="416">
         <v>8.67</v>
       </c>
-      <c r="Q33" s="407">
+      <c r="Q33" s="404">
         <v>5.17</v>
       </c>
-      <c r="R33" s="412">
+      <c r="R33" s="409">
         <v>1.33</v>
       </c>
-      <c r="S33" s="408">
+      <c r="S33" s="411">
         <v>1.8</v>
       </c>
-      <c r="T33" s="409">
-        <v>-0.44</v>
+      <c r="T33" s="405">
+        <v>-1.33</v>
       </c>
     </row>
     <row r="34">
@@ -9467,41 +9467,41 @@
       <c r="F35" t="str"/>
       <c r="G35" t="str"/>
       <c r="H35" t="str"/>
-      <c r="I35" s="423">
+      <c r="I35" s="419">
         <v>68.75</v>
       </c>
-      <c r="J35" s="424">
+      <c r="J35" s="420">
         <v>71.88</v>
       </c>
-      <c r="K35" s="419">
+      <c r="K35" s="422">
         <v>68.75</v>
       </c>
-      <c r="L35" s="420">
+      <c r="L35" s="423">
         <v>68.75</v>
       </c>
-      <c r="M35" s="421">
+      <c r="M35" s="424">
         <v>68.75</v>
       </c>
       <c r="N35" s="425">
         <v>71.88</v>
       </c>
-      <c r="O35" s="417">
+      <c r="O35" s="426">
         <v>71.88</v>
       </c>
-      <c r="P35" s="426">
+      <c r="P35" s="417">
         <v>62.5</v>
       </c>
-      <c r="Q35" s="427">
+      <c r="Q35" s="428">
         <v>65.63</v>
       </c>
-      <c r="R35" s="428">
+      <c r="R35" s="418">
         <v>62.5</v>
       </c>
-      <c r="S35" s="422">
+      <c r="S35" s="427">
         <v>65.63</v>
       </c>
-      <c r="T35" s="418">
-        <v>37.5</v>
+      <c r="T35" s="421">
+        <v>34.38</v>
       </c>
     </row>
     <row r="36">
@@ -9515,41 +9515,41 @@
       <c r="F36" t="str"/>
       <c r="G36" t="str"/>
       <c r="H36" t="str"/>
-      <c r="I36" s="436">
+      <c r="I36" s="432">
         <v>8.56</v>
       </c>
-      <c r="J36" s="437">
+      <c r="J36" s="433">
         <v>10.13</v>
       </c>
-      <c r="K36" s="438">
+      <c r="K36" s="437">
         <v>11.47</v>
       </c>
-      <c r="L36" s="432">
+      <c r="L36" s="431">
         <v>10.84</v>
       </c>
-      <c r="M36" s="430">
+      <c r="M36" s="438">
         <v>11.29</v>
       </c>
       <c r="N36" s="439">
         <v>10.99</v>
       </c>
-      <c r="O36" s="433">
+      <c r="O36" s="434">
         <v>12.53</v>
       </c>
-      <c r="P36" s="440">
+      <c r="P36" s="435">
         <v>11.98</v>
       </c>
-      <c r="Q36" s="434">
+      <c r="Q36" s="436">
         <v>10.83</v>
       </c>
-      <c r="R36" s="431">
+      <c r="R36" s="429">
         <v>10.67</v>
       </c>
-      <c r="S36" s="435">
+      <c r="S36" s="430">
         <v>10.08</v>
       </c>
-      <c r="T36" s="429">
-        <v>4.02</v>
+      <c r="T36" s="440">
+        <v>5.87</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/大小说家/index.xlsx
+++ b/youzi/大小说家/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="442">
+  <fills count="449">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -39,85 +39,2401 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46370"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7ECA90"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFEA8A93"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF82CB93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9EA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4352"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B25E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBE3C4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEFF0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB9199"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CDD1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8E1C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91D2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15663"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF3F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDE4C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BABF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91D2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBD5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7833"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF59BB6F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3DAF57"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD75"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8336"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF35AC50"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAEFDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBD6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3948"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4453"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB766"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF37AD52"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF218E3B"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF259C40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF73C586"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEAF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46370"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7ECA90"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
+        <fgColor rgb="FFB4E0BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2DA949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7BC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4BB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7E1C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -129,25 +2445,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFEA8790"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAFDFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -171,91 +2565,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9EA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF24993F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -267,2245 +2577,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4352"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B25E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEFF0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBE3C4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CDD1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB9199"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8E1C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91D2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15663"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF3F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDE4C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91D2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEB9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEB9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFEBD5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEB9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF59BB6F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8336"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD75"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7833"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3DAF57"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF35AC50"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFEBD6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAEFDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3948"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4453"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF82CB93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF37AD52"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB766"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF73C586"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB4E0BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8790"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7BC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2DA949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4BB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2517,19 +2595,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
+        <fgColor rgb="FFA81D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2541,25 +2607,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFAD202D"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2571,85 +2643,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2678,7 +2720,56 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="441">
+  <borders count="448">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -5770,7 +5861,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="441">
+  <cellXfs count="448">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -7090,6 +7181,27 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="440" fillId="441" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="441" fillId="442" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="442" fillId="443" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="443" fillId="444" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="444" fillId="445" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="445" fillId="446" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="446" fillId="447" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="447" fillId="448" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -7434,7 +7546,7 @@
       <c r="C2" t="str">
         <v>603319</v>
       </c>
-      <c r="D2" s="3" t="str">
+      <c r="D2" s="6" t="str">
         <v>净卖: -4050.11万</v>
       </c>
       <c r="E2">
@@ -7449,41 +7561,41 @@
       <c r="H2">
         <v>-2.13</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2" s="1">
         <v>-8.04</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="2">
         <v>-7</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="9">
         <v>-0.47</v>
       </c>
-      <c r="L2" s="7">
+      <c r="L2" s="11">
         <v>3.68</v>
       </c>
-      <c r="M2" s="8">
+      <c r="M2" s="12">
         <v>10.89</v>
       </c>
-      <c r="N2" s="10">
+      <c r="N2" s="3">
         <v>3.84</v>
       </c>
-      <c r="O2" s="11">
+      <c r="O2" s="10">
         <v>6.4</v>
       </c>
-      <c r="P2" s="12">
+      <c r="P2" s="7">
         <v>7.52</v>
       </c>
-      <c r="Q2" s="13">
+      <c r="Q2" s="4">
         <v>-2.98</v>
       </c>
-      <c r="R2" s="1">
+      <c r="R2" s="5">
         <v>2.88</v>
       </c>
-      <c r="S2" s="9">
+      <c r="S2" s="13">
         <v>6.19</v>
       </c>
-      <c r="T2" s="2">
-        <v>-7.08</v>
+      <c r="T2" s="8">
+        <v>-2.9</v>
       </c>
     </row>
     <row r="3">
@@ -7496,7 +7608,7 @@
       <c r="C3" t="str">
         <v>002923</v>
       </c>
-      <c r="D3" s="17" t="str">
+      <c r="D3" s="16" t="str">
         <v>净卖: -1342.21万</v>
       </c>
       <c r="E3">
@@ -7511,41 +7623,41 @@
       <c r="H3">
         <v>2.17</v>
       </c>
-      <c r="I3" s="18">
+      <c r="I3" s="25">
         <v>7.69</v>
       </c>
-      <c r="J3" s="19">
+      <c r="J3" s="17">
         <v>17.63</v>
       </c>
-      <c r="K3" s="15">
+      <c r="K3" s="18">
         <v>5.88</v>
       </c>
-      <c r="L3" s="14">
+      <c r="L3" s="19">
         <v>-4.3</v>
       </c>
-      <c r="M3" s="25">
+      <c r="M3" s="21">
         <v>-13.87</v>
       </c>
-      <c r="N3" s="26">
+      <c r="N3" s="22">
         <v>-11.45</v>
       </c>
-      <c r="O3" s="20">
+      <c r="O3" s="23">
         <v>-15.08</v>
       </c>
-      <c r="P3" s="21">
+      <c r="P3" s="26">
         <v>-14.66</v>
       </c>
-      <c r="Q3" s="22">
+      <c r="Q3" s="14">
         <v>-12.84</v>
       </c>
-      <c r="R3" s="23">
+      <c r="R3" s="20">
         <v>-21.56</v>
       </c>
-      <c r="S3" s="16">
+      <c r="S3" s="24">
         <v>-24.59</v>
       </c>
-      <c r="T3" s="24">
-        <v>-25.5</v>
+      <c r="T3" s="15">
+        <v>-26.17</v>
       </c>
     </row>
     <row r="4">
@@ -7558,7 +7670,7 @@
       <c r="C4" t="str">
         <v>002564</v>
       </c>
-      <c r="D4" s="38" t="str">
+      <c r="D4" s="29" t="str">
         <v>净买: 1737.48万</v>
       </c>
       <c r="E4">
@@ -7573,41 +7685,41 @@
       <c r="H4">
         <v>-1.38</v>
       </c>
-      <c r="I4" s="39">
+      <c r="I4" s="37">
         <v>11.55</v>
       </c>
-      <c r="J4" s="29">
+      <c r="J4" s="33">
         <v>2.39</v>
       </c>
-      <c r="K4" s="31">
+      <c r="K4" s="34">
         <v>12.55</v>
       </c>
-      <c r="L4" s="36">
+      <c r="L4" s="38">
         <v>5.58</v>
       </c>
-      <c r="M4" s="32">
+      <c r="M4" s="35">
         <v>16.14</v>
       </c>
-      <c r="N4" s="37">
+      <c r="N4" s="39">
         <v>21.51</v>
       </c>
-      <c r="O4" s="33">
+      <c r="O4" s="30">
         <v>16.14</v>
       </c>
-      <c r="P4" s="30">
+      <c r="P4" s="36">
         <v>19.92</v>
       </c>
-      <c r="Q4" s="34">
+      <c r="Q4" s="31">
         <v>20.72</v>
       </c>
-      <c r="R4" s="27">
+      <c r="R4" s="32">
         <v>15.94</v>
       </c>
-      <c r="S4" s="28">
+      <c r="S4" s="27">
         <v>8.96</v>
       </c>
-      <c r="T4" s="35">
-        <v>22.51</v>
+      <c r="T4" s="28">
+        <v>24.1</v>
       </c>
     </row>
     <row r="5">
@@ -7620,7 +7732,7 @@
       <c r="C5" t="str">
         <v>600735</v>
       </c>
-      <c r="D5" s="46" t="str">
+      <c r="D5" s="43" t="str">
         <v>净买: 1155.67万</v>
       </c>
       <c r="E5">
@@ -7635,25 +7747,25 @@
       <c r="H5">
         <v>1.24</v>
       </c>
-      <c r="I5" s="42">
+      <c r="I5" s="40">
         <v>8.71</v>
       </c>
-      <c r="J5" s="47">
+      <c r="J5" s="41">
         <v>8.84</v>
       </c>
-      <c r="K5" s="50">
+      <c r="K5" s="51">
         <v>7.48</v>
       </c>
-      <c r="L5" s="43">
+      <c r="L5" s="44">
         <v>4.63</v>
       </c>
-      <c r="M5" s="44">
+      <c r="M5" s="45">
         <v>5.71</v>
       </c>
-      <c r="N5" s="52">
+      <c r="N5" s="46">
         <v>11.16</v>
       </c>
-      <c r="O5" s="51">
+      <c r="O5" s="47">
         <v>9.66</v>
       </c>
       <c r="P5" s="48">
@@ -7662,13 +7774,13 @@
       <c r="Q5" s="49">
         <v>12.24</v>
       </c>
-      <c r="R5" s="40">
+      <c r="R5" s="50">
         <v>13.88</v>
       </c>
-      <c r="S5" s="41">
+      <c r="S5" s="52">
         <v>10.07</v>
       </c>
-      <c r="T5" s="45">
+      <c r="T5" s="42">
         <v>-8.44</v>
       </c>
     </row>
@@ -7697,40 +7809,40 @@
       <c r="H6">
         <v>-5.01</v>
       </c>
-      <c r="I6" s="61">
+      <c r="I6" s="56">
         <v>5.4</v>
       </c>
-      <c r="J6" s="56">
+      <c r="J6" s="63">
         <v>4.08</v>
       </c>
-      <c r="K6" s="59">
+      <c r="K6" s="64">
         <v>1.32</v>
       </c>
       <c r="L6" s="57">
         <v>2.37</v>
       </c>
-      <c r="M6" s="64">
+      <c r="M6" s="58">
         <v>7.64</v>
       </c>
-      <c r="N6" s="65">
+      <c r="N6" s="60">
         <v>6.19</v>
       </c>
-      <c r="O6" s="53">
+      <c r="O6" s="59">
         <v>3.43</v>
       </c>
-      <c r="P6" s="54">
+      <c r="P6" s="65">
         <v>8.7</v>
       </c>
-      <c r="Q6" s="62">
+      <c r="Q6" s="53">
         <v>10.28</v>
       </c>
-      <c r="R6" s="60">
+      <c r="R6" s="54">
         <v>6.59</v>
       </c>
-      <c r="S6" s="58">
+      <c r="S6" s="61">
         <v>3.43</v>
       </c>
-      <c r="T6" s="63">
+      <c r="T6" s="62">
         <v>-11.33</v>
       </c>
     </row>
@@ -7744,7 +7856,7 @@
       <c r="C7" t="str">
         <v>002365</v>
       </c>
-      <c r="D7" s="67" t="str">
+      <c r="D7" s="66" t="str">
         <v>净卖: -2887.03万</v>
       </c>
       <c r="E7">
@@ -7759,41 +7871,41 @@
       <c r="H7">
         <v>3.76</v>
       </c>
-      <c r="I7" s="68">
+      <c r="I7" s="76">
         <v>-4.32</v>
       </c>
-      <c r="J7" s="78">
+      <c r="J7" s="67">
         <v>5.25</v>
       </c>
-      <c r="K7" s="75">
+      <c r="K7" s="77">
         <v>15.76</v>
       </c>
-      <c r="L7" s="76">
+      <c r="L7" s="68">
         <v>27.33</v>
       </c>
-      <c r="M7" s="69">
+      <c r="M7" s="72">
         <v>35.58</v>
       </c>
-      <c r="N7" s="70">
+      <c r="N7" s="71">
         <v>40.03</v>
       </c>
       <c r="O7" s="73">
         <v>54.03</v>
       </c>
-      <c r="P7" s="74">
+      <c r="P7" s="69">
         <v>38.65</v>
       </c>
-      <c r="Q7" s="66">
+      <c r="Q7" s="70">
         <v>24.77</v>
       </c>
-      <c r="R7" s="77">
+      <c r="R7" s="78">
         <v>28.27</v>
       </c>
-      <c r="S7" s="71">
+      <c r="S7" s="74">
         <v>22.51</v>
       </c>
-      <c r="T7" s="72">
-        <v>-15.82</v>
+      <c r="T7" s="75">
+        <v>-19.2</v>
       </c>
     </row>
     <row r="8">
@@ -7806,7 +7918,7 @@
       <c r="C8" t="str">
         <v>603585</v>
       </c>
-      <c r="D8" s="80" t="str">
+      <c r="D8" s="86" t="str">
         <v>净买: 590.46万</v>
       </c>
       <c r="E8">
@@ -7821,41 +7933,41 @@
       <c r="H8">
         <v>-2.32</v>
       </c>
-      <c r="I8" s="81">
+      <c r="I8" s="83">
         <v>8.09</v>
       </c>
-      <c r="J8" s="82">
+      <c r="J8" s="87">
         <v>7.12</v>
       </c>
-      <c r="K8" s="85">
+      <c r="K8" s="81">
         <v>17.86</v>
       </c>
-      <c r="L8" s="83">
+      <c r="L8" s="90">
         <v>29.63</v>
       </c>
-      <c r="M8" s="90">
+      <c r="M8" s="84">
         <v>16.68</v>
       </c>
-      <c r="N8" s="84">
+      <c r="N8" s="91">
         <v>5.02</v>
       </c>
-      <c r="O8" s="86">
+      <c r="O8" s="88">
         <v>0.38</v>
       </c>
-      <c r="P8" s="87">
+      <c r="P8" s="79">
         <v>2.75</v>
       </c>
-      <c r="Q8" s="91">
+      <c r="Q8" s="82">
         <v>2.05</v>
       </c>
-      <c r="R8" s="79">
+      <c r="R8" s="80">
         <v>-0.32</v>
       </c>
-      <c r="S8" s="88">
+      <c r="S8" s="85">
         <v>-1.57</v>
       </c>
       <c r="T8" s="89">
-        <v>25.9</v>
+        <v>8.09</v>
       </c>
     </row>
     <row r="9">
@@ -7868,7 +7980,7 @@
       <c r="C9" t="str">
         <v>003029</v>
       </c>
-      <c r="D9" s="100" t="str">
+      <c r="D9" s="99" t="str">
         <v>净卖: -1441.18万</v>
       </c>
       <c r="E9">
@@ -7883,31 +7995,31 @@
       <c r="H9">
         <v>0.04</v>
       </c>
-      <c r="I9" s="96">
+      <c r="I9" s="100">
         <v>9.96</v>
       </c>
       <c r="J9" s="92">
         <v>14.48</v>
       </c>
-      <c r="K9" s="97">
+      <c r="K9" s="96">
         <v>8.49</v>
       </c>
-      <c r="L9" s="101">
+      <c r="L9" s="97">
         <v>8.99</v>
       </c>
-      <c r="M9" s="102">
+      <c r="M9" s="101">
         <v>7.77</v>
       </c>
-      <c r="N9" s="98">
+      <c r="N9" s="93">
         <v>2.72</v>
       </c>
-      <c r="O9" s="93">
+      <c r="O9" s="102">
         <v>1.22</v>
       </c>
       <c r="P9" s="94">
         <v>-1.33</v>
       </c>
-      <c r="Q9" s="99">
+      <c r="Q9" s="103">
         <v>-1.65</v>
       </c>
       <c r="R9" s="95">
@@ -7916,8 +8028,8 @@
       <c r="S9" s="104">
         <v>-2.01</v>
       </c>
-      <c r="T9" s="103">
-        <v>-24.79</v>
+      <c r="T9" s="98">
+        <v>-24.51</v>
       </c>
     </row>
     <row r="10">
@@ -7930,7 +8042,7 @@
       <c r="C10" t="str">
         <v>301486</v>
       </c>
-      <c r="D10" s="114" t="str">
+      <c r="D10" s="117" t="str">
         <v>净买: 2150.96万</v>
       </c>
       <c r="E10">
@@ -7945,41 +8057,41 @@
       <c r="H10">
         <v>1.79</v>
       </c>
-      <c r="I10" s="106">
+      <c r="I10" s="105">
         <v>17.9</v>
       </c>
-      <c r="J10" s="115">
+      <c r="J10" s="107">
         <v>21.2</v>
       </c>
-      <c r="K10" s="116">
+      <c r="K10" s="108">
         <v>12.29</v>
       </c>
-      <c r="L10" s="107">
+      <c r="L10" s="111">
         <v>14.55</v>
       </c>
-      <c r="M10" s="105">
+      <c r="M10" s="115">
         <v>21.65</v>
       </c>
-      <c r="N10" s="111">
+      <c r="N10" s="109">
         <v>15.36</v>
       </c>
-      <c r="O10" s="108">
+      <c r="O10" s="112">
         <v>9.81</v>
       </c>
-      <c r="P10" s="117">
+      <c r="P10" s="106">
         <v>10.06</v>
       </c>
-      <c r="Q10" s="112">
+      <c r="Q10" s="110">
         <v>17.68</v>
       </c>
-      <c r="R10" s="109">
+      <c r="R10" s="116">
         <v>24.45</v>
       </c>
       <c r="S10" s="113">
         <v>20.16</v>
       </c>
-      <c r="T10" s="110">
-        <v>167.99</v>
+      <c r="T10" s="114">
+        <v>152.02</v>
       </c>
     </row>
     <row r="11">
@@ -7992,7 +8104,7 @@
       <c r="C11" t="str">
         <v>002052</v>
       </c>
-      <c r="D11" s="120" t="str">
+      <c r="D11" s="125" t="str">
         <v>净卖: -1505.16万</v>
       </c>
       <c r="E11">
@@ -8007,41 +8119,41 @@
       <c r="H11">
         <v>10.03</v>
       </c>
-      <c r="I11" s="125">
+      <c r="I11" s="129">
         <v>0</v>
       </c>
-      <c r="J11" s="127">
+      <c r="J11" s="118">
         <v>4.18</v>
       </c>
-      <c r="K11" s="121">
+      <c r="K11" s="130">
         <v>14.59</v>
       </c>
-      <c r="L11" s="128">
+      <c r="L11" s="121">
         <v>26.06</v>
       </c>
-      <c r="M11" s="122">
+      <c r="M11" s="126">
         <v>38.68</v>
       </c>
-      <c r="N11" s="123">
+      <c r="N11" s="119">
         <v>44.38</v>
       </c>
-      <c r="O11" s="129">
+      <c r="O11" s="120">
         <v>45.82</v>
       </c>
-      <c r="P11" s="118">
+      <c r="P11" s="122">
         <v>53.88</v>
       </c>
-      <c r="Q11" s="130">
+      <c r="Q11" s="127">
         <v>45.36</v>
       </c>
-      <c r="R11" s="124">
+      <c r="R11" s="123">
         <v>34.42</v>
       </c>
-      <c r="S11" s="126">
+      <c r="S11" s="128">
         <v>39.06</v>
       </c>
-      <c r="T11" s="119">
-        <v>-22.64</v>
+      <c r="T11" s="124">
+        <v>-24.77</v>
       </c>
     </row>
     <row r="12">
@@ -8054,7 +8166,7 @@
       <c r="C12" t="str">
         <v>430476</v>
       </c>
-      <c r="D12" s="135" t="str">
+      <c r="D12" s="132" t="str">
         <v>净买: 566.61万</v>
       </c>
       <c r="E12">
@@ -8069,40 +8181,40 @@
       <c r="H12">
         <v>2.2</v>
       </c>
-      <c r="I12" s="132">
+      <c r="I12" s="137">
         <v>27.17</v>
       </c>
-      <c r="J12" s="136">
+      <c r="J12" s="143">
         <v>65.32</v>
       </c>
       <c r="K12" s="133">
         <v>65.69</v>
       </c>
-      <c r="L12" s="137">
+      <c r="L12" s="139">
         <v>47.53</v>
       </c>
-      <c r="M12" s="140">
+      <c r="M12" s="134">
         <v>34.9</v>
       </c>
-      <c r="N12" s="141">
+      <c r="N12" s="140">
         <v>37.51</v>
       </c>
       <c r="O12" s="138">
         <v>35.45</v>
       </c>
-      <c r="P12" s="134">
+      <c r="P12" s="135">
         <v>35.86</v>
       </c>
-      <c r="Q12" s="139">
+      <c r="Q12" s="141">
         <v>29.23</v>
       </c>
-      <c r="R12" s="131">
+      <c r="R12" s="142">
         <v>29.87</v>
       </c>
-      <c r="S12" s="142">
+      <c r="S12" s="136">
         <v>29.96</v>
       </c>
-      <c r="T12" s="143">
+      <c r="T12" s="131">
         <v>14.04</v>
       </c>
     </row>
@@ -8116,7 +8228,7 @@
       <c r="C13" t="str">
         <v>871981</v>
       </c>
-      <c r="D13" s="148" t="str">
+      <c r="D13" s="156" t="str">
         <v>净买: 779.65万</v>
       </c>
       <c r="E13">
@@ -8131,40 +8243,40 @@
       <c r="H13">
         <v>10.55</v>
       </c>
-      <c r="I13" s="149">
+      <c r="I13" s="150">
         <v>17.58</v>
       </c>
-      <c r="J13" s="155">
+      <c r="J13" s="151">
         <v>17.95</v>
       </c>
-      <c r="K13" s="146">
+      <c r="K13" s="152">
         <v>13.64</v>
       </c>
-      <c r="L13" s="150">
+      <c r="L13" s="153">
         <v>14.65</v>
       </c>
-      <c r="M13" s="156">
+      <c r="M13" s="144">
         <v>17.15</v>
       </c>
-      <c r="N13" s="144">
+      <c r="N13" s="145">
         <v>11.72</v>
       </c>
-      <c r="O13" s="153">
+      <c r="O13" s="147">
         <v>6.52</v>
       </c>
-      <c r="P13" s="145">
+      <c r="P13" s="154">
         <v>0.28</v>
       </c>
-      <c r="Q13" s="154">
+      <c r="Q13" s="146">
         <v>1.84</v>
       </c>
-      <c r="R13" s="147">
+      <c r="R13" s="155">
         <v>-1.52</v>
       </c>
-      <c r="S13" s="151">
+      <c r="S13" s="148">
         <v>0.2</v>
       </c>
-      <c r="T13" s="152">
+      <c r="T13" s="149">
         <v>-6.54</v>
       </c>
     </row>
@@ -8178,7 +8290,7 @@
       <c r="C14" t="str">
         <v>871981</v>
       </c>
-      <c r="D14" s="158" t="str">
+      <c r="D14" s="164" t="str">
         <v>净卖: -825.29万</v>
       </c>
       <c r="E14">
@@ -8193,40 +8305,40 @@
       <c r="H14">
         <v>7.39</v>
       </c>
-      <c r="I14" s="168">
+      <c r="I14" s="165">
         <v>-6.58</v>
       </c>
-      <c r="J14" s="162">
+      <c r="J14" s="161">
         <v>-10</v>
       </c>
-      <c r="K14" s="159">
+      <c r="K14" s="166">
         <v>-9.2</v>
       </c>
-      <c r="L14" s="164">
+      <c r="L14" s="167">
         <v>-7.22</v>
       </c>
-      <c r="M14" s="160">
+      <c r="M14" s="162">
         <v>-11.52</v>
       </c>
-      <c r="N14" s="169">
+      <c r="N14" s="158">
         <v>-15.64</v>
       </c>
-      <c r="O14" s="163">
+      <c r="O14" s="168">
         <v>-20.58</v>
       </c>
-      <c r="P14" s="165">
+      <c r="P14" s="169">
         <v>-19.34</v>
       </c>
-      <c r="Q14" s="166">
+      <c r="Q14" s="157">
         <v>-22</v>
       </c>
-      <c r="R14" s="161">
+      <c r="R14" s="163">
         <v>-20.64</v>
       </c>
-      <c r="S14" s="167">
+      <c r="S14" s="159">
         <v>-21.32</v>
       </c>
-      <c r="T14" s="157">
+      <c r="T14" s="160">
         <v>-25.98</v>
       </c>
     </row>
@@ -8240,7 +8352,7 @@
       <c r="C15" t="str">
         <v>301389</v>
       </c>
-      <c r="D15" s="181" t="str">
+      <c r="D15" s="180" t="str">
         <v>净买: 4127.06万</v>
       </c>
       <c r="E15">
@@ -8255,31 +8367,31 @@
       <c r="H15">
         <v>0.95</v>
       </c>
-      <c r="I15" s="178">
+      <c r="I15" s="172">
         <v>18.87</v>
       </c>
-      <c r="J15" s="172">
+      <c r="J15" s="181">
         <v>42.65</v>
       </c>
-      <c r="K15" s="175">
+      <c r="K15" s="176">
         <v>49.96</v>
       </c>
-      <c r="L15" s="176">
+      <c r="L15" s="173">
         <v>46.52</v>
       </c>
-      <c r="M15" s="182">
+      <c r="M15" s="174">
         <v>28.73</v>
       </c>
-      <c r="N15" s="179">
+      <c r="N15" s="177">
         <v>24.55</v>
       </c>
-      <c r="O15" s="173">
+      <c r="O15" s="175">
         <v>17.98</v>
       </c>
-      <c r="P15" s="177">
+      <c r="P15" s="178">
         <v>30.5</v>
       </c>
-      <c r="Q15" s="180">
+      <c r="Q15" s="182">
         <v>23.88</v>
       </c>
       <c r="R15" s="170">
@@ -8288,8 +8400,8 @@
       <c r="S15" s="171">
         <v>21.91</v>
       </c>
-      <c r="T15" s="174">
-        <v>23.41</v>
+      <c r="T15" s="179">
+        <v>13.93</v>
       </c>
     </row>
     <row r="16">
@@ -8302,7 +8414,7 @@
       <c r="C16" t="str">
         <v>301389</v>
       </c>
-      <c r="D16" s="183" t="str">
+      <c r="D16" s="191" t="str">
         <v>净买: 932.40万</v>
       </c>
       <c r="E16">
@@ -8317,41 +8429,41 @@
       <c r="H16">
         <v>-5.75</v>
       </c>
-      <c r="I16" s="184">
+      <c r="I16" s="189">
         <v>27.33</v>
       </c>
-      <c r="J16" s="185">
+      <c r="J16" s="190">
         <v>33.86</v>
       </c>
-      <c r="K16" s="194">
+      <c r="K16" s="195">
         <v>30.79</v>
       </c>
-      <c r="L16" s="189">
+      <c r="L16" s="192">
         <v>14.91</v>
       </c>
-      <c r="M16" s="186">
+      <c r="M16" s="184">
         <v>11.18</v>
       </c>
-      <c r="N16" s="192">
+      <c r="N16" s="185">
         <v>5.32</v>
       </c>
-      <c r="O16" s="187">
+      <c r="O16" s="186">
         <v>16.49</v>
       </c>
       <c r="P16" s="193">
         <v>10.58</v>
       </c>
-      <c r="Q16" s="190">
+      <c r="Q16" s="194">
         <v>7.02</v>
       </c>
-      <c r="R16" s="188">
+      <c r="R16" s="187">
         <v>8.82</v>
       </c>
-      <c r="S16" s="191">
+      <c r="S16" s="188">
         <v>15.05</v>
       </c>
-      <c r="T16" s="195">
-        <v>10.16</v>
+      <c r="T16" s="183">
+        <v>1.7</v>
       </c>
     </row>
     <row r="17">
@@ -8364,7 +8476,7 @@
       <c r="C17" t="str">
         <v>300450</v>
       </c>
-      <c r="D17" s="202" t="str">
+      <c r="D17" s="199" t="str">
         <v>净卖: -4644.14万</v>
       </c>
       <c r="E17">
@@ -8379,41 +8491,41 @@
       <c r="H17">
         <v>5.71</v>
       </c>
-      <c r="I17" s="196">
+      <c r="I17" s="208">
         <v>13.52</v>
       </c>
-      <c r="J17" s="203">
+      <c r="J17" s="204">
         <v>30.12</v>
       </c>
-      <c r="K17" s="204">
+      <c r="K17" s="200">
         <v>40.03</v>
       </c>
-      <c r="L17" s="197">
+      <c r="L17" s="205">
         <v>40.54</v>
       </c>
       <c r="M17" s="206">
         <v>43.32</v>
       </c>
-      <c r="N17" s="198">
+      <c r="N17" s="196">
         <v>71.99</v>
       </c>
-      <c r="O17" s="199">
+      <c r="O17" s="201">
         <v>83.47</v>
       </c>
-      <c r="P17" s="207">
+      <c r="P17" s="202">
         <v>79.22</v>
       </c>
-      <c r="Q17" s="200">
+      <c r="Q17" s="197">
         <v>87.37</v>
       </c>
-      <c r="R17" s="205">
+      <c r="R17" s="203">
         <v>92.23</v>
       </c>
-      <c r="S17" s="208">
+      <c r="S17" s="198">
         <v>75.19</v>
       </c>
-      <c r="T17" s="201">
-        <v>87.28</v>
+      <c r="T17" s="207">
+        <v>82.1</v>
       </c>
     </row>
     <row r="18">
@@ -8426,7 +8538,7 @@
       <c r="C18" t="str">
         <v>301389</v>
       </c>
-      <c r="D18" s="210" t="str">
+      <c r="D18" s="216" t="str">
         <v>净卖: -3733.12万</v>
       </c>
       <c r="E18">
@@ -8441,41 +8553,41 @@
       <c r="H18">
         <v>2.9</v>
       </c>
-      <c r="I18" s="211">
+      <c r="I18" s="220">
         <v>-5.04</v>
       </c>
-      <c r="J18" s="212">
+      <c r="J18" s="217">
         <v>-16.57</v>
       </c>
-      <c r="K18" s="218">
+      <c r="K18" s="209">
         <v>-19.28</v>
       </c>
-      <c r="L18" s="215">
+      <c r="L18" s="218">
         <v>-23.54</v>
       </c>
-      <c r="M18" s="216">
+      <c r="M18" s="214">
         <v>-15.42</v>
       </c>
-      <c r="N18" s="209">
+      <c r="N18" s="210">
         <v>-19.72</v>
       </c>
-      <c r="O18" s="219">
+      <c r="O18" s="215">
         <v>-22.3</v>
       </c>
-      <c r="P18" s="217">
+      <c r="P18" s="211">
         <v>-20.99</v>
       </c>
-      <c r="Q18" s="213">
+      <c r="Q18" s="221">
         <v>-16.47</v>
       </c>
-      <c r="R18" s="214">
+      <c r="R18" s="212">
         <v>-13.65</v>
       </c>
-      <c r="S18" s="220">
+      <c r="S18" s="213">
         <v>-15.93</v>
       </c>
-      <c r="T18" s="221">
-        <v>-20.02</v>
+      <c r="T18" s="219">
+        <v>-26.16</v>
       </c>
     </row>
     <row r="19">
@@ -8488,7 +8600,7 @@
       <c r="C19" t="str">
         <v>833580</v>
       </c>
-      <c r="D19" s="231" t="str">
+      <c r="D19" s="227" t="str">
         <v>净买: 656.67万</v>
       </c>
       <c r="E19">
@@ -8503,40 +8615,40 @@
       <c r="H19">
         <v>-1.6</v>
       </c>
-      <c r="I19" s="232">
+      <c r="I19" s="228">
         <v>32.07</v>
       </c>
-      <c r="J19" s="233">
+      <c r="J19" s="223">
         <v>19.86</v>
       </c>
-      <c r="K19" s="234">
+      <c r="K19" s="232">
         <v>10.83</v>
       </c>
-      <c r="L19" s="222">
+      <c r="L19" s="229">
         <v>7.1</v>
       </c>
-      <c r="M19" s="224">
+      <c r="M19" s="233">
         <v>12.21</v>
       </c>
-      <c r="N19" s="227">
+      <c r="N19" s="224">
         <v>19.07</v>
       </c>
-      <c r="O19" s="229">
+      <c r="O19" s="234">
         <v>16.13</v>
       </c>
-      <c r="P19" s="223">
+      <c r="P19" s="225">
         <v>10.95</v>
       </c>
-      <c r="Q19" s="230">
+      <c r="Q19" s="222">
         <v>8.72</v>
       </c>
-      <c r="R19" s="228">
+      <c r="R19" s="226">
         <v>8.78</v>
       </c>
-      <c r="S19" s="225">
+      <c r="S19" s="230">
         <v>9.81</v>
       </c>
-      <c r="T19" s="226">
+      <c r="T19" s="231">
         <v>-2.53</v>
       </c>
     </row>
@@ -8550,7 +8662,7 @@
       <c r="C20" t="str">
         <v>833580</v>
       </c>
-      <c r="D20" s="247" t="str">
+      <c r="D20" s="237" t="str">
         <v>净卖: -782.72万</v>
       </c>
       <c r="E20">
@@ -8565,19 +8677,19 @@
       <c r="H20">
         <v>8.88</v>
       </c>
-      <c r="I20" s="237">
+      <c r="I20" s="235">
         <v>-16.65</v>
       </c>
-      <c r="J20" s="235">
+      <c r="J20" s="238">
         <v>-22.93</v>
       </c>
-      <c r="K20" s="238">
+      <c r="K20" s="241">
         <v>-25.52</v>
       </c>
-      <c r="L20" s="236">
+      <c r="L20" s="242">
         <v>-21.97</v>
       </c>
-      <c r="M20" s="240">
+      <c r="M20" s="246">
         <v>-17.2</v>
       </c>
       <c r="N20" s="243">
@@ -8586,19 +8698,19 @@
       <c r="O20" s="244">
         <v>-22.85</v>
       </c>
-      <c r="P20" s="245">
+      <c r="P20" s="236">
         <v>-24.39</v>
       </c>
-      <c r="Q20" s="241">
+      <c r="Q20" s="239">
         <v>-24.35</v>
       </c>
-      <c r="R20" s="246">
+      <c r="R20" s="247">
         <v>-23.64</v>
       </c>
-      <c r="S20" s="239">
+      <c r="S20" s="245">
         <v>-28.45</v>
       </c>
-      <c r="T20" s="242">
+      <c r="T20" s="240">
         <v>-32.22</v>
       </c>
     </row>
@@ -8612,7 +8724,7 @@
       <c r="C21" t="str">
         <v>601068</v>
       </c>
-      <c r="D21" s="255" t="str">
+      <c r="D21" s="253" t="str">
         <v>净买: 656.95万</v>
       </c>
       <c r="E21">
@@ -8627,41 +8739,41 @@
       <c r="H21">
         <v>0</v>
       </c>
-      <c r="I21" s="258">
+      <c r="I21" s="250">
         <v>10.02</v>
       </c>
-      <c r="J21" s="252">
+      <c r="J21" s="257">
         <v>5.75</v>
       </c>
-      <c r="K21" s="253">
+      <c r="K21" s="248">
         <v>0.37</v>
       </c>
-      <c r="L21" s="259">
+      <c r="L21" s="258">
         <v>0</v>
       </c>
-      <c r="M21" s="249">
+      <c r="M21" s="251">
         <v>-1.86</v>
       </c>
-      <c r="N21" s="256">
+      <c r="N21" s="254">
         <v>0.19</v>
       </c>
-      <c r="O21" s="250">
+      <c r="O21" s="259">
         <v>0.37</v>
       </c>
-      <c r="P21" s="260">
+      <c r="P21" s="249">
         <v>-1.86</v>
       </c>
-      <c r="Q21" s="254">
+      <c r="Q21" s="255">
         <v>-1.11</v>
       </c>
-      <c r="R21" s="248">
+      <c r="R21" s="252">
         <v>-1.86</v>
       </c>
-      <c r="S21" s="257">
+      <c r="S21" s="256">
         <v>-0.74</v>
       </c>
-      <c r="T21" s="251">
-        <v>17.81</v>
+      <c r="T21" s="260">
+        <v>17.44</v>
       </c>
     </row>
     <row r="22">
@@ -8674,7 +8786,7 @@
       <c r="C22" t="str">
         <v>688146</v>
       </c>
-      <c r="D22" s="269" t="str">
+      <c r="D22" s="267" t="str">
         <v>净买: 1029.87万</v>
       </c>
       <c r="E22">
@@ -8689,41 +8801,41 @@
       <c r="H22">
         <v>-0.49</v>
       </c>
-      <c r="I22" s="262">
+      <c r="I22" s="273">
         <v>16.28</v>
       </c>
-      <c r="J22" s="270">
+      <c r="J22" s="263">
         <v>21.96</v>
       </c>
-      <c r="K22" s="272">
+      <c r="K22" s="268">
         <v>26.12</v>
       </c>
-      <c r="L22" s="271">
+      <c r="L22" s="269">
         <v>18.55</v>
       </c>
-      <c r="M22" s="268">
+      <c r="M22" s="270">
         <v>21.14</v>
       </c>
-      <c r="N22" s="273">
+      <c r="N22" s="261">
         <v>18.6</v>
       </c>
-      <c r="O22" s="263">
+      <c r="O22" s="271">
         <v>17.6</v>
       </c>
       <c r="P22" s="264">
         <v>15.63</v>
       </c>
-      <c r="Q22" s="265">
+      <c r="Q22" s="266">
         <v>18.84</v>
       </c>
-      <c r="R22" s="266">
+      <c r="R22" s="272">
         <v>17.44</v>
       </c>
-      <c r="S22" s="267">
+      <c r="S22" s="262">
         <v>15.25</v>
       </c>
-      <c r="T22" s="261">
-        <v>79.07</v>
+      <c r="T22" s="265">
+        <v>88.84</v>
       </c>
     </row>
     <row r="23">
@@ -8736,7 +8848,7 @@
       <c r="C23" t="str">
         <v>600678</v>
       </c>
-      <c r="D23" s="279" t="str">
+      <c r="D23" s="278" t="str">
         <v>净卖: -1248.78万</v>
       </c>
       <c r="E23">
@@ -8751,41 +8863,41 @@
       <c r="H23">
         <v>-7.51</v>
       </c>
-      <c r="I23" s="283">
+      <c r="I23" s="284">
         <v>-2.71</v>
       </c>
       <c r="J23" s="274">
         <v>-7.69</v>
       </c>
-      <c r="K23" s="275">
+      <c r="K23" s="279">
         <v>-3.85</v>
       </c>
-      <c r="L23" s="280">
+      <c r="L23" s="282">
         <v>-4.99</v>
       </c>
-      <c r="M23" s="284">
+      <c r="M23" s="275">
         <v>-9.33</v>
       </c>
-      <c r="N23" s="276">
+      <c r="N23" s="285">
         <v>-8.05</v>
       </c>
-      <c r="O23" s="277">
+      <c r="O23" s="283">
         <v>-3.7</v>
       </c>
-      <c r="P23" s="281">
+      <c r="P23" s="276">
         <v>-5.98</v>
       </c>
-      <c r="Q23" s="278">
+      <c r="Q23" s="277">
         <v>-8.9</v>
       </c>
-      <c r="R23" s="285">
+      <c r="R23" s="280">
         <v>-4.49</v>
       </c>
       <c r="S23" s="286">
         <v>-2.49</v>
       </c>
-      <c r="T23" s="282">
-        <v>-15.46</v>
+      <c r="T23" s="281">
+        <v>-13.25</v>
       </c>
     </row>
     <row r="24">
@@ -8798,7 +8910,7 @@
       <c r="C24" t="str">
         <v>301449</v>
       </c>
-      <c r="D24" s="297" t="str">
+      <c r="D24" s="288" t="str">
         <v>净卖: -1931.35万</v>
       </c>
       <c r="E24">
@@ -8813,41 +8925,41 @@
       <c r="H24">
         <v>-7.39</v>
       </c>
-      <c r="I24" s="291">
+      <c r="I24" s="289">
         <v>-10.16</v>
       </c>
-      <c r="J24" s="298">
+      <c r="J24" s="290">
         <v>-12.52</v>
       </c>
-      <c r="K24" s="299">
+      <c r="K24" s="294">
         <v>-14.52</v>
       </c>
-      <c r="L24" s="294">
+      <c r="L24" s="299">
         <v>-15.32</v>
       </c>
-      <c r="M24" s="292">
+      <c r="M24" s="295">
         <v>-9.86</v>
       </c>
       <c r="N24" s="287">
         <v>-11.91</v>
       </c>
-      <c r="O24" s="288">
+      <c r="O24" s="292">
         <v>-12.71</v>
       </c>
-      <c r="P24" s="293">
+      <c r="P24" s="296">
         <v>-12.71</v>
       </c>
-      <c r="Q24" s="295">
+      <c r="Q24" s="297">
         <v>-16.26</v>
       </c>
-      <c r="R24" s="289">
+      <c r="R24" s="291">
         <v>-10.13</v>
       </c>
-      <c r="S24" s="296">
+      <c r="S24" s="298">
         <v>-12.25</v>
       </c>
-      <c r="T24" s="290">
-        <v>-14.35</v>
+      <c r="T24" s="293">
+        <v>-17.14</v>
       </c>
     </row>
     <row r="25">
@@ -8860,7 +8972,7 @@
       <c r="C25" t="str">
         <v>688137</v>
       </c>
-      <c r="D25" s="309" t="str">
+      <c r="D25" s="302" t="str">
         <v>净买: 809.16万</v>
       </c>
       <c r="E25">
@@ -8878,38 +8990,38 @@
       <c r="I25" s="310">
         <v>15.54</v>
       </c>
-      <c r="J25" s="312">
+      <c r="J25" s="311">
         <v>13.21</v>
       </c>
-      <c r="K25" s="306">
+      <c r="K25" s="303">
         <v>11.95</v>
       </c>
-      <c r="L25" s="300">
+      <c r="L25" s="304">
         <v>9.95</v>
       </c>
-      <c r="M25" s="303">
+      <c r="M25" s="305">
         <v>6.85</v>
       </c>
-      <c r="N25" s="311">
+      <c r="N25" s="306">
         <v>6.78</v>
       </c>
-      <c r="O25" s="301">
+      <c r="O25" s="312">
         <v>13.58</v>
       </c>
-      <c r="P25" s="302">
+      <c r="P25" s="301">
         <v>14.61</v>
       </c>
-      <c r="Q25" s="307">
+      <c r="Q25" s="300">
         <v>16.47</v>
       </c>
-      <c r="R25" s="308">
+      <c r="R25" s="307">
         <v>23.92</v>
       </c>
-      <c r="S25" s="304">
+      <c r="S25" s="308">
         <v>15.3</v>
       </c>
-      <c r="T25" s="305">
-        <v>15.4</v>
+      <c r="T25" s="309">
+        <v>11.83</v>
       </c>
     </row>
     <row r="26">
@@ -8922,7 +9034,7 @@
       <c r="C26" t="str">
         <v>301408</v>
       </c>
-      <c r="D26" s="325" t="str">
+      <c r="D26" s="318" t="str">
         <v>净卖: -2207.20万</v>
       </c>
       <c r="E26">
@@ -8940,16 +9052,16 @@
       <c r="I26" s="314">
         <v>18.28</v>
       </c>
-      <c r="J26" s="317">
+      <c r="J26" s="315">
         <v>-5.37</v>
       </c>
-      <c r="K26" s="318">
+      <c r="K26" s="316">
         <v>-14.43</v>
       </c>
       <c r="L26" s="319">
         <v>-13.43</v>
       </c>
-      <c r="M26" s="323">
+      <c r="M26" s="317">
         <v>-12.24</v>
       </c>
       <c r="N26" s="320">
@@ -8958,20 +9070,20 @@
       <c r="O26" s="324">
         <v>-7.91</v>
       </c>
-      <c r="P26" s="321">
+      <c r="P26" s="325">
         <v>-4.69</v>
       </c>
-      <c r="Q26" s="313">
+      <c r="Q26" s="321">
         <v>-0.32</v>
       </c>
-      <c r="R26" s="315">
+      <c r="R26" s="313">
         <v>-8.55</v>
       </c>
       <c r="S26" s="322">
         <v>-11.88</v>
       </c>
-      <c r="T26" s="316">
-        <v>-19.63</v>
+      <c r="T26" s="323">
+        <v>-21.3</v>
       </c>
     </row>
     <row r="27">
@@ -8984,7 +9096,7 @@
       <c r="C27" t="str">
         <v>603598</v>
       </c>
-      <c r="D27" s="334" t="str">
+      <c r="D27" s="336" t="str">
         <v>净卖: -958.53万</v>
       </c>
       <c r="E27">
@@ -9002,38 +9114,38 @@
       <c r="I27" s="327">
         <v>0</v>
       </c>
-      <c r="J27" s="331">
+      <c r="J27" s="328">
         <v>-5.64</v>
       </c>
-      <c r="K27" s="328">
+      <c r="K27" s="329">
         <v>-1.1</v>
       </c>
-      <c r="L27" s="329">
+      <c r="L27" s="338">
         <v>1.88</v>
       </c>
-      <c r="M27" s="332">
+      <c r="M27" s="330">
         <v>4.9</v>
       </c>
-      <c r="N27" s="333">
+      <c r="N27" s="331">
         <v>3.33</v>
       </c>
-      <c r="O27" s="335">
+      <c r="O27" s="334">
         <v>1.33</v>
       </c>
-      <c r="P27" s="330">
+      <c r="P27" s="326">
         <v>-0.86</v>
       </c>
-      <c r="Q27" s="336">
+      <c r="Q27" s="332">
         <v>4.62</v>
       </c>
-      <c r="R27" s="337">
+      <c r="R27" s="335">
         <v>15.09</v>
       </c>
-      <c r="S27" s="338">
+      <c r="S27" s="333">
         <v>13.64</v>
       </c>
-      <c r="T27" s="326">
-        <v>-15.24</v>
+      <c r="T27" s="337">
+        <v>-19.08</v>
       </c>
     </row>
     <row r="28">
@@ -9046,7 +9158,7 @@
       <c r="C28" t="str">
         <v>920368</v>
       </c>
-      <c r="D28" s="346" t="str">
+      <c r="D28" s="340" t="str">
         <v>净买: 2785.37万</v>
       </c>
       <c r="E28">
@@ -9061,41 +9173,41 @@
       <c r="H28">
         <v>6.62</v>
       </c>
-      <c r="I28" s="347">
+      <c r="I28" s="351">
         <v>21.92</v>
       </c>
-      <c r="J28" s="348">
+      <c r="J28" s="341">
         <v>30.07</v>
       </c>
-      <c r="K28" s="345">
+      <c r="K28" s="348">
         <v>52.53</v>
       </c>
-      <c r="L28" s="342">
+      <c r="L28" s="349">
         <v>59.26</v>
       </c>
-      <c r="M28" s="349">
+      <c r="M28" s="342">
         <v>51.53</v>
       </c>
       <c r="N28" s="350">
         <v>48.42</v>
       </c>
-      <c r="O28" s="343">
+      <c r="O28" s="339">
         <v>50.72</v>
       </c>
-      <c r="P28" s="351">
+      <c r="P28" s="345">
         <v>78.13</v>
       </c>
-      <c r="Q28" s="339">
+      <c r="Q28" s="346">
         <v>61.84</v>
       </c>
-      <c r="R28" s="344">
+      <c r="R28" s="343">
         <v>41.93</v>
       </c>
-      <c r="S28" s="340">
+      <c r="S28" s="344">
         <v>52.17</v>
       </c>
-      <c r="T28" s="341">
-        <v>-2.9</v>
+      <c r="T28" s="347">
+        <v>-13.78</v>
       </c>
     </row>
     <row r="29">
@@ -9108,7 +9220,7 @@
       <c r="C29" t="str">
         <v>300017</v>
       </c>
-      <c r="D29" s="355" t="str">
+      <c r="D29" s="360" t="str">
         <v>净卖: -8231.84万</v>
       </c>
       <c r="E29">
@@ -9123,41 +9235,41 @@
       <c r="H29">
         <v>1.57</v>
       </c>
-      <c r="I29" s="363">
+      <c r="I29" s="358">
         <v>18.18</v>
       </c>
-      <c r="J29" s="364">
+      <c r="J29" s="353">
         <v>16.12</v>
       </c>
-      <c r="K29" s="360">
+      <c r="K29" s="359">
         <v>33.7</v>
       </c>
-      <c r="L29" s="361">
+      <c r="L29" s="354">
         <v>44.08</v>
       </c>
-      <c r="M29" s="356">
+      <c r="M29" s="361">
         <v>42.02</v>
       </c>
-      <c r="N29" s="354">
+      <c r="N29" s="355">
         <v>44.77</v>
       </c>
-      <c r="O29" s="352">
+      <c r="O29" s="356">
         <v>65.61</v>
       </c>
-      <c r="P29" s="357">
+      <c r="P29" s="362">
         <v>43.4</v>
       </c>
-      <c r="Q29" s="353">
+      <c r="Q29" s="363">
         <v>54.12</v>
       </c>
-      <c r="R29" s="358">
+      <c r="R29" s="357">
         <v>53.77</v>
       </c>
-      <c r="S29" s="359">
+      <c r="S29" s="364">
         <v>62.09</v>
       </c>
-      <c r="T29" s="362">
-        <v>54.2</v>
+      <c r="T29" s="352">
+        <v>52.66</v>
       </c>
     </row>
     <row r="30">
@@ -9170,7 +9282,7 @@
       <c r="C30" t="str">
         <v>603075</v>
       </c>
-      <c r="D30" s="371" t="str">
+      <c r="D30" s="366" t="str">
         <v>净卖: -1295.61万</v>
       </c>
       <c r="E30">
@@ -9185,41 +9297,41 @@
       <c r="H30">
         <v>-0.04</v>
       </c>
-      <c r="I30" s="369">
+      <c r="I30" s="376">
         <v>1.83</v>
       </c>
-      <c r="J30" s="373">
+      <c r="J30" s="367">
         <v>-4.09</v>
       </c>
-      <c r="K30" s="372">
+      <c r="K30" s="370">
         <v>-6.43</v>
       </c>
-      <c r="L30" s="374">
+      <c r="L30" s="371">
         <v>-7.11</v>
       </c>
-      <c r="M30" s="375">
+      <c r="M30" s="372">
         <v>-5.88</v>
       </c>
-      <c r="N30" s="370">
+      <c r="N30" s="373">
         <v>-7.63</v>
       </c>
-      <c r="O30" s="376">
+      <c r="O30" s="377">
         <v>-5.52</v>
       </c>
-      <c r="P30" s="365">
+      <c r="P30" s="368">
         <v>-4.65</v>
       </c>
-      <c r="Q30" s="366">
+      <c r="Q30" s="374">
         <v>-5.2</v>
       </c>
-      <c r="R30" s="377">
+      <c r="R30" s="365">
         <v>-5.72</v>
       </c>
-      <c r="S30" s="367">
+      <c r="S30" s="369">
         <v>-4.92</v>
       </c>
-      <c r="T30" s="368">
-        <v>-8.02</v>
+      <c r="T30" s="375">
+        <v>-6.12</v>
       </c>
     </row>
     <row r="31">
@@ -9232,7 +9344,7 @@
       <c r="C31" t="str">
         <v>920368</v>
       </c>
-      <c r="D31" s="388" t="str">
+      <c r="D31" s="390" t="str">
         <v>净卖: -476.30万</v>
       </c>
       <c r="E31">
@@ -9247,41 +9359,41 @@
       <c r="H31">
         <v>10.26</v>
       </c>
-      <c r="I31" s="381">
+      <c r="I31" s="378">
         <v>-3.25</v>
       </c>
       <c r="J31" s="384">
         <v>13.46</v>
       </c>
-      <c r="K31" s="387">
+      <c r="K31" s="385">
         <v>18.46</v>
       </c>
-      <c r="L31" s="389">
+      <c r="L31" s="379">
         <v>12.71</v>
       </c>
-      <c r="M31" s="390">
+      <c r="M31" s="380">
         <v>10.4</v>
       </c>
-      <c r="N31" s="378">
+      <c r="N31" s="386">
         <v>12.12</v>
       </c>
-      <c r="O31" s="385">
+      <c r="O31" s="388">
         <v>32.5</v>
       </c>
-      <c r="P31" s="379">
+      <c r="P31" s="381">
         <v>20.38</v>
       </c>
-      <c r="Q31" s="386">
+      <c r="Q31" s="382">
         <v>5.58</v>
       </c>
-      <c r="R31" s="382">
+      <c r="R31" s="383">
         <v>13.19</v>
       </c>
-      <c r="S31" s="383">
+      <c r="S31" s="387">
         <v>23.15</v>
       </c>
-      <c r="T31" s="380">
-        <v>-27.77</v>
+      <c r="T31" s="389">
+        <v>-35.87</v>
       </c>
     </row>
     <row r="32">
@@ -9294,7 +9406,7 @@
       <c r="C32" t="str">
         <v>600273</v>
       </c>
-      <c r="D32" s="403" t="str">
+      <c r="D32" s="395" t="str">
         <v>净卖: -3657.56万</v>
       </c>
       <c r="E32">
@@ -9309,41 +9421,41 @@
       <c r="H32">
         <v>3.89</v>
       </c>
-      <c r="I32" s="398">
+      <c r="I32" s="401">
         <v>5.92</v>
       </c>
-      <c r="J32" s="395">
+      <c r="J32" s="402">
         <v>2.96</v>
       </c>
-      <c r="K32" s="399">
+      <c r="K32" s="396">
         <v>-4.88</v>
       </c>
-      <c r="L32" s="396">
+      <c r="L32" s="397">
         <v>-3.05</v>
       </c>
-      <c r="M32" s="402">
+      <c r="M32" s="403">
         <v>-1.31</v>
       </c>
-      <c r="N32" s="400">
+      <c r="N32" s="398">
         <v>-4.18</v>
       </c>
       <c r="O32" s="391">
         <v>-1.74</v>
       </c>
-      <c r="P32" s="392">
+      <c r="P32" s="399">
         <v>-1.66</v>
       </c>
-      <c r="Q32" s="401">
+      <c r="Q32" s="393">
         <v>0.78</v>
       </c>
-      <c r="R32" s="397">
+      <c r="R32" s="392">
         <v>1.83</v>
       </c>
-      <c r="S32" s="393">
+      <c r="S32" s="394">
         <v>2.7</v>
       </c>
-      <c r="T32" s="394">
-        <v>-22.3</v>
+      <c r="T32" s="400">
+        <v>-22.82</v>
       </c>
     </row>
     <row r="33">
@@ -9356,7 +9468,7 @@
       <c r="C33" t="str">
         <v>300257</v>
       </c>
-      <c r="D33" s="406" t="str">
+      <c r="D33" s="412" t="str">
         <v>净卖: -2507.66万</v>
       </c>
       <c r="E33">
@@ -9371,142 +9483,132 @@
       <c r="H33">
         <v>2.76</v>
       </c>
-      <c r="I33" s="412">
+      <c r="I33" s="411">
         <v>16.77</v>
       </c>
-      <c r="J33" s="407">
+      <c r="J33" s="413">
         <v>17.59</v>
       </c>
-      <c r="K33" s="410">
+      <c r="K33" s="414">
         <v>16.46</v>
       </c>
-      <c r="L33" s="413">
+      <c r="L33" s="408">
         <v>7.35</v>
       </c>
-      <c r="M33" s="414">
+      <c r="M33" s="415">
         <v>14.56</v>
       </c>
-      <c r="N33" s="408">
+      <c r="N33" s="405">
         <v>8.23</v>
       </c>
-      <c r="O33" s="415">
+      <c r="O33" s="406">
         <v>8.64</v>
       </c>
-      <c r="P33" s="416">
+      <c r="P33" s="409">
         <v>8.67</v>
       </c>
-      <c r="Q33" s="404">
+      <c r="Q33" s="410">
         <v>5.17</v>
       </c>
-      <c r="R33" s="409">
+      <c r="R33" s="416">
         <v>1.33</v>
       </c>
-      <c r="S33" s="411">
+      <c r="S33" s="407">
         <v>1.8</v>
       </c>
-      <c r="T33" s="405">
-        <v>-1.33</v>
+      <c r="T33" s="404">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>纪录总数</v>
-      </c>
-      <c r="B34" t="str"/>
-      <c r="C34" t="str"/>
-      <c r="D34" t="str"/>
-      <c r="E34" t="str"/>
-      <c r="F34" t="str"/>
-      <c r="G34" t="str"/>
-      <c r="H34" t="str"/>
-      <c r="I34">
-        <v>32</v>
-      </c>
-      <c r="J34">
-        <v>32</v>
-      </c>
-      <c r="K34">
-        <v>32</v>
-      </c>
-      <c r="L34">
-        <v>32</v>
-      </c>
-      <c r="M34">
-        <v>32</v>
-      </c>
-      <c r="N34">
-        <v>32</v>
-      </c>
-      <c r="O34">
-        <v>32</v>
-      </c>
-      <c r="P34">
-        <v>32</v>
-      </c>
-      <c r="Q34">
-        <v>32</v>
-      </c>
-      <c r="R34">
-        <v>32</v>
-      </c>
-      <c r="S34">
-        <v>32</v>
-      </c>
-      <c r="T34">
-        <v>32</v>
+        <v>2026-04-22</v>
+      </c>
+      <c r="B34" t="str">
+        <v>百利科技</v>
+      </c>
+      <c r="C34" t="str">
+        <v>603959</v>
+      </c>
+      <c r="D34" s="418" t="str">
+        <v>净买: 674.52万</v>
+      </c>
+      <c r="E34">
+        <v>6.77</v>
+      </c>
+      <c r="F34">
+        <v>6.02</v>
+      </c>
+      <c r="G34">
+        <v>6.77</v>
+      </c>
+      <c r="H34">
+        <v>1.2</v>
+      </c>
+      <c r="I34" s="419">
+        <v>-11.08</v>
+      </c>
+      <c r="J34" s="420">
+        <v>-12.85</v>
+      </c>
+      <c r="K34" s="421">
+        <v>-21.57</v>
+      </c>
+      <c r="L34" t="str"/>
+      <c r="M34" t="str"/>
+      <c r="N34" t="str"/>
+      <c r="O34" t="str"/>
+      <c r="P34" t="str"/>
+      <c r="Q34" t="str"/>
+      <c r="R34" t="str"/>
+      <c r="S34" t="str"/>
+      <c r="T34" s="417">
+        <v>-21.57</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>上涨比例</v>
-      </c>
-      <c r="B35" t="str"/>
-      <c r="C35" t="str"/>
-      <c r="D35" t="str"/>
-      <c r="E35" t="str"/>
-      <c r="F35" t="str"/>
-      <c r="G35" t="str"/>
-      <c r="H35" t="str"/>
-      <c r="I35" s="419">
-        <v>68.75</v>
-      </c>
-      <c r="J35" s="420">
-        <v>71.88</v>
-      </c>
-      <c r="K35" s="422">
-        <v>68.75</v>
-      </c>
-      <c r="L35" s="423">
-        <v>68.75</v>
-      </c>
-      <c r="M35" s="424">
-        <v>68.75</v>
-      </c>
-      <c r="N35" s="425">
-        <v>71.88</v>
-      </c>
-      <c r="O35" s="426">
-        <v>71.88</v>
-      </c>
-      <c r="P35" s="417">
-        <v>62.5</v>
-      </c>
-      <c r="Q35" s="428">
-        <v>65.63</v>
-      </c>
-      <c r="R35" s="418">
-        <v>62.5</v>
-      </c>
-      <c r="S35" s="427">
-        <v>65.63</v>
-      </c>
-      <c r="T35" s="421">
-        <v>34.38</v>
-      </c>
+        <v>2026-04-24</v>
+      </c>
+      <c r="B35" t="str">
+        <v>百利科技</v>
+      </c>
+      <c r="C35" t="str">
+        <v>603959</v>
+      </c>
+      <c r="D35" s="423" t="str">
+        <v>净买: 1493.75万</v>
+      </c>
+      <c r="E35">
+        <v>5.66</v>
+      </c>
+      <c r="F35">
+        <v>5.31</v>
+      </c>
+      <c r="G35">
+        <v>5.66</v>
+      </c>
+      <c r="H35">
+        <v>-4.07</v>
+      </c>
+      <c r="I35" s="422">
+        <v>-6.18</v>
+      </c>
+      <c r="J35" t="str"/>
+      <c r="K35" t="str"/>
+      <c r="L35" t="str"/>
+      <c r="M35" t="str"/>
+      <c r="N35" t="str"/>
+      <c r="O35" t="str"/>
+      <c r="P35" t="str"/>
+      <c r="Q35" t="str"/>
+      <c r="R35" t="str"/>
+      <c r="S35" t="str"/>
+      <c r="T35" t="str"/>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>平均涨幅</v>
+        <v>纪录总数</v>
       </c>
       <c r="B36" t="str"/>
       <c r="C36" t="str"/>
@@ -9515,41 +9617,137 @@
       <c r="F36" t="str"/>
       <c r="G36" t="str"/>
       <c r="H36" t="str"/>
-      <c r="I36" s="432">
-        <v>8.56</v>
-      </c>
-      <c r="J36" s="433">
-        <v>10.13</v>
-      </c>
-      <c r="K36" s="437">
-        <v>11.47</v>
-      </c>
-      <c r="L36" s="431">
+      <c r="I36">
+        <v>34</v>
+      </c>
+      <c r="J36">
+        <v>33</v>
+      </c>
+      <c r="K36">
+        <v>33</v>
+      </c>
+      <c r="L36">
+        <v>32</v>
+      </c>
+      <c r="M36">
+        <v>32</v>
+      </c>
+      <c r="N36">
+        <v>32</v>
+      </c>
+      <c r="O36">
+        <v>32</v>
+      </c>
+      <c r="P36">
+        <v>32</v>
+      </c>
+      <c r="Q36">
+        <v>32</v>
+      </c>
+      <c r="R36">
+        <v>32</v>
+      </c>
+      <c r="S36">
+        <v>32</v>
+      </c>
+      <c r="T36">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>上涨比例</v>
+      </c>
+      <c r="B37" t="str"/>
+      <c r="C37" t="str"/>
+      <c r="D37" t="str"/>
+      <c r="E37" t="str"/>
+      <c r="F37" t="str"/>
+      <c r="G37" t="str"/>
+      <c r="H37" t="str"/>
+      <c r="I37" s="426">
+        <v>64.71</v>
+      </c>
+      <c r="J37" s="427">
+        <v>69.7</v>
+      </c>
+      <c r="K37" s="431">
+        <v>66.67</v>
+      </c>
+      <c r="L37" s="434">
+        <v>68.75</v>
+      </c>
+      <c r="M37" s="429">
+        <v>68.75</v>
+      </c>
+      <c r="N37" s="435">
+        <v>71.88</v>
+      </c>
+      <c r="O37" s="432">
+        <v>71.88</v>
+      </c>
+      <c r="P37" s="424">
+        <v>62.5</v>
+      </c>
+      <c r="Q37" s="433">
+        <v>65.63</v>
+      </c>
+      <c r="R37" s="428">
+        <v>62.5</v>
+      </c>
+      <c r="S37" s="425">
+        <v>65.63</v>
+      </c>
+      <c r="T37" s="430">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>平均涨幅</v>
+      </c>
+      <c r="B38" t="str"/>
+      <c r="C38" t="str"/>
+      <c r="D38" t="str"/>
+      <c r="E38" t="str"/>
+      <c r="F38" t="str"/>
+      <c r="G38" t="str"/>
+      <c r="H38" t="str"/>
+      <c r="I38" s="439">
+        <v>7.55</v>
+      </c>
+      <c r="J38" s="442">
+        <v>9.44</v>
+      </c>
+      <c r="K38" s="444">
+        <v>10.47</v>
+      </c>
+      <c r="L38" s="440">
         <v>10.84</v>
       </c>
-      <c r="M36" s="438">
+      <c r="M38" s="445">
         <v>11.29</v>
       </c>
-      <c r="N36" s="439">
+      <c r="N38" s="446">
         <v>10.99</v>
       </c>
-      <c r="O36" s="434">
+      <c r="O38" s="436">
         <v>12.53</v>
       </c>
-      <c r="P36" s="435">
+      <c r="P38" s="437">
         <v>11.98</v>
       </c>
-      <c r="Q36" s="436">
+      <c r="Q38" s="447">
         <v>10.83</v>
       </c>
-      <c r="R36" s="429">
+      <c r="R38" s="438">
         <v>10.67</v>
       </c>
-      <c r="S36" s="430">
+      <c r="S38" s="441">
         <v>10.08</v>
       </c>
-      <c r="T36" s="440">
-        <v>5.87</v>
+      <c r="T38" s="443">
+        <v>2.57</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/大小说家/index.xlsx
+++ b/youzi/大小说家/index.xlsx
@@ -39,6 +39,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7ECA90"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF83CC93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1E8337"/>
         <bgColor/>
       </patternFill>
@@ -51,13 +81,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE46370"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF7ECA90"/>
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -69,49 +111,1177 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9EA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4352"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5BBB71"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B25E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBE3C4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEFF0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB9199"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CDD1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8E1C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91D2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15663"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF3F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDE4C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC12837"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF82CB93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEAF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -123,6 +1293,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -135,7 +1311,1081 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91D2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBD5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF59BB6F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8336"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD75"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7833"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3DAF57"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF35AC50"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAEFDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4453"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBD6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3948"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB766"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF37AD52"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF73C586"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7E1C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -147,7 +2397,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
+        <fgColor rgb="FF4BB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB4E0BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8790"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2DA949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7BC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -159,6 +2541,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -177,31 +2565,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF24993F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -213,169 +2577,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9EA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4352"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA6"/>
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -387,2311 +2685,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B25E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBE3C4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEFF0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB9199"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CDD1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8E1C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91D2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15663"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF3F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDE4C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BABF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91D2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEB9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEB9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEB9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFEBD5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7833"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF59BB6F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3DAF57"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD75"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8336"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF35AC50"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAEFDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFEBD6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3948"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4453"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB766"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF37AD52"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF73C586"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB4E0BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2DA949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7BC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4BB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8790"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAFDFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -7546,7 +7546,7 @@
       <c r="C2" t="str">
         <v>603319</v>
       </c>
-      <c r="D2" s="6" t="str">
+      <c r="D2" s="1" t="str">
         <v>净卖: -4050.11万</v>
       </c>
       <c r="E2">
@@ -7561,41 +7561,41 @@
       <c r="H2">
         <v>-2.13</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2" s="6">
         <v>-8.04</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="7">
         <v>-7</v>
       </c>
-      <c r="K2" s="9">
+      <c r="K2" s="2">
         <v>-0.47</v>
       </c>
       <c r="L2" s="11">
         <v>3.68</v>
       </c>
-      <c r="M2" s="12">
+      <c r="M2" s="8">
         <v>10.89</v>
       </c>
-      <c r="N2" s="3">
+      <c r="N2" s="9">
         <v>3.84</v>
       </c>
-      <c r="O2" s="10">
+      <c r="O2" s="13">
         <v>6.4</v>
       </c>
-      <c r="P2" s="7">
+      <c r="P2" s="3">
         <v>7.52</v>
       </c>
       <c r="Q2" s="4">
         <v>-2.98</v>
       </c>
-      <c r="R2" s="5">
+      <c r="R2" s="12">
         <v>2.88</v>
       </c>
-      <c r="S2" s="13">
+      <c r="S2" s="10">
         <v>6.19</v>
       </c>
-      <c r="T2" s="8">
-        <v>-2.9</v>
+      <c r="T2" s="5">
+        <v>-2.88</v>
       </c>
     </row>
     <row r="3">
@@ -7608,7 +7608,7 @@
       <c r="C3" t="str">
         <v>002923</v>
       </c>
-      <c r="D3" s="16" t="str">
+      <c r="D3" s="19" t="str">
         <v>净卖: -1342.21万</v>
       </c>
       <c r="E3">
@@ -7623,41 +7623,41 @@
       <c r="H3">
         <v>2.17</v>
       </c>
-      <c r="I3" s="25">
+      <c r="I3" s="15">
         <v>7.69</v>
       </c>
-      <c r="J3" s="17">
+      <c r="J3" s="25">
         <v>17.63</v>
       </c>
-      <c r="K3" s="18">
+      <c r="K3" s="16">
         <v>5.88</v>
       </c>
-      <c r="L3" s="19">
+      <c r="L3" s="20">
         <v>-4.3</v>
       </c>
       <c r="M3" s="21">
         <v>-13.87</v>
       </c>
-      <c r="N3" s="22">
+      <c r="N3" s="17">
         <v>-11.45</v>
       </c>
-      <c r="O3" s="23">
+      <c r="O3" s="22">
         <v>-15.08</v>
       </c>
-      <c r="P3" s="26">
+      <c r="P3" s="23">
         <v>-14.66</v>
       </c>
-      <c r="Q3" s="14">
+      <c r="Q3" s="26">
         <v>-12.84</v>
       </c>
-      <c r="R3" s="20">
+      <c r="R3" s="24">
         <v>-21.56</v>
       </c>
-      <c r="S3" s="24">
+      <c r="S3" s="14">
         <v>-24.59</v>
       </c>
-      <c r="T3" s="15">
-        <v>-26.17</v>
+      <c r="T3" s="18">
+        <v>-24.05</v>
       </c>
     </row>
     <row r="4">
@@ -7670,7 +7670,7 @@
       <c r="C4" t="str">
         <v>002564</v>
       </c>
-      <c r="D4" s="29" t="str">
+      <c r="D4" s="33" t="str">
         <v>净买: 1737.48万</v>
       </c>
       <c r="E4">
@@ -7685,41 +7685,41 @@
       <c r="H4">
         <v>-1.38</v>
       </c>
-      <c r="I4" s="37">
+      <c r="I4" s="34">
         <v>11.55</v>
       </c>
-      <c r="J4" s="33">
+      <c r="J4" s="27">
         <v>2.39</v>
       </c>
-      <c r="K4" s="34">
+      <c r="K4" s="36">
         <v>12.55</v>
       </c>
-      <c r="L4" s="38">
+      <c r="L4" s="28">
         <v>5.58</v>
       </c>
-      <c r="M4" s="35">
+      <c r="M4" s="29">
         <v>16.14</v>
       </c>
-      <c r="N4" s="39">
+      <c r="N4" s="37">
         <v>21.51</v>
       </c>
       <c r="O4" s="30">
         <v>16.14</v>
       </c>
-      <c r="P4" s="36">
+      <c r="P4" s="38">
         <v>19.92</v>
       </c>
-      <c r="Q4" s="31">
+      <c r="Q4" s="35">
         <v>20.72</v>
       </c>
-      <c r="R4" s="32">
+      <c r="R4" s="31">
         <v>15.94</v>
       </c>
-      <c r="S4" s="27">
+      <c r="S4" s="32">
         <v>8.96</v>
       </c>
-      <c r="T4" s="28">
-        <v>24.1</v>
+      <c r="T4" s="39">
+        <v>26.69</v>
       </c>
     </row>
     <row r="5">
@@ -7732,7 +7732,7 @@
       <c r="C5" t="str">
         <v>600735</v>
       </c>
-      <c r="D5" s="43" t="str">
+      <c r="D5" s="47" t="str">
         <v>净买: 1155.67万</v>
       </c>
       <c r="E5">
@@ -7753,22 +7753,22 @@
       <c r="J5" s="41">
         <v>8.84</v>
       </c>
-      <c r="K5" s="51">
+      <c r="K5" s="42">
         <v>7.48</v>
       </c>
-      <c r="L5" s="44">
+      <c r="L5" s="45">
         <v>4.63</v>
       </c>
-      <c r="M5" s="45">
+      <c r="M5" s="48">
         <v>5.71</v>
       </c>
-      <c r="N5" s="46">
+      <c r="N5" s="51">
         <v>11.16</v>
       </c>
-      <c r="O5" s="47">
+      <c r="O5" s="43">
         <v>9.66</v>
       </c>
-      <c r="P5" s="48">
+      <c r="P5" s="44">
         <v>6.8</v>
       </c>
       <c r="Q5" s="49">
@@ -7780,8 +7780,8 @@
       <c r="S5" s="52">
         <v>10.07</v>
       </c>
-      <c r="T5" s="42">
-        <v>-8.44</v>
+      <c r="T5" s="46">
+        <v>-3.81</v>
       </c>
     </row>
     <row r="6">
@@ -7794,7 +7794,7 @@
       <c r="C6" t="str">
         <v>600735</v>
       </c>
-      <c r="D6" s="55" t="str">
+      <c r="D6" s="57" t="str">
         <v>净卖: -1139.95万</v>
       </c>
       <c r="E6">
@@ -7809,41 +7809,41 @@
       <c r="H6">
         <v>-5.01</v>
       </c>
-      <c r="I6" s="56">
+      <c r="I6" s="58">
         <v>5.4</v>
       </c>
-      <c r="J6" s="63">
+      <c r="J6" s="53">
         <v>4.08</v>
       </c>
-      <c r="K6" s="64">
+      <c r="K6" s="62">
         <v>1.32</v>
       </c>
-      <c r="L6" s="57">
+      <c r="L6" s="59">
         <v>2.37</v>
       </c>
-      <c r="M6" s="58">
+      <c r="M6" s="54">
         <v>7.64</v>
       </c>
-      <c r="N6" s="60">
+      <c r="N6" s="63">
         <v>6.19</v>
       </c>
-      <c r="O6" s="59">
+      <c r="O6" s="55">
         <v>3.43</v>
       </c>
-      <c r="P6" s="65">
+      <c r="P6" s="56">
         <v>8.7</v>
       </c>
-      <c r="Q6" s="53">
+      <c r="Q6" s="64">
         <v>10.28</v>
       </c>
-      <c r="R6" s="54">
+      <c r="R6" s="65">
         <v>6.59</v>
       </c>
-      <c r="S6" s="61">
+      <c r="S6" s="60">
         <v>3.43</v>
       </c>
-      <c r="T6" s="62">
-        <v>-11.33</v>
+      <c r="T6" s="61">
+        <v>-6.85</v>
       </c>
     </row>
     <row r="7">
@@ -7856,7 +7856,7 @@
       <c r="C7" t="str">
         <v>002365</v>
       </c>
-      <c r="D7" s="66" t="str">
+      <c r="D7" s="67" t="str">
         <v>净卖: -2887.03万</v>
       </c>
       <c r="E7">
@@ -7871,41 +7871,41 @@
       <c r="H7">
         <v>3.76</v>
       </c>
-      <c r="I7" s="76">
+      <c r="I7" s="71">
         <v>-4.32</v>
       </c>
-      <c r="J7" s="67">
+      <c r="J7" s="68">
         <v>5.25</v>
       </c>
-      <c r="K7" s="77">
+      <c r="K7" s="69">
         <v>15.76</v>
       </c>
-      <c r="L7" s="68">
+      <c r="L7" s="75">
         <v>27.33</v>
       </c>
-      <c r="M7" s="72">
+      <c r="M7" s="76">
         <v>35.58</v>
       </c>
-      <c r="N7" s="71">
+      <c r="N7" s="70">
         <v>40.03</v>
       </c>
-      <c r="O7" s="73">
+      <c r="O7" s="72">
         <v>54.03</v>
       </c>
-      <c r="P7" s="69">
+      <c r="P7" s="73">
         <v>38.65</v>
       </c>
-      <c r="Q7" s="70">
+      <c r="Q7" s="74">
         <v>24.77</v>
       </c>
-      <c r="R7" s="78">
+      <c r="R7" s="77">
         <v>28.27</v>
       </c>
-      <c r="S7" s="74">
+      <c r="S7" s="78">
         <v>22.51</v>
       </c>
-      <c r="T7" s="75">
-        <v>-19.2</v>
+      <c r="T7" s="66">
+        <v>-17.76</v>
       </c>
     </row>
     <row r="8">
@@ -7936,38 +7936,38 @@
       <c r="I8" s="83">
         <v>8.09</v>
       </c>
-      <c r="J8" s="87">
+      <c r="J8" s="89">
         <v>7.12</v>
       </c>
-      <c r="K8" s="81">
+      <c r="K8" s="84">
         <v>17.86</v>
       </c>
-      <c r="L8" s="90">
+      <c r="L8" s="87">
         <v>29.63</v>
       </c>
-      <c r="M8" s="84">
+      <c r="M8" s="88">
         <v>16.68</v>
       </c>
-      <c r="N8" s="91">
+      <c r="N8" s="80">
         <v>5.02</v>
       </c>
-      <c r="O8" s="88">
+      <c r="O8" s="85">
         <v>0.38</v>
       </c>
-      <c r="P8" s="79">
+      <c r="P8" s="81">
         <v>2.75</v>
       </c>
-      <c r="Q8" s="82">
+      <c r="Q8" s="90">
         <v>2.05</v>
       </c>
-      <c r="R8" s="80">
+      <c r="R8" s="91">
         <v>-0.32</v>
       </c>
-      <c r="S8" s="85">
+      <c r="S8" s="82">
         <v>-1.57</v>
       </c>
-      <c r="T8" s="89">
-        <v>8.09</v>
+      <c r="T8" s="79">
+        <v>5.34</v>
       </c>
     </row>
     <row r="9">
@@ -7980,7 +7980,7 @@
       <c r="C9" t="str">
         <v>003029</v>
       </c>
-      <c r="D9" s="99" t="str">
+      <c r="D9" s="104" t="str">
         <v>净卖: -1441.18万</v>
       </c>
       <c r="E9">
@@ -7998,38 +7998,38 @@
       <c r="I9" s="100">
         <v>9.96</v>
       </c>
-      <c r="J9" s="92">
+      <c r="J9" s="97">
         <v>14.48</v>
       </c>
-      <c r="K9" s="96">
+      <c r="K9" s="92">
         <v>8.49</v>
       </c>
-      <c r="L9" s="97">
+      <c r="L9" s="98">
         <v>8.99</v>
       </c>
-      <c r="M9" s="101">
+      <c r="M9" s="93">
         <v>7.77</v>
       </c>
-      <c r="N9" s="93">
+      <c r="N9" s="94">
         <v>2.72</v>
       </c>
-      <c r="O9" s="102">
+      <c r="O9" s="101">
         <v>1.22</v>
       </c>
-      <c r="P9" s="94">
+      <c r="P9" s="95">
         <v>-1.33</v>
       </c>
       <c r="Q9" s="103">
         <v>-1.65</v>
       </c>
-      <c r="R9" s="95">
+      <c r="R9" s="99">
         <v>-1.04</v>
       </c>
-      <c r="S9" s="104">
+      <c r="S9" s="102">
         <v>-2.01</v>
       </c>
-      <c r="T9" s="98">
-        <v>-24.51</v>
+      <c r="T9" s="96">
+        <v>-23.75</v>
       </c>
     </row>
     <row r="10">
@@ -8042,7 +8042,7 @@
       <c r="C10" t="str">
         <v>301486</v>
       </c>
-      <c r="D10" s="117" t="str">
+      <c r="D10" s="114" t="str">
         <v>净买: 2150.96万</v>
       </c>
       <c r="E10">
@@ -8057,41 +8057,41 @@
       <c r="H10">
         <v>1.79</v>
       </c>
-      <c r="I10" s="105">
+      <c r="I10" s="115">
         <v>17.9</v>
       </c>
-      <c r="J10" s="107">
+      <c r="J10" s="109">
         <v>21.2</v>
       </c>
-      <c r="K10" s="108">
+      <c r="K10" s="110">
         <v>12.29</v>
       </c>
       <c r="L10" s="111">
         <v>14.55</v>
       </c>
-      <c r="M10" s="115">
+      <c r="M10" s="112">
         <v>21.65</v>
       </c>
-      <c r="N10" s="109">
+      <c r="N10" s="116">
         <v>15.36</v>
       </c>
-      <c r="O10" s="112">
+      <c r="O10" s="106">
         <v>9.81</v>
       </c>
-      <c r="P10" s="106">
+      <c r="P10" s="117">
         <v>10.06</v>
       </c>
-      <c r="Q10" s="110">
+      <c r="Q10" s="105">
         <v>17.68</v>
       </c>
-      <c r="R10" s="116">
+      <c r="R10" s="107">
         <v>24.45</v>
       </c>
       <c r="S10" s="113">
         <v>20.16</v>
       </c>
-      <c r="T10" s="114">
-        <v>152.02</v>
+      <c r="T10" s="108">
+        <v>169.31</v>
       </c>
     </row>
     <row r="11">
@@ -8104,7 +8104,7 @@
       <c r="C11" t="str">
         <v>002052</v>
       </c>
-      <c r="D11" s="125" t="str">
+      <c r="D11" s="129" t="str">
         <v>净卖: -1505.16万</v>
       </c>
       <c r="E11">
@@ -8119,41 +8119,41 @@
       <c r="H11">
         <v>10.03</v>
       </c>
-      <c r="I11" s="129">
+      <c r="I11" s="120">
         <v>0</v>
       </c>
-      <c r="J11" s="118">
+      <c r="J11" s="125">
         <v>4.18</v>
       </c>
-      <c r="K11" s="130">
+      <c r="K11" s="126">
         <v>14.59</v>
       </c>
       <c r="L11" s="121">
         <v>26.06</v>
       </c>
-      <c r="M11" s="126">
+      <c r="M11" s="118">
         <v>38.68</v>
       </c>
-      <c r="N11" s="119">
+      <c r="N11" s="122">
         <v>44.38</v>
       </c>
-      <c r="O11" s="120">
+      <c r="O11" s="127">
         <v>45.82</v>
       </c>
-      <c r="P11" s="122">
+      <c r="P11" s="130">
         <v>53.88</v>
       </c>
-      <c r="Q11" s="127">
+      <c r="Q11" s="123">
         <v>45.36</v>
       </c>
-      <c r="R11" s="123">
+      <c r="R11" s="119">
         <v>34.42</v>
       </c>
-      <c r="S11" s="128">
+      <c r="S11" s="124">
         <v>39.06</v>
       </c>
-      <c r="T11" s="124">
-        <v>-24.77</v>
+      <c r="T11" s="128">
+        <v>-25.76</v>
       </c>
     </row>
     <row r="12">
@@ -8166,7 +8166,7 @@
       <c r="C12" t="str">
         <v>430476</v>
       </c>
-      <c r="D12" s="132" t="str">
+      <c r="D12" s="136" t="str">
         <v>净买: 566.61万</v>
       </c>
       <c r="E12">
@@ -8181,37 +8181,37 @@
       <c r="H12">
         <v>2.2</v>
       </c>
-      <c r="I12" s="137">
+      <c r="I12" s="132">
         <v>27.17</v>
       </c>
-      <c r="J12" s="143">
+      <c r="J12" s="137">
         <v>65.32</v>
       </c>
       <c r="K12" s="133">
         <v>65.69</v>
       </c>
-      <c r="L12" s="139">
+      <c r="L12" s="142">
         <v>47.53</v>
       </c>
-      <c r="M12" s="134">
+      <c r="M12" s="143">
         <v>34.9</v>
       </c>
-      <c r="N12" s="140">
+      <c r="N12" s="138">
         <v>37.51</v>
       </c>
-      <c r="O12" s="138">
+      <c r="O12" s="134">
         <v>35.45</v>
       </c>
-      <c r="P12" s="135">
+      <c r="P12" s="139">
         <v>35.86</v>
       </c>
-      <c r="Q12" s="141">
+      <c r="Q12" s="140">
         <v>29.23</v>
       </c>
-      <c r="R12" s="142">
+      <c r="R12" s="141">
         <v>29.87</v>
       </c>
-      <c r="S12" s="136">
+      <c r="S12" s="135">
         <v>29.96</v>
       </c>
       <c r="T12" s="131">
@@ -8228,7 +8228,7 @@
       <c r="C13" t="str">
         <v>871981</v>
       </c>
-      <c r="D13" s="156" t="str">
+      <c r="D13" s="148" t="str">
         <v>净买: 779.65万</v>
       </c>
       <c r="E13">
@@ -8243,40 +8243,40 @@
       <c r="H13">
         <v>10.55</v>
       </c>
-      <c r="I13" s="150">
+      <c r="I13" s="149">
         <v>17.58</v>
       </c>
-      <c r="J13" s="151">
+      <c r="J13" s="155">
         <v>17.95</v>
       </c>
-      <c r="K13" s="152">
+      <c r="K13" s="150">
         <v>13.64</v>
       </c>
-      <c r="L13" s="153">
+      <c r="L13" s="151">
         <v>14.65</v>
       </c>
-      <c r="M13" s="144">
+      <c r="M13" s="156">
         <v>17.15</v>
       </c>
-      <c r="N13" s="145">
+      <c r="N13" s="154">
         <v>11.72</v>
       </c>
-      <c r="O13" s="147">
+      <c r="O13" s="144">
         <v>6.52</v>
       </c>
-      <c r="P13" s="154">
+      <c r="P13" s="145">
         <v>0.28</v>
       </c>
-      <c r="Q13" s="146">
+      <c r="Q13" s="152">
         <v>1.84</v>
       </c>
-      <c r="R13" s="155">
+      <c r="R13" s="153">
         <v>-1.52</v>
       </c>
-      <c r="S13" s="148">
+      <c r="S13" s="146">
         <v>0.2</v>
       </c>
-      <c r="T13" s="149">
+      <c r="T13" s="147">
         <v>-6.54</v>
       </c>
     </row>
@@ -8305,40 +8305,40 @@
       <c r="H14">
         <v>7.39</v>
       </c>
-      <c r="I14" s="165">
+      <c r="I14" s="167">
         <v>-6.58</v>
       </c>
-      <c r="J14" s="161">
+      <c r="J14" s="160">
         <v>-10</v>
       </c>
-      <c r="K14" s="166">
+      <c r="K14" s="161">
         <v>-9.2</v>
       </c>
-      <c r="L14" s="167">
+      <c r="L14" s="168">
         <v>-7.22</v>
       </c>
-      <c r="M14" s="162">
+      <c r="M14" s="169">
         <v>-11.52</v>
       </c>
-      <c r="N14" s="158">
+      <c r="N14" s="157">
         <v>-15.64</v>
       </c>
-      <c r="O14" s="168">
+      <c r="O14" s="165">
         <v>-20.58</v>
       </c>
-      <c r="P14" s="169">
+      <c r="P14" s="166">
         <v>-19.34</v>
       </c>
-      <c r="Q14" s="157">
+      <c r="Q14" s="162">
         <v>-22</v>
       </c>
-      <c r="R14" s="163">
+      <c r="R14" s="158">
         <v>-20.64</v>
       </c>
-      <c r="S14" s="159">
+      <c r="S14" s="163">
         <v>-21.32</v>
       </c>
-      <c r="T14" s="160">
+      <c r="T14" s="159">
         <v>-25.98</v>
       </c>
     </row>
@@ -8352,7 +8352,7 @@
       <c r="C15" t="str">
         <v>301389</v>
       </c>
-      <c r="D15" s="180" t="str">
+      <c r="D15" s="177" t="str">
         <v>净买: 4127.06万</v>
       </c>
       <c r="E15">
@@ -8367,41 +8367,41 @@
       <c r="H15">
         <v>0.95</v>
       </c>
-      <c r="I15" s="172">
+      <c r="I15" s="178">
         <v>18.87</v>
       </c>
-      <c r="J15" s="181">
+      <c r="J15" s="170">
         <v>42.65</v>
       </c>
-      <c r="K15" s="176">
+      <c r="K15" s="171">
         <v>49.96</v>
       </c>
-      <c r="L15" s="173">
+      <c r="L15" s="179">
         <v>46.52</v>
       </c>
-      <c r="M15" s="174">
+      <c r="M15" s="180">
         <v>28.73</v>
       </c>
-      <c r="N15" s="177">
+      <c r="N15" s="181">
         <v>24.55</v>
       </c>
-      <c r="O15" s="175">
+      <c r="O15" s="172">
         <v>17.98</v>
       </c>
-      <c r="P15" s="178">
+      <c r="P15" s="182">
         <v>30.5</v>
       </c>
-      <c r="Q15" s="182">
+      <c r="Q15" s="173">
         <v>23.88</v>
       </c>
-      <c r="R15" s="170">
+      <c r="R15" s="174">
         <v>19.89</v>
       </c>
-      <c r="S15" s="171">
+      <c r="S15" s="175">
         <v>21.91</v>
       </c>
-      <c r="T15" s="179">
-        <v>13.93</v>
+      <c r="T15" s="176">
+        <v>20.46</v>
       </c>
     </row>
     <row r="16">
@@ -8414,7 +8414,7 @@
       <c r="C16" t="str">
         <v>301389</v>
       </c>
-      <c r="D16" s="191" t="str">
+      <c r="D16" s="193" t="str">
         <v>净买: 932.40万</v>
       </c>
       <c r="E16">
@@ -8429,7 +8429,7 @@
       <c r="H16">
         <v>-5.75</v>
       </c>
-      <c r="I16" s="189">
+      <c r="I16" s="194">
         <v>27.33</v>
       </c>
       <c r="J16" s="190">
@@ -8438,32 +8438,32 @@
       <c r="K16" s="195">
         <v>30.79</v>
       </c>
-      <c r="L16" s="192">
+      <c r="L16" s="191">
         <v>14.91</v>
       </c>
-      <c r="M16" s="184">
+      <c r="M16" s="183">
         <v>11.18</v>
       </c>
-      <c r="N16" s="185">
+      <c r="N16" s="187">
         <v>5.32</v>
       </c>
-      <c r="O16" s="186">
+      <c r="O16" s="188">
         <v>16.49</v>
       </c>
-      <c r="P16" s="193">
+      <c r="P16" s="189">
         <v>10.58</v>
       </c>
-      <c r="Q16" s="194">
+      <c r="Q16" s="184">
         <v>7.02</v>
       </c>
-      <c r="R16" s="187">
+      <c r="R16" s="185">
         <v>8.82</v>
       </c>
-      <c r="S16" s="188">
+      <c r="S16" s="186">
         <v>15.05</v>
       </c>
-      <c r="T16" s="183">
-        <v>1.7</v>
+      <c r="T16" s="192">
+        <v>7.53</v>
       </c>
     </row>
     <row r="17">
@@ -8476,7 +8476,7 @@
       <c r="C17" t="str">
         <v>300450</v>
       </c>
-      <c r="D17" s="199" t="str">
+      <c r="D17" s="202" t="str">
         <v>净卖: -4644.14万</v>
       </c>
       <c r="E17">
@@ -8491,41 +8491,41 @@
       <c r="H17">
         <v>5.71</v>
       </c>
-      <c r="I17" s="208">
+      <c r="I17" s="203">
         <v>13.52</v>
       </c>
-      <c r="J17" s="204">
+      <c r="J17" s="208">
         <v>30.12</v>
       </c>
-      <c r="K17" s="200">
+      <c r="K17" s="205">
         <v>40.03</v>
       </c>
-      <c r="L17" s="205">
+      <c r="L17" s="201">
         <v>40.54</v>
       </c>
-      <c r="M17" s="206">
+      <c r="M17" s="196">
         <v>43.32</v>
       </c>
-      <c r="N17" s="196">
+      <c r="N17" s="204">
         <v>71.99</v>
       </c>
-      <c r="O17" s="201">
+      <c r="O17" s="197">
         <v>83.47</v>
       </c>
-      <c r="P17" s="202">
+      <c r="P17" s="206">
         <v>79.22</v>
       </c>
-      <c r="Q17" s="197">
+      <c r="Q17" s="207">
         <v>87.37</v>
       </c>
-      <c r="R17" s="203">
+      <c r="R17" s="198">
         <v>92.23</v>
       </c>
-      <c r="S17" s="198">
+      <c r="S17" s="199">
         <v>75.19</v>
       </c>
-      <c r="T17" s="207">
-        <v>82.1</v>
+      <c r="T17" s="200">
+        <v>83.6</v>
       </c>
     </row>
     <row r="18">
@@ -8538,7 +8538,7 @@
       <c r="C18" t="str">
         <v>301389</v>
       </c>
-      <c r="D18" s="216" t="str">
+      <c r="D18" s="212" t="str">
         <v>净卖: -3733.12万</v>
       </c>
       <c r="E18">
@@ -8553,41 +8553,41 @@
       <c r="H18">
         <v>2.9</v>
       </c>
-      <c r="I18" s="220">
+      <c r="I18" s="210">
         <v>-5.04</v>
       </c>
-      <c r="J18" s="217">
+      <c r="J18" s="214">
         <v>-16.57</v>
       </c>
-      <c r="K18" s="209">
+      <c r="K18" s="218">
         <v>-19.28</v>
       </c>
-      <c r="L18" s="218">
+      <c r="L18" s="219">
         <v>-23.54</v>
       </c>
-      <c r="M18" s="214">
+      <c r="M18" s="220">
         <v>-15.42</v>
       </c>
-      <c r="N18" s="210">
+      <c r="N18" s="215">
         <v>-19.72</v>
       </c>
-      <c r="O18" s="215">
+      <c r="O18" s="213">
         <v>-22.3</v>
       </c>
-      <c r="P18" s="211">
+      <c r="P18" s="216">
         <v>-20.99</v>
       </c>
       <c r="Q18" s="221">
         <v>-16.47</v>
       </c>
-      <c r="R18" s="212">
+      <c r="R18" s="209">
         <v>-13.65</v>
       </c>
-      <c r="S18" s="213">
+      <c r="S18" s="217">
         <v>-15.93</v>
       </c>
-      <c r="T18" s="219">
-        <v>-26.16</v>
+      <c r="T18" s="211">
+        <v>-21.93</v>
       </c>
     </row>
     <row r="19">
@@ -8600,7 +8600,7 @@
       <c r="C19" t="str">
         <v>833580</v>
       </c>
-      <c r="D19" s="227" t="str">
+      <c r="D19" s="225" t="str">
         <v>净买: 656.67万</v>
       </c>
       <c r="E19">
@@ -8615,40 +8615,40 @@
       <c r="H19">
         <v>-1.6</v>
       </c>
-      <c r="I19" s="228">
+      <c r="I19" s="232">
         <v>32.07</v>
       </c>
-      <c r="J19" s="223">
+      <c r="J19" s="227">
         <v>19.86</v>
       </c>
-      <c r="K19" s="232">
+      <c r="K19" s="233">
         <v>10.83</v>
       </c>
-      <c r="L19" s="229">
+      <c r="L19" s="228">
         <v>7.1</v>
       </c>
-      <c r="M19" s="233">
+      <c r="M19" s="226">
         <v>12.21</v>
       </c>
-      <c r="N19" s="224">
+      <c r="N19" s="234">
         <v>19.07</v>
       </c>
-      <c r="O19" s="234">
+      <c r="O19" s="222">
         <v>16.13</v>
       </c>
-      <c r="P19" s="225">
+      <c r="P19" s="229">
         <v>10.95</v>
       </c>
-      <c r="Q19" s="222">
+      <c r="Q19" s="230">
         <v>8.72</v>
       </c>
-      <c r="R19" s="226">
+      <c r="R19" s="231">
         <v>8.78</v>
       </c>
-      <c r="S19" s="230">
+      <c r="S19" s="223">
         <v>9.81</v>
       </c>
-      <c r="T19" s="231">
+      <c r="T19" s="224">
         <v>-2.53</v>
       </c>
     </row>
@@ -8662,7 +8662,7 @@
       <c r="C20" t="str">
         <v>833580</v>
       </c>
-      <c r="D20" s="237" t="str">
+      <c r="D20" s="247" t="str">
         <v>净卖: -782.72万</v>
       </c>
       <c r="E20">
@@ -8677,40 +8677,40 @@
       <c r="H20">
         <v>8.88</v>
       </c>
-      <c r="I20" s="235">
+      <c r="I20" s="246">
         <v>-16.65</v>
       </c>
-      <c r="J20" s="238">
+      <c r="J20" s="235">
         <v>-22.93</v>
       </c>
-      <c r="K20" s="241">
+      <c r="K20" s="238">
         <v>-25.52</v>
       </c>
-      <c r="L20" s="242">
+      <c r="L20" s="239">
         <v>-21.97</v>
       </c>
-      <c r="M20" s="246">
+      <c r="M20" s="244">
         <v>-17.2</v>
       </c>
-      <c r="N20" s="243">
+      <c r="N20" s="236">
         <v>-19.25</v>
       </c>
-      <c r="O20" s="244">
+      <c r="O20" s="240">
         <v>-22.85</v>
       </c>
-      <c r="P20" s="236">
+      <c r="P20" s="241">
         <v>-24.39</v>
       </c>
-      <c r="Q20" s="239">
+      <c r="Q20" s="237">
         <v>-24.35</v>
       </c>
-      <c r="R20" s="247">
+      <c r="R20" s="242">
         <v>-23.64</v>
       </c>
-      <c r="S20" s="245">
+      <c r="S20" s="243">
         <v>-28.45</v>
       </c>
-      <c r="T20" s="240">
+      <c r="T20" s="245">
         <v>-32.22</v>
       </c>
     </row>
@@ -8724,7 +8724,7 @@
       <c r="C21" t="str">
         <v>601068</v>
       </c>
-      <c r="D21" s="253" t="str">
+      <c r="D21" s="254" t="str">
         <v>净买: 656.95万</v>
       </c>
       <c r="E21">
@@ -8739,41 +8739,41 @@
       <c r="H21">
         <v>0</v>
       </c>
-      <c r="I21" s="250">
+      <c r="I21" s="248">
         <v>10.02</v>
       </c>
-      <c r="J21" s="257">
+      <c r="J21" s="251">
         <v>5.75</v>
       </c>
-      <c r="K21" s="248">
+      <c r="K21" s="255">
         <v>0.37</v>
       </c>
-      <c r="L21" s="258">
+      <c r="L21" s="260">
         <v>0</v>
       </c>
-      <c r="M21" s="251">
+      <c r="M21" s="252">
         <v>-1.86</v>
       </c>
-      <c r="N21" s="254">
+      <c r="N21" s="256">
         <v>0.19</v>
       </c>
-      <c r="O21" s="259">
+      <c r="O21" s="257">
         <v>0.37</v>
       </c>
-      <c r="P21" s="249">
+      <c r="P21" s="258">
         <v>-1.86</v>
       </c>
-      <c r="Q21" s="255">
+      <c r="Q21" s="259">
         <v>-1.11</v>
       </c>
-      <c r="R21" s="252">
+      <c r="R21" s="253">
         <v>-1.86</v>
       </c>
-      <c r="S21" s="256">
+      <c r="S21" s="249">
         <v>-0.74</v>
       </c>
-      <c r="T21" s="260">
-        <v>17.44</v>
+      <c r="T21" s="250">
+        <v>15.03</v>
       </c>
     </row>
     <row r="22">
@@ -8801,41 +8801,41 @@
       <c r="H22">
         <v>-0.49</v>
       </c>
-      <c r="I22" s="273">
+      <c r="I22" s="270">
         <v>16.28</v>
       </c>
-      <c r="J22" s="263">
+      <c r="J22" s="264">
         <v>21.96</v>
       </c>
-      <c r="K22" s="268">
+      <c r="K22" s="271">
         <v>26.12</v>
       </c>
-      <c r="L22" s="269">
+      <c r="L22" s="265">
         <v>18.55</v>
       </c>
-      <c r="M22" s="270">
+      <c r="M22" s="272">
         <v>21.14</v>
       </c>
-      <c r="N22" s="261">
+      <c r="N22" s="273">
         <v>18.6</v>
       </c>
-      <c r="O22" s="271">
+      <c r="O22" s="268">
         <v>17.6</v>
       </c>
-      <c r="P22" s="264">
+      <c r="P22" s="261">
         <v>15.63</v>
       </c>
-      <c r="Q22" s="266">
+      <c r="Q22" s="269">
         <v>18.84</v>
       </c>
-      <c r="R22" s="272">
+      <c r="R22" s="262">
         <v>17.44</v>
       </c>
-      <c r="S22" s="262">
+      <c r="S22" s="263">
         <v>15.25</v>
       </c>
-      <c r="T22" s="265">
-        <v>88.84</v>
+      <c r="T22" s="266">
+        <v>84.5</v>
       </c>
     </row>
     <row r="23">
@@ -8848,7 +8848,7 @@
       <c r="C23" t="str">
         <v>600678</v>
       </c>
-      <c r="D23" s="278" t="str">
+      <c r="D23" s="282" t="str">
         <v>净卖: -1248.78万</v>
       </c>
       <c r="E23">
@@ -8863,41 +8863,41 @@
       <c r="H23">
         <v>-7.51</v>
       </c>
-      <c r="I23" s="284">
+      <c r="I23" s="286">
         <v>-2.71</v>
       </c>
       <c r="J23" s="274">
         <v>-7.69</v>
       </c>
-      <c r="K23" s="279">
+      <c r="K23" s="275">
         <v>-3.85</v>
       </c>
-      <c r="L23" s="282">
+      <c r="L23" s="283">
         <v>-4.99</v>
       </c>
-      <c r="M23" s="275">
+      <c r="M23" s="279">
         <v>-9.33</v>
       </c>
-      <c r="N23" s="285">
+      <c r="N23" s="276">
         <v>-8.05</v>
       </c>
-      <c r="O23" s="283">
+      <c r="O23" s="277">
         <v>-3.7</v>
       </c>
-      <c r="P23" s="276">
+      <c r="P23" s="278">
         <v>-5.98</v>
       </c>
-      <c r="Q23" s="277">
+      <c r="Q23" s="280">
         <v>-8.9</v>
       </c>
-      <c r="R23" s="280">
+      <c r="R23" s="284">
         <v>-4.49</v>
       </c>
-      <c r="S23" s="286">
+      <c r="S23" s="281">
         <v>-2.49</v>
       </c>
-      <c r="T23" s="281">
-        <v>-13.25</v>
+      <c r="T23" s="285">
+        <v>-20.37</v>
       </c>
     </row>
     <row r="24">
@@ -8910,7 +8910,7 @@
       <c r="C24" t="str">
         <v>301449</v>
       </c>
-      <c r="D24" s="288" t="str">
+      <c r="D24" s="295" t="str">
         <v>净卖: -1931.35万</v>
       </c>
       <c r="E24">
@@ -8925,41 +8925,41 @@
       <c r="H24">
         <v>-7.39</v>
       </c>
-      <c r="I24" s="289">
+      <c r="I24" s="296">
         <v>-10.16</v>
       </c>
-      <c r="J24" s="290">
+      <c r="J24" s="293">
         <v>-12.52</v>
       </c>
-      <c r="K24" s="294">
+      <c r="K24" s="297">
         <v>-14.52</v>
       </c>
-      <c r="L24" s="299">
+      <c r="L24" s="289">
         <v>-15.32</v>
       </c>
-      <c r="M24" s="295">
+      <c r="M24" s="291">
         <v>-9.86</v>
       </c>
-      <c r="N24" s="287">
+      <c r="N24" s="298">
         <v>-11.91</v>
       </c>
-      <c r="O24" s="292">
+      <c r="O24" s="299">
         <v>-12.71</v>
       </c>
-      <c r="P24" s="296">
+      <c r="P24" s="287">
         <v>-12.71</v>
       </c>
-      <c r="Q24" s="297">
+      <c r="Q24" s="290">
         <v>-16.26</v>
       </c>
-      <c r="R24" s="291">
+      <c r="R24" s="288">
         <v>-10.13</v>
       </c>
-      <c r="S24" s="298">
+      <c r="S24" s="294">
         <v>-12.25</v>
       </c>
-      <c r="T24" s="293">
-        <v>-17.14</v>
+      <c r="T24" s="292">
+        <v>-18.32</v>
       </c>
     </row>
     <row r="25">
@@ -8972,7 +8972,7 @@
       <c r="C25" t="str">
         <v>688137</v>
       </c>
-      <c r="D25" s="302" t="str">
+      <c r="D25" s="304" t="str">
         <v>净买: 809.16万</v>
       </c>
       <c r="E25">
@@ -8987,41 +8987,41 @@
       <c r="H25">
         <v>-0.09</v>
       </c>
-      <c r="I25" s="310">
+      <c r="I25" s="302">
         <v>15.54</v>
       </c>
-      <c r="J25" s="311">
+      <c r="J25" s="305">
         <v>13.21</v>
       </c>
-      <c r="K25" s="303">
+      <c r="K25" s="312">
         <v>11.95</v>
       </c>
-      <c r="L25" s="304">
+      <c r="L25" s="303">
         <v>9.95</v>
       </c>
-      <c r="M25" s="305">
+      <c r="M25" s="306">
         <v>6.85</v>
       </c>
-      <c r="N25" s="306">
+      <c r="N25" s="307">
         <v>6.78</v>
       </c>
-      <c r="O25" s="312">
+      <c r="O25" s="308">
         <v>13.58</v>
       </c>
-      <c r="P25" s="301">
+      <c r="P25" s="300">
         <v>14.61</v>
       </c>
-      <c r="Q25" s="300">
+      <c r="Q25" s="301">
         <v>16.47</v>
       </c>
-      <c r="R25" s="307">
+      <c r="R25" s="309">
         <v>23.92</v>
       </c>
-      <c r="S25" s="308">
+      <c r="S25" s="310">
         <v>15.3</v>
       </c>
-      <c r="T25" s="309">
-        <v>11.83</v>
+      <c r="T25" s="311">
+        <v>13.6</v>
       </c>
     </row>
     <row r="26">
@@ -9034,7 +9034,7 @@
       <c r="C26" t="str">
         <v>301408</v>
       </c>
-      <c r="D26" s="318" t="str">
+      <c r="D26" s="319" t="str">
         <v>净卖: -2207.20万</v>
       </c>
       <c r="E26">
@@ -9049,41 +9049,41 @@
       <c r="H26">
         <v>1.45</v>
       </c>
-      <c r="I26" s="314">
+      <c r="I26" s="325">
         <v>18.28</v>
       </c>
-      <c r="J26" s="315">
+      <c r="J26" s="320">
         <v>-5.37</v>
       </c>
       <c r="K26" s="316">
         <v>-14.43</v>
       </c>
-      <c r="L26" s="319">
+      <c r="L26" s="317">
         <v>-13.43</v>
       </c>
-      <c r="M26" s="317">
+      <c r="M26" s="321">
         <v>-12.24</v>
       </c>
-      <c r="N26" s="320">
+      <c r="N26" s="322">
         <v>-13.31</v>
       </c>
-      <c r="O26" s="324">
+      <c r="O26" s="323">
         <v>-7.91</v>
       </c>
-      <c r="P26" s="325">
+      <c r="P26" s="313">
         <v>-4.69</v>
       </c>
-      <c r="Q26" s="321">
+      <c r="Q26" s="318">
         <v>-0.32</v>
       </c>
-      <c r="R26" s="313">
+      <c r="R26" s="314">
         <v>-8.55</v>
       </c>
-      <c r="S26" s="322">
+      <c r="S26" s="324">
         <v>-11.88</v>
       </c>
-      <c r="T26" s="323">
-        <v>-21.3</v>
+      <c r="T26" s="315">
+        <v>-20.63</v>
       </c>
     </row>
     <row r="27">
@@ -9096,7 +9096,7 @@
       <c r="C27" t="str">
         <v>603598</v>
       </c>
-      <c r="D27" s="336" t="str">
+      <c r="D27" s="334" t="str">
         <v>净卖: -958.53万</v>
       </c>
       <c r="E27">
@@ -9111,41 +9111,41 @@
       <c r="H27">
         <v>-10.01</v>
       </c>
-      <c r="I27" s="327">
+      <c r="I27" s="335">
         <v>0</v>
       </c>
-      <c r="J27" s="328">
+      <c r="J27" s="330">
         <v>-5.64</v>
       </c>
-      <c r="K27" s="329">
+      <c r="K27" s="332">
         <v>-1.1</v>
       </c>
-      <c r="L27" s="338">
+      <c r="L27" s="331">
         <v>1.88</v>
       </c>
-      <c r="M27" s="330">
+      <c r="M27" s="336">
         <v>4.9</v>
       </c>
-      <c r="N27" s="331">
+      <c r="N27" s="337">
         <v>3.33</v>
       </c>
-      <c r="O27" s="334">
+      <c r="O27" s="333">
         <v>1.33</v>
       </c>
       <c r="P27" s="326">
         <v>-0.86</v>
       </c>
-      <c r="Q27" s="332">
+      <c r="Q27" s="327">
         <v>4.62</v>
       </c>
-      <c r="R27" s="335">
+      <c r="R27" s="328">
         <v>15.09</v>
       </c>
-      <c r="S27" s="333">
+      <c r="S27" s="329">
         <v>13.64</v>
       </c>
-      <c r="T27" s="337">
-        <v>-19.08</v>
+      <c r="T27" s="338">
+        <v>-19.67</v>
       </c>
     </row>
     <row r="28">
@@ -9158,7 +9158,7 @@
       <c r="C28" t="str">
         <v>920368</v>
       </c>
-      <c r="D28" s="340" t="str">
+      <c r="D28" s="341" t="str">
         <v>净买: 2785.37万</v>
       </c>
       <c r="E28">
@@ -9173,10 +9173,10 @@
       <c r="H28">
         <v>6.62</v>
       </c>
-      <c r="I28" s="351">
+      <c r="I28" s="346">
         <v>21.92</v>
       </c>
-      <c r="J28" s="341">
+      <c r="J28" s="347">
         <v>30.07</v>
       </c>
       <c r="K28" s="348">
@@ -9185,29 +9185,29 @@
       <c r="L28" s="349">
         <v>59.26</v>
       </c>
-      <c r="M28" s="342">
+      <c r="M28" s="344">
         <v>51.53</v>
       </c>
       <c r="N28" s="350">
         <v>48.42</v>
       </c>
-      <c r="O28" s="339">
+      <c r="O28" s="351">
         <v>50.72</v>
       </c>
-      <c r="P28" s="345">
+      <c r="P28" s="339">
         <v>78.13</v>
       </c>
-      <c r="Q28" s="346">
+      <c r="Q28" s="340">
         <v>61.84</v>
       </c>
-      <c r="R28" s="343">
+      <c r="R28" s="342">
         <v>41.93</v>
       </c>
-      <c r="S28" s="344">
+      <c r="S28" s="343">
         <v>52.17</v>
       </c>
-      <c r="T28" s="347">
-        <v>-13.78</v>
+      <c r="T28" s="345">
+        <v>-17.71</v>
       </c>
     </row>
     <row r="29">
@@ -9220,7 +9220,7 @@
       <c r="C29" t="str">
         <v>300017</v>
       </c>
-      <c r="D29" s="360" t="str">
+      <c r="D29" s="356" t="str">
         <v>净卖: -8231.84万</v>
       </c>
       <c r="E29">
@@ -9235,41 +9235,41 @@
       <c r="H29">
         <v>1.57</v>
       </c>
-      <c r="I29" s="358">
+      <c r="I29" s="364">
         <v>18.18</v>
       </c>
-      <c r="J29" s="353">
+      <c r="J29" s="357">
         <v>16.12</v>
       </c>
-      <c r="K29" s="359">
+      <c r="K29" s="354">
         <v>33.7</v>
       </c>
-      <c r="L29" s="354">
+      <c r="L29" s="358">
         <v>44.08</v>
       </c>
-      <c r="M29" s="361">
+      <c r="M29" s="355">
         <v>42.02</v>
       </c>
-      <c r="N29" s="355">
+      <c r="N29" s="359">
         <v>44.77</v>
       </c>
-      <c r="O29" s="356">
+      <c r="O29" s="360">
         <v>65.61</v>
       </c>
-      <c r="P29" s="362">
+      <c r="P29" s="352">
         <v>43.4</v>
       </c>
-      <c r="Q29" s="363">
+      <c r="Q29" s="361">
         <v>54.12</v>
       </c>
-      <c r="R29" s="357">
+      <c r="R29" s="353">
         <v>53.77</v>
       </c>
-      <c r="S29" s="364">
+      <c r="S29" s="362">
         <v>62.09</v>
       </c>
-      <c r="T29" s="352">
-        <v>52.66</v>
+      <c r="T29" s="363">
+        <v>44.85</v>
       </c>
     </row>
     <row r="30">
@@ -9297,41 +9297,41 @@
       <c r="H30">
         <v>-0.04</v>
       </c>
-      <c r="I30" s="376">
+      <c r="I30" s="367">
         <v>1.83</v>
       </c>
-      <c r="J30" s="367">
+      <c r="J30" s="368">
         <v>-4.09</v>
       </c>
-      <c r="K30" s="370">
+      <c r="K30" s="369">
         <v>-6.43</v>
       </c>
-      <c r="L30" s="371">
+      <c r="L30" s="370">
         <v>-7.11</v>
       </c>
-      <c r="M30" s="372">
+      <c r="M30" s="371">
         <v>-5.88</v>
       </c>
-      <c r="N30" s="373">
+      <c r="N30" s="372">
         <v>-7.63</v>
       </c>
-      <c r="O30" s="377">
+      <c r="O30" s="373">
         <v>-5.52</v>
       </c>
-      <c r="P30" s="368">
+      <c r="P30" s="374">
         <v>-4.65</v>
       </c>
-      <c r="Q30" s="374">
+      <c r="Q30" s="375">
         <v>-5.2</v>
       </c>
       <c r="R30" s="365">
         <v>-5.72</v>
       </c>
-      <c r="S30" s="369">
+      <c r="S30" s="376">
         <v>-4.92</v>
       </c>
-      <c r="T30" s="375">
-        <v>-6.12</v>
+      <c r="T30" s="377">
+        <v>-6.47</v>
       </c>
     </row>
     <row r="31">
@@ -9344,7 +9344,7 @@
       <c r="C31" t="str">
         <v>920368</v>
       </c>
-      <c r="D31" s="390" t="str">
+      <c r="D31" s="389" t="str">
         <v>净卖: -476.30万</v>
       </c>
       <c r="E31">
@@ -9359,41 +9359,41 @@
       <c r="H31">
         <v>10.26</v>
       </c>
-      <c r="I31" s="378">
+      <c r="I31" s="385">
         <v>-3.25</v>
       </c>
-      <c r="J31" s="384">
+      <c r="J31" s="381">
         <v>13.46</v>
       </c>
-      <c r="K31" s="385">
+      <c r="K31" s="386">
         <v>18.46</v>
       </c>
-      <c r="L31" s="379">
+      <c r="L31" s="387">
         <v>12.71</v>
       </c>
-      <c r="M31" s="380">
+      <c r="M31" s="382">
         <v>10.4</v>
       </c>
-      <c r="N31" s="386">
+      <c r="N31" s="390">
         <v>12.12</v>
       </c>
       <c r="O31" s="388">
         <v>32.5</v>
       </c>
-      <c r="P31" s="381">
+      <c r="P31" s="378">
         <v>20.38</v>
       </c>
-      <c r="Q31" s="382">
+      <c r="Q31" s="383">
         <v>5.58</v>
       </c>
-      <c r="R31" s="383">
+      <c r="R31" s="379">
         <v>13.19</v>
       </c>
-      <c r="S31" s="387">
+      <c r="S31" s="380">
         <v>23.15</v>
       </c>
-      <c r="T31" s="389">
-        <v>-35.87</v>
+      <c r="T31" s="384">
+        <v>-38.79</v>
       </c>
     </row>
     <row r="32">
@@ -9406,7 +9406,7 @@
       <c r="C32" t="str">
         <v>600273</v>
       </c>
-      <c r="D32" s="395" t="str">
+      <c r="D32" s="400" t="str">
         <v>净卖: -3657.56万</v>
       </c>
       <c r="E32">
@@ -9421,41 +9421,41 @@
       <c r="H32">
         <v>3.89</v>
       </c>
-      <c r="I32" s="401">
+      <c r="I32" s="393">
         <v>5.92</v>
       </c>
-      <c r="J32" s="402">
+      <c r="J32" s="398">
         <v>2.96</v>
       </c>
-      <c r="K32" s="396">
+      <c r="K32" s="399">
         <v>-4.88</v>
       </c>
-      <c r="L32" s="397">
+      <c r="L32" s="401">
         <v>-3.05</v>
       </c>
-      <c r="M32" s="403">
+      <c r="M32" s="402">
         <v>-1.31</v>
       </c>
-      <c r="N32" s="398">
+      <c r="N32" s="394">
         <v>-4.18</v>
       </c>
-      <c r="O32" s="391">
+      <c r="O32" s="395">
         <v>-1.74</v>
       </c>
-      <c r="P32" s="399">
+      <c r="P32" s="391">
         <v>-1.66</v>
       </c>
-      <c r="Q32" s="393">
+      <c r="Q32" s="396">
         <v>0.78</v>
       </c>
-      <c r="R32" s="392">
+      <c r="R32" s="397">
         <v>1.83</v>
       </c>
-      <c r="S32" s="394">
+      <c r="S32" s="403">
         <v>2.7</v>
       </c>
-      <c r="T32" s="400">
-        <v>-22.82</v>
+      <c r="T32" s="392">
+        <v>-27.79</v>
       </c>
     </row>
     <row r="33">
@@ -9468,7 +9468,7 @@
       <c r="C33" t="str">
         <v>300257</v>
       </c>
-      <c r="D33" s="412" t="str">
+      <c r="D33" s="413" t="str">
         <v>净卖: -2507.66万</v>
       </c>
       <c r="E33">
@@ -9483,41 +9483,41 @@
       <c r="H33">
         <v>2.76</v>
       </c>
-      <c r="I33" s="411">
+      <c r="I33" s="414">
         <v>16.77</v>
       </c>
-      <c r="J33" s="413">
+      <c r="J33" s="409">
         <v>17.59</v>
       </c>
-      <c r="K33" s="414">
+      <c r="K33" s="404">
         <v>16.46</v>
       </c>
-      <c r="L33" s="408">
+      <c r="L33" s="415">
         <v>7.35</v>
       </c>
-      <c r="M33" s="415">
+      <c r="M33" s="416">
         <v>14.56</v>
       </c>
       <c r="N33" s="405">
         <v>8.23</v>
       </c>
-      <c r="O33" s="406">
+      <c r="O33" s="410">
         <v>8.64</v>
       </c>
-      <c r="P33" s="409">
+      <c r="P33" s="411">
         <v>8.67</v>
       </c>
-      <c r="Q33" s="410">
+      <c r="Q33" s="412">
         <v>5.17</v>
       </c>
-      <c r="R33" s="416">
+      <c r="R33" s="406">
         <v>1.33</v>
       </c>
       <c r="S33" s="407">
         <v>1.8</v>
       </c>
-      <c r="T33" s="404">
-        <v>-0.1</v>
+      <c r="T33" s="408">
+        <v>0.99</v>
       </c>
     </row>
     <row r="34">
@@ -9665,41 +9665,41 @@
       <c r="F37" t="str"/>
       <c r="G37" t="str"/>
       <c r="H37" t="str"/>
-      <c r="I37" s="426">
+      <c r="I37" s="428">
         <v>64.71</v>
       </c>
-      <c r="J37" s="427">
+      <c r="J37" s="432">
         <v>69.7</v>
       </c>
-      <c r="K37" s="431">
+      <c r="K37" s="424">
         <v>66.67</v>
       </c>
-      <c r="L37" s="434">
+      <c r="L37" s="433">
         <v>68.75</v>
       </c>
-      <c r="M37" s="429">
+      <c r="M37" s="426">
         <v>68.75</v>
       </c>
-      <c r="N37" s="435">
+      <c r="N37" s="427">
         <v>71.88</v>
       </c>
-      <c r="O37" s="432">
+      <c r="O37" s="425">
         <v>71.88</v>
       </c>
-      <c r="P37" s="424">
+      <c r="P37" s="429">
         <v>62.5</v>
       </c>
-      <c r="Q37" s="433">
+      <c r="Q37" s="430">
         <v>65.63</v>
       </c>
-      <c r="R37" s="428">
+      <c r="R37" s="431">
         <v>62.5</v>
       </c>
-      <c r="S37" s="425">
+      <c r="S37" s="434">
         <v>65.63</v>
       </c>
-      <c r="T37" s="430">
-        <v>33.33</v>
+      <c r="T37" s="435">
+        <v>36.36</v>
       </c>
     </row>
     <row r="38">
@@ -9713,41 +9713,41 @@
       <c r="F38" t="str"/>
       <c r="G38" t="str"/>
       <c r="H38" t="str"/>
-      <c r="I38" s="439">
+      <c r="I38" s="442">
         <v>7.55</v>
       </c>
-      <c r="J38" s="442">
+      <c r="J38" s="439">
         <v>9.44</v>
       </c>
-      <c r="K38" s="444">
+      <c r="K38" s="440">
         <v>10.47</v>
       </c>
-      <c r="L38" s="440">
+      <c r="L38" s="436">
         <v>10.84</v>
       </c>
-      <c r="M38" s="445">
+      <c r="M38" s="446">
         <v>11.29</v>
       </c>
-      <c r="N38" s="446">
+      <c r="N38" s="443">
         <v>10.99</v>
       </c>
-      <c r="O38" s="436">
+      <c r="O38" s="444">
         <v>12.53</v>
       </c>
       <c r="P38" s="437">
         <v>11.98</v>
       </c>
-      <c r="Q38" s="447">
+      <c r="Q38" s="438">
         <v>10.83</v>
       </c>
-      <c r="R38" s="438">
+      <c r="R38" s="445">
         <v>10.67</v>
       </c>
-      <c r="S38" s="441">
+      <c r="S38" s="447">
         <v>10.08</v>
       </c>
-      <c r="T38" s="443">
-        <v>2.57</v>
+      <c r="T38" s="441">
+        <v>3.05</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/大小说家/index.xlsx
+++ b/youzi/大小说家/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="449">
+  <fills count="452">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -45,25 +45,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7ECA90"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFEAF6ED"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7ECA90"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF83CC93"/>
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8A93"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -75,18 +105,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFE46370"/>
         <bgColor/>
       </patternFill>
@@ -99,61 +117,643 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8A93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFBF2836"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD23040"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB2212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9EA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4352"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D8DB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9ED7AB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B25E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFCEFF0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBE3C4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CDD1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
+        <fgColor rgb="FFC5E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8E1C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB9199"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91D2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -165,6 +765,216 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15663"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF3F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDE4C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -183,19 +993,1357 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEE9EA6"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91D2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBD5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7833"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8336"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3DAF57"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF59BB6F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD75"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF35AC50"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBD6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4453"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3948"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAEFDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF37AD52"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB766"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF73C586"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -225,7 +2373,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2212F"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7BC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7E1C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2DA949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB4E0BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8790"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4BB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDFEFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -237,43 +2553,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -285,2293 +2613,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4352"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5BBB71"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B25E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBE3C4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEFF0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB9199"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CDD1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8E1C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91D2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15663"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF3F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDE4C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91D2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEB9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEB9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEB9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFEBD5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF59BB6F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8336"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD75"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7833"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3DAF57"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF35AC50"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAEFDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4453"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFEBD6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3948"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB766"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF37AD52"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF73C586"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4BB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB4E0BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8790"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2DA949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7BC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2589,97 +2649,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFCE2F3E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3C4B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2720,7 +2738,28 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="448">
+  <borders count="451">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -5861,7 +5900,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="448">
+  <cellXfs count="451">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -7202,6 +7241,15 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="447" fillId="448" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="448" fillId="449" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="449" fillId="450" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="450" fillId="451" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -7561,41 +7609,41 @@
       <c r="H2">
         <v>-2.13</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="11">
         <v>-8.04</v>
       </c>
-      <c r="J2" s="7">
+      <c r="J2" s="2">
         <v>-7</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2" s="8">
         <v>-0.47</v>
       </c>
-      <c r="L2" s="11">
+      <c r="L2" s="9">
         <v>3.68</v>
       </c>
-      <c r="M2" s="8">
+      <c r="M2" s="3">
         <v>10.89</v>
       </c>
-      <c r="N2" s="9">
+      <c r="N2" s="12">
         <v>3.84</v>
       </c>
-      <c r="O2" s="13">
+      <c r="O2" s="4">
         <v>6.4</v>
       </c>
-      <c r="P2" s="3">
+      <c r="P2" s="5">
         <v>7.52</v>
       </c>
-      <c r="Q2" s="4">
+      <c r="Q2" s="7">
         <v>-2.98</v>
       </c>
-      <c r="R2" s="12">
+      <c r="R2" s="10">
         <v>2.88</v>
       </c>
-      <c r="S2" s="10">
+      <c r="S2" s="13">
         <v>6.19</v>
       </c>
-      <c r="T2" s="5">
-        <v>-2.88</v>
+      <c r="T2" s="6">
+        <v>-6.92</v>
       </c>
     </row>
     <row r="3">
@@ -7608,7 +7656,7 @@
       <c r="C3" t="str">
         <v>002923</v>
       </c>
-      <c r="D3" s="19" t="str">
+      <c r="D3" s="25" t="str">
         <v>净卖: -1342.21万</v>
       </c>
       <c r="E3">
@@ -7623,41 +7671,41 @@
       <c r="H3">
         <v>2.17</v>
       </c>
-      <c r="I3" s="15">
+      <c r="I3" s="18">
         <v>7.69</v>
       </c>
-      <c r="J3" s="25">
+      <c r="J3" s="19">
         <v>17.63</v>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="24">
         <v>5.88</v>
       </c>
-      <c r="L3" s="20">
+      <c r="L3" s="21">
         <v>-4.3</v>
       </c>
-      <c r="M3" s="21">
+      <c r="M3" s="22">
         <v>-13.87</v>
       </c>
-      <c r="N3" s="17">
+      <c r="N3" s="26">
         <v>-11.45</v>
       </c>
-      <c r="O3" s="22">
+      <c r="O3" s="20">
         <v>-15.08</v>
       </c>
-      <c r="P3" s="23">
+      <c r="P3" s="14">
         <v>-14.66</v>
       </c>
-      <c r="Q3" s="26">
+      <c r="Q3" s="15">
         <v>-12.84</v>
       </c>
-      <c r="R3" s="24">
+      <c r="R3" s="23">
         <v>-21.56</v>
       </c>
-      <c r="S3" s="14">
+      <c r="S3" s="16">
         <v>-24.59</v>
       </c>
-      <c r="T3" s="18">
-        <v>-24.05</v>
+      <c r="T3" s="17">
+        <v>-16.47</v>
       </c>
     </row>
     <row r="4">
@@ -7670,7 +7718,7 @@
       <c r="C4" t="str">
         <v>002564</v>
       </c>
-      <c r="D4" s="33" t="str">
+      <c r="D4" s="35" t="str">
         <v>净买: 1737.48万</v>
       </c>
       <c r="E4">
@@ -7685,41 +7733,41 @@
       <c r="H4">
         <v>-1.38</v>
       </c>
-      <c r="I4" s="34">
+      <c r="I4" s="36">
         <v>11.55</v>
       </c>
-      <c r="J4" s="27">
+      <c r="J4" s="37">
         <v>2.39</v>
       </c>
-      <c r="K4" s="36">
+      <c r="K4" s="38">
         <v>12.55</v>
       </c>
-      <c r="L4" s="28">
+      <c r="L4" s="32">
         <v>5.58</v>
       </c>
-      <c r="M4" s="29">
+      <c r="M4" s="39">
         <v>16.14</v>
       </c>
-      <c r="N4" s="37">
+      <c r="N4" s="28">
         <v>21.51</v>
       </c>
-      <c r="O4" s="30">
+      <c r="O4" s="29">
         <v>16.14</v>
       </c>
-      <c r="P4" s="38">
+      <c r="P4" s="30">
         <v>19.92</v>
       </c>
-      <c r="Q4" s="35">
+      <c r="Q4" s="31">
         <v>20.72</v>
       </c>
-      <c r="R4" s="31">
+      <c r="R4" s="33">
         <v>15.94</v>
       </c>
-      <c r="S4" s="32">
+      <c r="S4" s="27">
         <v>8.96</v>
       </c>
-      <c r="T4" s="39">
-        <v>26.69</v>
+      <c r="T4" s="34">
+        <v>26.1</v>
       </c>
     </row>
     <row r="5">
@@ -7732,7 +7780,7 @@
       <c r="C5" t="str">
         <v>600735</v>
       </c>
-      <c r="D5" s="47" t="str">
+      <c r="D5" s="43" t="str">
         <v>净买: 1155.67万</v>
       </c>
       <c r="E5">
@@ -7747,41 +7795,41 @@
       <c r="H5">
         <v>1.24</v>
       </c>
-      <c r="I5" s="40">
+      <c r="I5" s="50">
         <v>8.71</v>
       </c>
-      <c r="J5" s="41">
+      <c r="J5" s="40">
         <v>8.84</v>
       </c>
-      <c r="K5" s="42">
+      <c r="K5" s="44">
         <v>7.48</v>
       </c>
-      <c r="L5" s="45">
+      <c r="L5" s="41">
         <v>4.63</v>
       </c>
-      <c r="M5" s="48">
+      <c r="M5" s="47">
         <v>5.71</v>
       </c>
       <c r="N5" s="51">
         <v>11.16</v>
       </c>
-      <c r="O5" s="43">
+      <c r="O5" s="45">
         <v>9.66</v>
       </c>
-      <c r="P5" s="44">
+      <c r="P5" s="42">
         <v>6.8</v>
       </c>
-      <c r="Q5" s="49">
+      <c r="Q5" s="52">
         <v>12.24</v>
       </c>
-      <c r="R5" s="50">
+      <c r="R5" s="46">
         <v>13.88</v>
       </c>
-      <c r="S5" s="52">
+      <c r="S5" s="48">
         <v>10.07</v>
       </c>
-      <c r="T5" s="46">
-        <v>-3.81</v>
+      <c r="T5" s="49">
+        <v>0.95</v>
       </c>
     </row>
     <row r="6">
@@ -7794,7 +7842,7 @@
       <c r="C6" t="str">
         <v>600735</v>
       </c>
-      <c r="D6" s="57" t="str">
+      <c r="D6" s="64" t="str">
         <v>净卖: -1139.95万</v>
       </c>
       <c r="E6">
@@ -7809,41 +7857,41 @@
       <c r="H6">
         <v>-5.01</v>
       </c>
-      <c r="I6" s="58">
+      <c r="I6" s="59">
         <v>5.4</v>
       </c>
-      <c r="J6" s="53">
+      <c r="J6" s="65">
         <v>4.08</v>
       </c>
-      <c r="K6" s="62">
+      <c r="K6" s="61">
         <v>1.32</v>
       </c>
-      <c r="L6" s="59">
+      <c r="L6" s="56">
         <v>2.37</v>
       </c>
-      <c r="M6" s="54">
+      <c r="M6" s="57">
         <v>7.64</v>
       </c>
-      <c r="N6" s="63">
+      <c r="N6" s="53">
         <v>6.19</v>
       </c>
-      <c r="O6" s="55">
+      <c r="O6" s="62">
         <v>3.43</v>
       </c>
-      <c r="P6" s="56">
+      <c r="P6" s="58">
         <v>8.7</v>
       </c>
-      <c r="Q6" s="64">
+      <c r="Q6" s="54">
         <v>10.28</v>
       </c>
-      <c r="R6" s="65">
+      <c r="R6" s="55">
         <v>6.59</v>
       </c>
-      <c r="S6" s="60">
+      <c r="S6" s="63">
         <v>3.43</v>
       </c>
-      <c r="T6" s="61">
-        <v>-6.85</v>
+      <c r="T6" s="60">
+        <v>-2.24</v>
       </c>
     </row>
     <row r="7">
@@ -7856,7 +7904,7 @@
       <c r="C7" t="str">
         <v>002365</v>
       </c>
-      <c r="D7" s="67" t="str">
+      <c r="D7" s="70" t="str">
         <v>净卖: -2887.03万</v>
       </c>
       <c r="E7">
@@ -7871,41 +7919,41 @@
       <c r="H7">
         <v>3.76</v>
       </c>
-      <c r="I7" s="71">
+      <c r="I7" s="74">
         <v>-4.32</v>
       </c>
-      <c r="J7" s="68">
+      <c r="J7" s="66">
         <v>5.25</v>
       </c>
-      <c r="K7" s="69">
+      <c r="K7" s="67">
         <v>15.76</v>
       </c>
       <c r="L7" s="75">
         <v>27.33</v>
       </c>
-      <c r="M7" s="76">
+      <c r="M7" s="68">
         <v>35.58</v>
       </c>
-      <c r="N7" s="70">
+      <c r="N7" s="76">
         <v>40.03</v>
       </c>
-      <c r="O7" s="72">
+      <c r="O7" s="69">
         <v>54.03</v>
       </c>
-      <c r="P7" s="73">
+      <c r="P7" s="77">
         <v>38.65</v>
       </c>
-      <c r="Q7" s="74">
+      <c r="Q7" s="71">
         <v>24.77</v>
       </c>
-      <c r="R7" s="77">
+      <c r="R7" s="72">
         <v>28.27</v>
       </c>
-      <c r="S7" s="78">
+      <c r="S7" s="73">
         <v>22.51</v>
       </c>
-      <c r="T7" s="66">
-        <v>-17.76</v>
+      <c r="T7" s="78">
+        <v>-18.64</v>
       </c>
     </row>
     <row r="8">
@@ -7918,7 +7966,7 @@
       <c r="C8" t="str">
         <v>603585</v>
       </c>
-      <c r="D8" s="86" t="str">
+      <c r="D8" s="80" t="str">
         <v>净买: 590.46万</v>
       </c>
       <c r="E8">
@@ -7933,41 +7981,41 @@
       <c r="H8">
         <v>-2.32</v>
       </c>
-      <c r="I8" s="83">
+      <c r="I8" s="88">
         <v>8.09</v>
       </c>
       <c r="J8" s="89">
         <v>7.12</v>
       </c>
-      <c r="K8" s="84">
+      <c r="K8" s="85">
         <v>17.86</v>
       </c>
-      <c r="L8" s="87">
+      <c r="L8" s="90">
         <v>29.63</v>
       </c>
-      <c r="M8" s="88">
+      <c r="M8" s="81">
         <v>16.68</v>
       </c>
-      <c r="N8" s="80">
+      <c r="N8" s="91">
         <v>5.02</v>
       </c>
-      <c r="O8" s="85">
+      <c r="O8" s="79">
         <v>0.38</v>
       </c>
-      <c r="P8" s="81">
+      <c r="P8" s="82">
         <v>2.75</v>
       </c>
-      <c r="Q8" s="90">
+      <c r="Q8" s="86">
         <v>2.05</v>
       </c>
-      <c r="R8" s="91">
+      <c r="R8" s="83">
         <v>-0.32</v>
       </c>
-      <c r="S8" s="82">
+      <c r="S8" s="84">
         <v>-1.57</v>
       </c>
-      <c r="T8" s="79">
-        <v>5.34</v>
+      <c r="T8" s="87">
+        <v>4.8</v>
       </c>
     </row>
     <row r="9">
@@ -7980,7 +8028,7 @@
       <c r="C9" t="str">
         <v>003029</v>
       </c>
-      <c r="D9" s="104" t="str">
+      <c r="D9" s="99" t="str">
         <v>净卖: -1441.18万</v>
       </c>
       <c r="E9">
@@ -7995,41 +8043,41 @@
       <c r="H9">
         <v>0.04</v>
       </c>
-      <c r="I9" s="100">
+      <c r="I9" s="93">
         <v>9.96</v>
       </c>
-      <c r="J9" s="97">
+      <c r="J9" s="103">
         <v>14.48</v>
       </c>
-      <c r="K9" s="92">
+      <c r="K9" s="94">
         <v>8.49</v>
       </c>
-      <c r="L9" s="98">
+      <c r="L9" s="95">
         <v>8.99</v>
       </c>
-      <c r="M9" s="93">
+      <c r="M9" s="97">
         <v>7.77</v>
       </c>
-      <c r="N9" s="94">
+      <c r="N9" s="104">
         <v>2.72</v>
       </c>
-      <c r="O9" s="101">
+      <c r="O9" s="98">
         <v>1.22</v>
       </c>
-      <c r="P9" s="95">
+      <c r="P9" s="100">
         <v>-1.33</v>
       </c>
-      <c r="Q9" s="103">
+      <c r="Q9" s="101">
         <v>-1.65</v>
       </c>
-      <c r="R9" s="99">
+      <c r="R9" s="102">
         <v>-1.04</v>
       </c>
-      <c r="S9" s="102">
+      <c r="S9" s="92">
         <v>-2.01</v>
       </c>
       <c r="T9" s="96">
-        <v>-23.75</v>
+        <v>-26.66</v>
       </c>
     </row>
     <row r="10">
@@ -8042,7 +8090,7 @@
       <c r="C10" t="str">
         <v>301486</v>
       </c>
-      <c r="D10" s="114" t="str">
+      <c r="D10" s="116" t="str">
         <v>净买: 2150.96万</v>
       </c>
       <c r="E10">
@@ -8057,41 +8105,41 @@
       <c r="H10">
         <v>1.79</v>
       </c>
-      <c r="I10" s="115">
+      <c r="I10" s="113">
         <v>17.9</v>
       </c>
-      <c r="J10" s="109">
+      <c r="J10" s="107">
         <v>21.2</v>
       </c>
-      <c r="K10" s="110">
+      <c r="K10" s="117">
         <v>12.29</v>
       </c>
-      <c r="L10" s="111">
+      <c r="L10" s="110">
         <v>14.55</v>
       </c>
-      <c r="M10" s="112">
+      <c r="M10" s="111">
         <v>21.65</v>
       </c>
-      <c r="N10" s="116">
+      <c r="N10" s="105">
         <v>15.36</v>
       </c>
-      <c r="O10" s="106">
+      <c r="O10" s="108">
         <v>9.81</v>
       </c>
-      <c r="P10" s="117">
+      <c r="P10" s="114">
         <v>10.06</v>
       </c>
-      <c r="Q10" s="105">
+      <c r="Q10" s="115">
         <v>17.68</v>
       </c>
-      <c r="R10" s="107">
+      <c r="R10" s="112">
         <v>24.45</v>
       </c>
-      <c r="S10" s="113">
+      <c r="S10" s="106">
         <v>20.16</v>
       </c>
-      <c r="T10" s="108">
-        <v>169.31</v>
+      <c r="T10" s="109">
+        <v>160.04</v>
       </c>
     </row>
     <row r="11">
@@ -8104,7 +8152,7 @@
       <c r="C11" t="str">
         <v>002052</v>
       </c>
-      <c r="D11" s="129" t="str">
+      <c r="D11" s="126" t="str">
         <v>净卖: -1505.16万</v>
       </c>
       <c r="E11">
@@ -8119,41 +8167,41 @@
       <c r="H11">
         <v>10.03</v>
       </c>
-      <c r="I11" s="120">
+      <c r="I11" s="127">
         <v>0</v>
       </c>
-      <c r="J11" s="125">
+      <c r="J11" s="128">
         <v>4.18</v>
       </c>
-      <c r="K11" s="126">
+      <c r="K11" s="122">
         <v>14.59</v>
       </c>
-      <c r="L11" s="121">
+      <c r="L11" s="125">
         <v>26.06</v>
       </c>
-      <c r="M11" s="118">
+      <c r="M11" s="123">
         <v>38.68</v>
       </c>
-      <c r="N11" s="122">
+      <c r="N11" s="129">
         <v>44.38</v>
       </c>
-      <c r="O11" s="127">
+      <c r="O11" s="124">
         <v>45.82</v>
       </c>
-      <c r="P11" s="130">
+      <c r="P11" s="119">
         <v>53.88</v>
       </c>
-      <c r="Q11" s="123">
+      <c r="Q11" s="130">
         <v>45.36</v>
       </c>
-      <c r="R11" s="119">
+      <c r="R11" s="120">
         <v>34.42</v>
       </c>
-      <c r="S11" s="124">
+      <c r="S11" s="118">
         <v>39.06</v>
       </c>
-      <c r="T11" s="128">
-        <v>-25.76</v>
+      <c r="T11" s="121">
+        <v>-28.57</v>
       </c>
     </row>
     <row r="12">
@@ -8166,7 +8214,7 @@
       <c r="C12" t="str">
         <v>430476</v>
       </c>
-      <c r="D12" s="136" t="str">
+      <c r="D12" s="142" t="str">
         <v>净买: 566.61万</v>
       </c>
       <c r="E12">
@@ -8181,40 +8229,40 @@
       <c r="H12">
         <v>2.2</v>
       </c>
-      <c r="I12" s="132">
+      <c r="I12" s="138">
         <v>27.17</v>
       </c>
-      <c r="J12" s="137">
+      <c r="J12" s="134">
         <v>65.32</v>
       </c>
-      <c r="K12" s="133">
+      <c r="K12" s="135">
         <v>65.69</v>
       </c>
-      <c r="L12" s="142">
+      <c r="L12" s="143">
         <v>47.53</v>
       </c>
-      <c r="M12" s="143">
+      <c r="M12" s="136">
         <v>34.9</v>
       </c>
-      <c r="N12" s="138">
+      <c r="N12" s="139">
         <v>37.51</v>
       </c>
-      <c r="O12" s="134">
+      <c r="O12" s="133">
         <v>35.45</v>
       </c>
-      <c r="P12" s="139">
+      <c r="P12" s="137">
         <v>35.86</v>
       </c>
-      <c r="Q12" s="140">
+      <c r="Q12" s="131">
         <v>29.23</v>
       </c>
-      <c r="R12" s="141">
+      <c r="R12" s="132">
         <v>29.87</v>
       </c>
-      <c r="S12" s="135">
+      <c r="S12" s="140">
         <v>29.96</v>
       </c>
-      <c r="T12" s="131">
+      <c r="T12" s="141">
         <v>14.04</v>
       </c>
     </row>
@@ -8228,7 +8276,7 @@
       <c r="C13" t="str">
         <v>871981</v>
       </c>
-      <c r="D13" s="148" t="str">
+      <c r="D13" s="155" t="str">
         <v>净买: 779.65万</v>
       </c>
       <c r="E13">
@@ -8243,40 +8291,40 @@
       <c r="H13">
         <v>10.55</v>
       </c>
-      <c r="I13" s="149">
+      <c r="I13" s="156">
         <v>17.58</v>
       </c>
-      <c r="J13" s="155">
+      <c r="J13" s="144">
         <v>17.95</v>
       </c>
-      <c r="K13" s="150">
+      <c r="K13" s="149">
         <v>13.64</v>
       </c>
-      <c r="L13" s="151">
+      <c r="L13" s="152">
         <v>14.65</v>
       </c>
-      <c r="M13" s="156">
+      <c r="M13" s="145">
         <v>17.15</v>
       </c>
-      <c r="N13" s="154">
+      <c r="N13" s="146">
         <v>11.72</v>
       </c>
-      <c r="O13" s="144">
+      <c r="O13" s="153">
         <v>6.52</v>
       </c>
-      <c r="P13" s="145">
+      <c r="P13" s="150">
         <v>0.28</v>
       </c>
-      <c r="Q13" s="152">
+      <c r="Q13" s="147">
         <v>1.84</v>
       </c>
-      <c r="R13" s="153">
+      <c r="R13" s="151">
         <v>-1.52</v>
       </c>
-      <c r="S13" s="146">
+      <c r="S13" s="154">
         <v>0.2</v>
       </c>
-      <c r="T13" s="147">
+      <c r="T13" s="148">
         <v>-6.54</v>
       </c>
     </row>
@@ -8290,7 +8338,7 @@
       <c r="C14" t="str">
         <v>871981</v>
       </c>
-      <c r="D14" s="164" t="str">
+      <c r="D14" s="167" t="str">
         <v>净卖: -825.29万</v>
       </c>
       <c r="E14">
@@ -8305,16 +8353,16 @@
       <c r="H14">
         <v>7.39</v>
       </c>
-      <c r="I14" s="167">
+      <c r="I14" s="162">
         <v>-6.58</v>
       </c>
-      <c r="J14" s="160">
+      <c r="J14" s="168">
         <v>-10</v>
       </c>
-      <c r="K14" s="161">
+      <c r="K14" s="163">
         <v>-9.2</v>
       </c>
-      <c r="L14" s="168">
+      <c r="L14" s="164">
         <v>-7.22</v>
       </c>
       <c r="M14" s="169">
@@ -8326,19 +8374,19 @@
       <c r="O14" s="165">
         <v>-20.58</v>
       </c>
-      <c r="P14" s="166">
+      <c r="P14" s="160">
         <v>-19.34</v>
       </c>
-      <c r="Q14" s="162">
+      <c r="Q14" s="166">
         <v>-22</v>
       </c>
       <c r="R14" s="158">
         <v>-20.64</v>
       </c>
-      <c r="S14" s="163">
+      <c r="S14" s="159">
         <v>-21.32</v>
       </c>
-      <c r="T14" s="159">
+      <c r="T14" s="161">
         <v>-25.98</v>
       </c>
     </row>
@@ -8352,7 +8400,7 @@
       <c r="C15" t="str">
         <v>301389</v>
       </c>
-      <c r="D15" s="177" t="str">
+      <c r="D15" s="180" t="str">
         <v>净买: 4127.06万</v>
       </c>
       <c r="E15">
@@ -8367,41 +8415,41 @@
       <c r="H15">
         <v>0.95</v>
       </c>
-      <c r="I15" s="178">
+      <c r="I15" s="181">
         <v>18.87</v>
       </c>
-      <c r="J15" s="170">
+      <c r="J15" s="175">
         <v>42.65</v>
       </c>
-      <c r="K15" s="171">
+      <c r="K15" s="182">
         <v>49.96</v>
       </c>
-      <c r="L15" s="179">
+      <c r="L15" s="178">
         <v>46.52</v>
       </c>
-      <c r="M15" s="180">
+      <c r="M15" s="170">
         <v>28.73</v>
       </c>
-      <c r="N15" s="181">
+      <c r="N15" s="171">
         <v>24.55</v>
       </c>
-      <c r="O15" s="172">
+      <c r="O15" s="176">
         <v>17.98</v>
       </c>
-      <c r="P15" s="182">
+      <c r="P15" s="177">
         <v>30.5</v>
       </c>
-      <c r="Q15" s="173">
+      <c r="Q15" s="172">
         <v>23.88</v>
       </c>
-      <c r="R15" s="174">
+      <c r="R15" s="173">
         <v>19.89</v>
       </c>
-      <c r="S15" s="175">
+      <c r="S15" s="179">
         <v>21.91</v>
       </c>
-      <c r="T15" s="176">
-        <v>20.46</v>
+      <c r="T15" s="174">
+        <v>23.23</v>
       </c>
     </row>
     <row r="16">
@@ -8414,7 +8462,7 @@
       <c r="C16" t="str">
         <v>301389</v>
       </c>
-      <c r="D16" s="193" t="str">
+      <c r="D16" s="190" t="str">
         <v>净买: 932.40万</v>
       </c>
       <c r="E16">
@@ -8429,41 +8477,41 @@
       <c r="H16">
         <v>-5.75</v>
       </c>
-      <c r="I16" s="194">
+      <c r="I16" s="186">
         <v>27.33</v>
       </c>
-      <c r="J16" s="190">
+      <c r="J16" s="191">
         <v>33.86</v>
       </c>
       <c r="K16" s="195">
         <v>30.79</v>
       </c>
-      <c r="L16" s="191">
+      <c r="L16" s="187">
         <v>14.91</v>
       </c>
       <c r="M16" s="183">
         <v>11.18</v>
       </c>
-      <c r="N16" s="187">
+      <c r="N16" s="192">
         <v>5.32</v>
       </c>
-      <c r="O16" s="188">
+      <c r="O16" s="189">
         <v>16.49</v>
       </c>
-      <c r="P16" s="189">
+      <c r="P16" s="188">
         <v>10.58</v>
       </c>
-      <c r="Q16" s="184">
+      <c r="Q16" s="193">
         <v>7.02</v>
       </c>
-      <c r="R16" s="185">
+      <c r="R16" s="184">
         <v>8.82</v>
       </c>
-      <c r="S16" s="186">
+      <c r="S16" s="185">
         <v>15.05</v>
       </c>
-      <c r="T16" s="192">
-        <v>7.53</v>
+      <c r="T16" s="194">
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -8476,7 +8524,7 @@
       <c r="C17" t="str">
         <v>300450</v>
       </c>
-      <c r="D17" s="202" t="str">
+      <c r="D17" s="197" t="str">
         <v>净卖: -4644.14万</v>
       </c>
       <c r="E17">
@@ -8491,41 +8539,41 @@
       <c r="H17">
         <v>5.71</v>
       </c>
-      <c r="I17" s="203">
+      <c r="I17" s="204">
         <v>13.52</v>
       </c>
-      <c r="J17" s="208">
+      <c r="J17" s="205">
         <v>30.12</v>
       </c>
-      <c r="K17" s="205">
+      <c r="K17" s="198">
         <v>40.03</v>
       </c>
-      <c r="L17" s="201">
+      <c r="L17" s="207">
         <v>40.54</v>
       </c>
-      <c r="M17" s="196">
+      <c r="M17" s="199">
         <v>43.32</v>
       </c>
-      <c r="N17" s="204">
+      <c r="N17" s="203">
         <v>71.99</v>
       </c>
-      <c r="O17" s="197">
+      <c r="O17" s="200">
         <v>83.47</v>
       </c>
-      <c r="P17" s="206">
+      <c r="P17" s="208">
         <v>79.22</v>
       </c>
-      <c r="Q17" s="207">
+      <c r="Q17" s="201">
         <v>87.37</v>
       </c>
-      <c r="R17" s="198">
+      <c r="R17" s="206">
         <v>92.23</v>
       </c>
-      <c r="S17" s="199">
+      <c r="S17" s="196">
         <v>75.19</v>
       </c>
-      <c r="T17" s="200">
-        <v>83.6</v>
+      <c r="T17" s="202">
+        <v>76.98</v>
       </c>
     </row>
     <row r="18">
@@ -8538,7 +8586,7 @@
       <c r="C18" t="str">
         <v>301389</v>
       </c>
-      <c r="D18" s="212" t="str">
+      <c r="D18" s="209" t="str">
         <v>净卖: -3733.12万</v>
       </c>
       <c r="E18">
@@ -8556,38 +8604,38 @@
       <c r="I18" s="210">
         <v>-5.04</v>
       </c>
-      <c r="J18" s="214">
+      <c r="J18" s="215">
         <v>-16.57</v>
       </c>
-      <c r="K18" s="218">
+      <c r="K18" s="211">
         <v>-19.28</v>
       </c>
-      <c r="L18" s="219">
+      <c r="L18" s="212">
         <v>-23.54</v>
       </c>
-      <c r="M18" s="220">
+      <c r="M18" s="216">
         <v>-15.42</v>
       </c>
-      <c r="N18" s="215">
+      <c r="N18" s="213">
         <v>-19.72</v>
       </c>
-      <c r="O18" s="213">
+      <c r="O18" s="217">
         <v>-22.3</v>
       </c>
-      <c r="P18" s="216">
+      <c r="P18" s="218">
         <v>-20.99</v>
       </c>
-      <c r="Q18" s="221">
+      <c r="Q18" s="219">
         <v>-16.47</v>
       </c>
-      <c r="R18" s="209">
+      <c r="R18" s="220">
         <v>-13.65</v>
       </c>
-      <c r="S18" s="217">
+      <c r="S18" s="214">
         <v>-15.93</v>
       </c>
-      <c r="T18" s="211">
-        <v>-21.93</v>
+      <c r="T18" s="221">
+        <v>-20.14</v>
       </c>
     </row>
     <row r="19">
@@ -8600,7 +8648,7 @@
       <c r="C19" t="str">
         <v>833580</v>
       </c>
-      <c r="D19" s="225" t="str">
+      <c r="D19" s="228" t="str">
         <v>净买: 656.67万</v>
       </c>
       <c r="E19">
@@ -8615,40 +8663,40 @@
       <c r="H19">
         <v>-1.6</v>
       </c>
-      <c r="I19" s="232">
+      <c r="I19" s="223">
         <v>32.07</v>
       </c>
-      <c r="J19" s="227">
+      <c r="J19" s="231">
         <v>19.86</v>
       </c>
-      <c r="K19" s="233">
+      <c r="K19" s="229">
         <v>10.83</v>
       </c>
-      <c r="L19" s="228">
+      <c r="L19" s="233">
         <v>7.1</v>
       </c>
-      <c r="M19" s="226">
+      <c r="M19" s="224">
         <v>12.21</v>
       </c>
-      <c r="N19" s="234">
+      <c r="N19" s="225">
         <v>19.07</v>
       </c>
-      <c r="O19" s="222">
+      <c r="O19" s="232">
         <v>16.13</v>
       </c>
-      <c r="P19" s="229">
+      <c r="P19" s="234">
         <v>10.95</v>
       </c>
-      <c r="Q19" s="230">
+      <c r="Q19" s="226">
         <v>8.72</v>
       </c>
-      <c r="R19" s="231">
+      <c r="R19" s="227">
         <v>8.78</v>
       </c>
-      <c r="S19" s="223">
+      <c r="S19" s="230">
         <v>9.81</v>
       </c>
-      <c r="T19" s="224">
+      <c r="T19" s="222">
         <v>-2.53</v>
       </c>
     </row>
@@ -8662,7 +8710,7 @@
       <c r="C20" t="str">
         <v>833580</v>
       </c>
-      <c r="D20" s="247" t="str">
+      <c r="D20" s="240" t="str">
         <v>净卖: -782.72万</v>
       </c>
       <c r="E20">
@@ -8677,40 +8725,40 @@
       <c r="H20">
         <v>8.88</v>
       </c>
-      <c r="I20" s="246">
+      <c r="I20" s="237">
         <v>-16.65</v>
       </c>
-      <c r="J20" s="235">
+      <c r="J20" s="247">
         <v>-22.93</v>
       </c>
-      <c r="K20" s="238">
+      <c r="K20" s="241">
         <v>-25.52</v>
       </c>
-      <c r="L20" s="239">
+      <c r="L20" s="238">
         <v>-21.97</v>
       </c>
-      <c r="M20" s="244">
+      <c r="M20" s="239">
         <v>-17.2</v>
       </c>
-      <c r="N20" s="236">
+      <c r="N20" s="242">
         <v>-19.25</v>
       </c>
-      <c r="O20" s="240">
+      <c r="O20" s="244">
         <v>-22.85</v>
       </c>
-      <c r="P20" s="241">
+      <c r="P20" s="245">
         <v>-24.39</v>
       </c>
-      <c r="Q20" s="237">
+      <c r="Q20" s="246">
         <v>-24.35</v>
       </c>
-      <c r="R20" s="242">
+      <c r="R20" s="243">
         <v>-23.64</v>
       </c>
-      <c r="S20" s="243">
+      <c r="S20" s="235">
         <v>-28.45</v>
       </c>
-      <c r="T20" s="245">
+      <c r="T20" s="236">
         <v>-32.22</v>
       </c>
     </row>
@@ -8724,7 +8772,7 @@
       <c r="C21" t="str">
         <v>601068</v>
       </c>
-      <c r="D21" s="254" t="str">
+      <c r="D21" s="251" t="str">
         <v>净买: 656.95万</v>
       </c>
       <c r="E21">
@@ -8739,41 +8787,41 @@
       <c r="H21">
         <v>0</v>
       </c>
-      <c r="I21" s="248">
+      <c r="I21" s="255">
         <v>10.02</v>
       </c>
-      <c r="J21" s="251">
+      <c r="J21" s="252">
         <v>5.75</v>
       </c>
-      <c r="K21" s="255">
+      <c r="K21" s="256">
         <v>0.37</v>
       </c>
-      <c r="L21" s="260">
+      <c r="L21" s="253">
         <v>0</v>
       </c>
-      <c r="M21" s="252">
+      <c r="M21" s="254">
         <v>-1.86</v>
       </c>
-      <c r="N21" s="256">
+      <c r="N21" s="250">
         <v>0.19</v>
       </c>
-      <c r="O21" s="257">
+      <c r="O21" s="258">
         <v>0.37</v>
       </c>
-      <c r="P21" s="258">
+      <c r="P21" s="259">
         <v>-1.86</v>
       </c>
-      <c r="Q21" s="259">
+      <c r="Q21" s="260">
         <v>-1.11</v>
       </c>
-      <c r="R21" s="253">
+      <c r="R21" s="257">
         <v>-1.86</v>
       </c>
-      <c r="S21" s="249">
+      <c r="S21" s="248">
         <v>-0.74</v>
       </c>
-      <c r="T21" s="250">
-        <v>15.03</v>
+      <c r="T21" s="249">
+        <v>13.91</v>
       </c>
     </row>
     <row r="22">
@@ -8786,7 +8834,7 @@
       <c r="C22" t="str">
         <v>688146</v>
       </c>
-      <c r="D22" s="267" t="str">
+      <c r="D22" s="273" t="str">
         <v>净买: 1029.87万</v>
       </c>
       <c r="E22">
@@ -8801,41 +8849,41 @@
       <c r="H22">
         <v>-0.49</v>
       </c>
-      <c r="I22" s="270">
+      <c r="I22" s="269">
         <v>16.28</v>
       </c>
       <c r="J22" s="264">
         <v>21.96</v>
       </c>
-      <c r="K22" s="271">
+      <c r="K22" s="261">
         <v>26.12</v>
       </c>
-      <c r="L22" s="265">
+      <c r="L22" s="270">
         <v>18.55</v>
       </c>
-      <c r="M22" s="272">
+      <c r="M22" s="271">
         <v>21.14</v>
       </c>
-      <c r="N22" s="273">
+      <c r="N22" s="265">
         <v>18.6</v>
       </c>
-      <c r="O22" s="268">
+      <c r="O22" s="263">
         <v>17.6</v>
       </c>
-      <c r="P22" s="261">
+      <c r="P22" s="266">
         <v>15.63</v>
       </c>
-      <c r="Q22" s="269">
+      <c r="Q22" s="267">
         <v>18.84</v>
       </c>
-      <c r="R22" s="262">
+      <c r="R22" s="268">
         <v>17.44</v>
       </c>
-      <c r="S22" s="263">
+      <c r="S22" s="262">
         <v>15.25</v>
       </c>
-      <c r="T22" s="266">
-        <v>84.5</v>
+      <c r="T22" s="272">
+        <v>91.27</v>
       </c>
     </row>
     <row r="23">
@@ -8848,7 +8896,7 @@
       <c r="C23" t="str">
         <v>600678</v>
       </c>
-      <c r="D23" s="282" t="str">
+      <c r="D23" s="284" t="str">
         <v>净卖: -1248.78万</v>
       </c>
       <c r="E23">
@@ -8863,41 +8911,41 @@
       <c r="H23">
         <v>-7.51</v>
       </c>
-      <c r="I23" s="286">
+      <c r="I23" s="285">
         <v>-2.71</v>
       </c>
-      <c r="J23" s="274">
+      <c r="J23" s="277">
         <v>-7.69</v>
       </c>
-      <c r="K23" s="275">
+      <c r="K23" s="281">
         <v>-3.85</v>
       </c>
-      <c r="L23" s="283">
+      <c r="L23" s="274">
         <v>-4.99</v>
       </c>
-      <c r="M23" s="279">
+      <c r="M23" s="275">
         <v>-9.33</v>
       </c>
-      <c r="N23" s="276">
+      <c r="N23" s="278">
         <v>-8.05</v>
       </c>
-      <c r="O23" s="277">
+      <c r="O23" s="286">
         <v>-3.7</v>
       </c>
-      <c r="P23" s="278">
+      <c r="P23" s="282">
         <v>-5.98</v>
       </c>
-      <c r="Q23" s="280">
+      <c r="Q23" s="276">
         <v>-8.9</v>
       </c>
-      <c r="R23" s="284">
+      <c r="R23" s="279">
         <v>-4.49</v>
       </c>
-      <c r="S23" s="281">
+      <c r="S23" s="283">
         <v>-2.49</v>
       </c>
-      <c r="T23" s="285">
-        <v>-20.37</v>
+      <c r="T23" s="280">
+        <v>-22.15</v>
       </c>
     </row>
     <row r="24">
@@ -8910,7 +8958,7 @@
       <c r="C24" t="str">
         <v>301449</v>
       </c>
-      <c r="D24" s="295" t="str">
+      <c r="D24" s="291" t="str">
         <v>净卖: -1931.35万</v>
       </c>
       <c r="E24">
@@ -8925,41 +8973,41 @@
       <c r="H24">
         <v>-7.39</v>
       </c>
-      <c r="I24" s="296">
+      <c r="I24" s="293">
         <v>-10.16</v>
       </c>
-      <c r="J24" s="293">
+      <c r="J24" s="296">
         <v>-12.52</v>
       </c>
-      <c r="K24" s="297">
+      <c r="K24" s="289">
         <v>-14.52</v>
       </c>
-      <c r="L24" s="289">
+      <c r="L24" s="292">
         <v>-15.32</v>
       </c>
-      <c r="M24" s="291">
+      <c r="M24" s="297">
         <v>-9.86</v>
       </c>
       <c r="N24" s="298">
         <v>-11.91</v>
       </c>
-      <c r="O24" s="299">
+      <c r="O24" s="290">
         <v>-12.71</v>
       </c>
-      <c r="P24" s="287">
+      <c r="P24" s="299">
         <v>-12.71</v>
       </c>
-      <c r="Q24" s="290">
+      <c r="Q24" s="294">
         <v>-16.26</v>
       </c>
-      <c r="R24" s="288">
+      <c r="R24" s="287">
         <v>-10.13</v>
       </c>
-      <c r="S24" s="294">
+      <c r="S24" s="295">
         <v>-12.25</v>
       </c>
-      <c r="T24" s="292">
-        <v>-18.32</v>
+      <c r="T24" s="288">
+        <v>-27.07</v>
       </c>
     </row>
     <row r="25">
@@ -8972,7 +9020,7 @@
       <c r="C25" t="str">
         <v>688137</v>
       </c>
-      <c r="D25" s="304" t="str">
+      <c r="D25" s="306" t="str">
         <v>净买: 809.16万</v>
       </c>
       <c r="E25">
@@ -8987,41 +9035,41 @@
       <c r="H25">
         <v>-0.09</v>
       </c>
-      <c r="I25" s="302">
+      <c r="I25" s="309">
         <v>15.54</v>
       </c>
-      <c r="J25" s="305">
+      <c r="J25" s="307">
         <v>13.21</v>
       </c>
-      <c r="K25" s="312">
+      <c r="K25" s="311">
         <v>11.95</v>
       </c>
-      <c r="L25" s="303">
+      <c r="L25" s="312">
         <v>9.95</v>
       </c>
-      <c r="M25" s="306">
+      <c r="M25" s="308">
         <v>6.85</v>
       </c>
-      <c r="N25" s="307">
+      <c r="N25" s="304">
         <v>6.78</v>
       </c>
-      <c r="O25" s="308">
+      <c r="O25" s="300">
         <v>13.58</v>
       </c>
-      <c r="P25" s="300">
+      <c r="P25" s="310">
         <v>14.61</v>
       </c>
       <c r="Q25" s="301">
         <v>16.47</v>
       </c>
-      <c r="R25" s="309">
+      <c r="R25" s="305">
         <v>23.92</v>
       </c>
-      <c r="S25" s="310">
+      <c r="S25" s="302">
         <v>15.3</v>
       </c>
-      <c r="T25" s="311">
-        <v>13.6</v>
+      <c r="T25" s="303">
+        <v>14.37</v>
       </c>
     </row>
     <row r="26">
@@ -9034,7 +9082,7 @@
       <c r="C26" t="str">
         <v>301408</v>
       </c>
-      <c r="D26" s="319" t="str">
+      <c r="D26" s="324" t="str">
         <v>净卖: -2207.20万</v>
       </c>
       <c r="E26">
@@ -9052,38 +9100,38 @@
       <c r="I26" s="325">
         <v>18.28</v>
       </c>
-      <c r="J26" s="320">
+      <c r="J26" s="319">
         <v>-5.37</v>
       </c>
-      <c r="K26" s="316">
+      <c r="K26" s="315">
         <v>-14.43</v>
       </c>
-      <c r="L26" s="317">
+      <c r="L26" s="313">
         <v>-13.43</v>
       </c>
-      <c r="M26" s="321">
+      <c r="M26" s="320">
         <v>-12.24</v>
       </c>
-      <c r="N26" s="322">
+      <c r="N26" s="314">
         <v>-13.31</v>
       </c>
-      <c r="O26" s="323">
+      <c r="O26" s="316">
         <v>-7.91</v>
       </c>
-      <c r="P26" s="313">
+      <c r="P26" s="317">
         <v>-4.69</v>
       </c>
-      <c r="Q26" s="318">
+      <c r="Q26" s="321">
         <v>-0.32</v>
       </c>
-      <c r="R26" s="314">
+      <c r="R26" s="318">
         <v>-8.55</v>
       </c>
-      <c r="S26" s="324">
+      <c r="S26" s="322">
         <v>-11.88</v>
       </c>
-      <c r="T26" s="315">
-        <v>-20.63</v>
+      <c r="T26" s="323">
+        <v>-18.6</v>
       </c>
     </row>
     <row r="27">
@@ -9096,7 +9144,7 @@
       <c r="C27" t="str">
         <v>603598</v>
       </c>
-      <c r="D27" s="334" t="str">
+      <c r="D27" s="332" t="str">
         <v>净卖: -958.53万</v>
       </c>
       <c r="E27">
@@ -9111,41 +9159,41 @@
       <c r="H27">
         <v>-10.01</v>
       </c>
-      <c r="I27" s="335">
+      <c r="I27" s="333">
         <v>0</v>
       </c>
-      <c r="J27" s="330">
+      <c r="J27" s="334">
         <v>-5.64</v>
       </c>
-      <c r="K27" s="332">
+      <c r="K27" s="328">
         <v>-1.1</v>
       </c>
-      <c r="L27" s="331">
+      <c r="L27" s="326">
         <v>1.88</v>
       </c>
-      <c r="M27" s="336">
+      <c r="M27" s="330">
         <v>4.9</v>
       </c>
-      <c r="N27" s="337">
+      <c r="N27" s="335">
         <v>3.33</v>
       </c>
-      <c r="O27" s="333">
+      <c r="O27" s="336">
         <v>1.33</v>
       </c>
-      <c r="P27" s="326">
+      <c r="P27" s="331">
         <v>-0.86</v>
       </c>
-      <c r="Q27" s="327">
+      <c r="Q27" s="329">
         <v>4.62</v>
       </c>
-      <c r="R27" s="328">
+      <c r="R27" s="337">
         <v>15.09</v>
       </c>
-      <c r="S27" s="329">
+      <c r="S27" s="338">
         <v>13.64</v>
       </c>
-      <c r="T27" s="338">
-        <v>-19.67</v>
+      <c r="T27" s="327">
+        <v>-22.49</v>
       </c>
     </row>
     <row r="28">
@@ -9158,7 +9206,7 @@
       <c r="C28" t="str">
         <v>920368</v>
       </c>
-      <c r="D28" s="341" t="str">
+      <c r="D28" s="349" t="str">
         <v>净买: 2785.37万</v>
       </c>
       <c r="E28">
@@ -9173,41 +9221,41 @@
       <c r="H28">
         <v>6.62</v>
       </c>
-      <c r="I28" s="346">
+      <c r="I28" s="350">
         <v>21.92</v>
       </c>
-      <c r="J28" s="347">
+      <c r="J28" s="341">
         <v>30.07</v>
       </c>
-      <c r="K28" s="348">
+      <c r="K28" s="351">
         <v>52.53</v>
       </c>
-      <c r="L28" s="349">
+      <c r="L28" s="342">
         <v>59.26</v>
       </c>
-      <c r="M28" s="344">
+      <c r="M28" s="343">
         <v>51.53</v>
       </c>
-      <c r="N28" s="350">
+      <c r="N28" s="346">
         <v>48.42</v>
       </c>
-      <c r="O28" s="351">
+      <c r="O28" s="344">
         <v>50.72</v>
       </c>
       <c r="P28" s="339">
         <v>78.13</v>
       </c>
-      <c r="Q28" s="340">
+      <c r="Q28" s="345">
         <v>61.84</v>
       </c>
-      <c r="R28" s="342">
+      <c r="R28" s="340">
         <v>41.93</v>
       </c>
-      <c r="S28" s="343">
+      <c r="S28" s="347">
         <v>52.17</v>
       </c>
-      <c r="T28" s="345">
-        <v>-17.71</v>
+      <c r="T28" s="348">
+        <v>-19.31</v>
       </c>
     </row>
     <row r="29">
@@ -9220,7 +9268,7 @@
       <c r="C29" t="str">
         <v>300017</v>
       </c>
-      <c r="D29" s="356" t="str">
+      <c r="D29" s="352" t="str">
         <v>净卖: -8231.84万</v>
       </c>
       <c r="E29">
@@ -9235,41 +9283,41 @@
       <c r="H29">
         <v>1.57</v>
       </c>
-      <c r="I29" s="364">
+      <c r="I29" s="357">
         <v>18.18</v>
       </c>
-      <c r="J29" s="357">
+      <c r="J29" s="358">
         <v>16.12</v>
       </c>
-      <c r="K29" s="354">
+      <c r="K29" s="353">
         <v>33.7</v>
       </c>
-      <c r="L29" s="358">
+      <c r="L29" s="354">
         <v>44.08</v>
       </c>
-      <c r="M29" s="355">
+      <c r="M29" s="359">
         <v>42.02</v>
       </c>
-      <c r="N29" s="359">
+      <c r="N29" s="360">
         <v>44.77</v>
       </c>
-      <c r="O29" s="360">
+      <c r="O29" s="361">
         <v>65.61</v>
       </c>
-      <c r="P29" s="352">
+      <c r="P29" s="362">
         <v>43.4</v>
       </c>
-      <c r="Q29" s="361">
+      <c r="Q29" s="355">
         <v>54.12</v>
       </c>
-      <c r="R29" s="353">
+      <c r="R29" s="356">
         <v>53.77</v>
       </c>
-      <c r="S29" s="362">
+      <c r="S29" s="363">
         <v>62.09</v>
       </c>
-      <c r="T29" s="363">
-        <v>44.85</v>
+      <c r="T29" s="364">
+        <v>38.51</v>
       </c>
     </row>
     <row r="30">
@@ -9282,7 +9330,7 @@
       <c r="C30" t="str">
         <v>603075</v>
       </c>
-      <c r="D30" s="366" t="str">
+      <c r="D30" s="365" t="str">
         <v>净卖: -1295.61万</v>
       </c>
       <c r="E30">
@@ -9297,41 +9345,41 @@
       <c r="H30">
         <v>-0.04</v>
       </c>
-      <c r="I30" s="367">
+      <c r="I30" s="366">
         <v>1.83</v>
       </c>
-      <c r="J30" s="368">
+      <c r="J30" s="376">
         <v>-4.09</v>
       </c>
-      <c r="K30" s="369">
+      <c r="K30" s="367">
         <v>-6.43</v>
       </c>
-      <c r="L30" s="370">
+      <c r="L30" s="368">
         <v>-7.11</v>
       </c>
-      <c r="M30" s="371">
+      <c r="M30" s="369">
         <v>-5.88</v>
       </c>
-      <c r="N30" s="372">
+      <c r="N30" s="374">
         <v>-7.63</v>
       </c>
-      <c r="O30" s="373">
+      <c r="O30" s="370">
         <v>-5.52</v>
       </c>
-      <c r="P30" s="374">
+      <c r="P30" s="372">
         <v>-4.65</v>
       </c>
-      <c r="Q30" s="375">
+      <c r="Q30" s="373">
         <v>-5.2</v>
       </c>
-      <c r="R30" s="365">
+      <c r="R30" s="375">
         <v>-5.72</v>
       </c>
-      <c r="S30" s="376">
+      <c r="S30" s="371">
         <v>-4.92</v>
       </c>
       <c r="T30" s="377">
-        <v>-6.47</v>
+        <v>-7.59</v>
       </c>
     </row>
     <row r="31">
@@ -9344,7 +9392,7 @@
       <c r="C31" t="str">
         <v>920368</v>
       </c>
-      <c r="D31" s="389" t="str">
+      <c r="D31" s="383" t="str">
         <v>净卖: -476.30万</v>
       </c>
       <c r="E31">
@@ -9359,41 +9407,41 @@
       <c r="H31">
         <v>10.26</v>
       </c>
-      <c r="I31" s="385">
+      <c r="I31" s="378">
         <v>-3.25</v>
       </c>
-      <c r="J31" s="381">
+      <c r="J31" s="384">
         <v>13.46</v>
       </c>
-      <c r="K31" s="386">
+      <c r="K31" s="379">
         <v>18.46</v>
       </c>
-      <c r="L31" s="387">
+      <c r="L31" s="380">
         <v>12.71</v>
       </c>
-      <c r="M31" s="382">
+      <c r="M31" s="388">
         <v>10.4</v>
       </c>
-      <c r="N31" s="390">
+      <c r="N31" s="381">
         <v>12.12</v>
       </c>
-      <c r="O31" s="388">
+      <c r="O31" s="385">
         <v>32.5</v>
       </c>
-      <c r="P31" s="378">
+      <c r="P31" s="382">
         <v>20.38</v>
       </c>
-      <c r="Q31" s="383">
+      <c r="Q31" s="386">
         <v>5.58</v>
       </c>
-      <c r="R31" s="379">
+      <c r="R31" s="387">
         <v>13.19</v>
       </c>
-      <c r="S31" s="380">
+      <c r="S31" s="389">
         <v>23.15</v>
       </c>
-      <c r="T31" s="384">
-        <v>-38.79</v>
+      <c r="T31" s="390">
+        <v>-39.98</v>
       </c>
     </row>
     <row r="32">
@@ -9406,7 +9454,7 @@
       <c r="C32" t="str">
         <v>600273</v>
       </c>
-      <c r="D32" s="400" t="str">
+      <c r="D32" s="394" t="str">
         <v>净卖: -3657.56万</v>
       </c>
       <c r="E32">
@@ -9421,41 +9469,41 @@
       <c r="H32">
         <v>3.89</v>
       </c>
-      <c r="I32" s="393">
+      <c r="I32" s="395">
         <v>5.92</v>
       </c>
-      <c r="J32" s="398">
+      <c r="J32" s="400">
         <v>2.96</v>
       </c>
-      <c r="K32" s="399">
+      <c r="K32" s="396">
         <v>-4.88</v>
       </c>
-      <c r="L32" s="401">
+      <c r="L32" s="391">
         <v>-3.05</v>
       </c>
-      <c r="M32" s="402">
+      <c r="M32" s="398">
         <v>-1.31</v>
       </c>
-      <c r="N32" s="394">
+      <c r="N32" s="401">
         <v>-4.18</v>
       </c>
-      <c r="O32" s="395">
+      <c r="O32" s="399">
         <v>-1.74</v>
       </c>
-      <c r="P32" s="391">
+      <c r="P32" s="392">
         <v>-1.66</v>
       </c>
-      <c r="Q32" s="396">
+      <c r="Q32" s="402">
         <v>0.78</v>
       </c>
-      <c r="R32" s="397">
+      <c r="R32" s="403">
         <v>1.83</v>
       </c>
-      <c r="S32" s="403">
+      <c r="S32" s="393">
         <v>2.7</v>
       </c>
-      <c r="T32" s="392">
-        <v>-27.79</v>
+      <c r="T32" s="397">
+        <v>-27.96</v>
       </c>
     </row>
     <row r="33">
@@ -9483,41 +9531,41 @@
       <c r="H33">
         <v>2.76</v>
       </c>
-      <c r="I33" s="414">
+      <c r="I33" s="409">
         <v>16.77</v>
       </c>
-      <c r="J33" s="409">
+      <c r="J33" s="410">
         <v>17.59</v>
       </c>
-      <c r="K33" s="404">
+      <c r="K33" s="414">
         <v>16.46</v>
       </c>
-      <c r="L33" s="415">
+      <c r="L33" s="411">
         <v>7.35</v>
       </c>
-      <c r="M33" s="416">
+      <c r="M33" s="415">
         <v>14.56</v>
       </c>
-      <c r="N33" s="405">
+      <c r="N33" s="406">
         <v>8.23</v>
       </c>
-      <c r="O33" s="410">
+      <c r="O33" s="416">
         <v>8.64</v>
       </c>
-      <c r="P33" s="411">
+      <c r="P33" s="404">
         <v>8.67</v>
       </c>
-      <c r="Q33" s="412">
+      <c r="Q33" s="407">
         <v>5.17</v>
       </c>
-      <c r="R33" s="406">
+      <c r="R33" s="408">
         <v>1.33</v>
       </c>
-      <c r="S33" s="407">
+      <c r="S33" s="412">
         <v>1.8</v>
       </c>
-      <c r="T33" s="408">
-        <v>0.99</v>
+      <c r="T33" s="405">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="34">
@@ -9525,12 +9573,12 @@
         <v>2026-04-22</v>
       </c>
       <c r="B34" t="str">
-        <v>百利科技</v>
+        <v>ST百利</v>
       </c>
       <c r="C34" t="str">
         <v>603959</v>
       </c>
-      <c r="D34" s="418" t="str">
+      <c r="D34" s="419" t="str">
         <v>净买: 674.52万</v>
       </c>
       <c r="E34">
@@ -9545,16 +9593,18 @@
       <c r="H34">
         <v>1.2</v>
       </c>
-      <c r="I34" s="419">
+      <c r="I34" s="420">
         <v>-11.08</v>
       </c>
-      <c r="J34" s="420">
+      <c r="J34" s="421">
         <v>-12.85</v>
       </c>
-      <c r="K34" s="421">
+      <c r="K34" s="422">
         <v>-21.57</v>
       </c>
-      <c r="L34" t="str"/>
+      <c r="L34" s="417">
+        <v>-25.55</v>
+      </c>
       <c r="M34" t="str"/>
       <c r="N34" t="str"/>
       <c r="O34" t="str"/>
@@ -9562,8 +9612,8 @@
       <c r="Q34" t="str"/>
       <c r="R34" t="str"/>
       <c r="S34" t="str"/>
-      <c r="T34" s="417">
-        <v>-21.57</v>
+      <c r="T34" s="418">
+        <v>-25.55</v>
       </c>
     </row>
     <row r="35">
@@ -9571,7 +9621,7 @@
         <v>2026-04-24</v>
       </c>
       <c r="B35" t="str">
-        <v>百利科技</v>
+        <v>ST百利</v>
       </c>
       <c r="C35" t="str">
         <v>603959</v>
@@ -9591,10 +9641,12 @@
       <c r="H35">
         <v>-4.07</v>
       </c>
-      <c r="I35" s="422">
+      <c r="I35" s="424">
         <v>-6.18</v>
       </c>
-      <c r="J35" t="str"/>
+      <c r="J35" s="425">
+        <v>-10.95</v>
+      </c>
       <c r="K35" t="str"/>
       <c r="L35" t="str"/>
       <c r="M35" t="str"/>
@@ -9604,7 +9656,9 @@
       <c r="Q35" t="str"/>
       <c r="R35" t="str"/>
       <c r="S35" t="str"/>
-      <c r="T35" t="str"/>
+      <c r="T35" s="426">
+        <v>-10.95</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
@@ -9621,13 +9675,13 @@
         <v>34</v>
       </c>
       <c r="J36">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K36">
         <v>33</v>
       </c>
       <c r="L36">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M36">
         <v>32</v>
@@ -9651,7 +9705,7 @@
         <v>32</v>
       </c>
       <c r="T36">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37">
@@ -9668,38 +9722,38 @@
       <c r="I37" s="428">
         <v>64.71</v>
       </c>
-      <c r="J37" s="432">
-        <v>69.7</v>
-      </c>
-      <c r="K37" s="424">
+      <c r="J37" s="429">
+        <v>67.65</v>
+      </c>
+      <c r="K37" s="438">
         <v>66.67</v>
       </c>
-      <c r="L37" s="433">
+      <c r="L37" s="434">
+        <v>66.67</v>
+      </c>
+      <c r="M37" s="430">
         <v>68.75</v>
       </c>
-      <c r="M37" s="426">
-        <v>68.75</v>
-      </c>
-      <c r="N37" s="427">
+      <c r="N37" s="435">
         <v>71.88</v>
       </c>
-      <c r="O37" s="425">
+      <c r="O37" s="432">
         <v>71.88</v>
       </c>
-      <c r="P37" s="429">
+      <c r="P37" s="436">
         <v>62.5</v>
       </c>
-      <c r="Q37" s="430">
+      <c r="Q37" s="427">
         <v>65.63</v>
       </c>
       <c r="R37" s="431">
         <v>62.5</v>
       </c>
-      <c r="S37" s="434">
+      <c r="S37" s="433">
         <v>65.63</v>
       </c>
-      <c r="T37" s="435">
-        <v>36.36</v>
+      <c r="T37" s="437">
+        <v>35.29</v>
       </c>
     </row>
     <row r="38">
@@ -9713,41 +9767,41 @@
       <c r="F38" t="str"/>
       <c r="G38" t="str"/>
       <c r="H38" t="str"/>
-      <c r="I38" s="442">
+      <c r="I38" s="443">
         <v>7.55</v>
       </c>
-      <c r="J38" s="439">
-        <v>9.44</v>
-      </c>
-      <c r="K38" s="440">
+      <c r="J38" s="449">
+        <v>8.84</v>
+      </c>
+      <c r="K38" s="441">
         <v>10.47</v>
       </c>
-      <c r="L38" s="436">
-        <v>10.84</v>
-      </c>
-      <c r="M38" s="446">
+      <c r="L38" s="450">
+        <v>9.74</v>
+      </c>
+      <c r="M38" s="447">
         <v>11.29</v>
       </c>
-      <c r="N38" s="443">
+      <c r="N38" s="442">
         <v>10.99</v>
       </c>
       <c r="O38" s="444">
         <v>12.53</v>
       </c>
-      <c r="P38" s="437">
+      <c r="P38" s="445">
         <v>11.98</v>
       </c>
-      <c r="Q38" s="438">
+      <c r="Q38" s="439">
         <v>10.83</v>
       </c>
-      <c r="R38" s="445">
+      <c r="R38" s="446">
         <v>10.67</v>
       </c>
-      <c r="S38" s="447">
+      <c r="S38" s="448">
         <v>10.08</v>
       </c>
-      <c r="T38" s="441">
-        <v>3.05</v>
+      <c r="T38" s="440">
+        <v>1.93</v>
       </c>
     </row>
   </sheetData>
